--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10431.3</v>
+        <v>10494.4</v>
       </c>
       <c r="C2" t="n">
-        <v>10523.5</v>
+        <v>10508.6</v>
       </c>
       <c r="D2" t="n">
-        <v>10428.6</v>
+        <v>10468.4</v>
       </c>
       <c r="E2" t="n">
-        <v>10494.2</v>
+        <v>10508.6</v>
       </c>
       <c r="F2" t="n">
-        <v>63.6</v>
+        <v>14.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0014</v>
       </c>
       <c r="H2" t="n">
-        <v>94.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="I2" t="n">
-        <v>10268.3</v>
+        <v>10333.7</v>
       </c>
       <c r="J2" t="n">
-        <v>10247.68</v>
+        <v>10408.38</v>
       </c>
       <c r="K2" t="n">
-        <v>10355.15</v>
+        <v>10446.75</v>
       </c>
       <c r="L2" t="n">
-        <v>10462.62</v>
+        <v>10485.12</v>
       </c>
       <c r="M2" t="n">
-        <v>10506.05</v>
+        <v>10541.65</v>
       </c>
       <c r="N2" t="n">
-        <v>10549.47</v>
+        <v>10598.18</v>
       </c>
       <c r="O2" t="n">
-        <v>10721</v>
+        <v>10618.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -697,13 +697,11 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -725,63 +723,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10494.4</v>
+        <v>10510.2</v>
       </c>
       <c r="C3" t="n">
-        <v>10508.6</v>
+        <v>10510.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10468.4</v>
+        <v>10376.6</v>
       </c>
       <c r="E3" t="n">
-        <v>10508.6</v>
+        <v>10399.7</v>
       </c>
       <c r="F3" t="n">
-        <v>14.4</v>
+        <v>-108.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0104</v>
       </c>
       <c r="H3" t="n">
-        <v>40.2</v>
+        <v>133.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10333.7</v>
+        <v>10428.2</v>
       </c>
       <c r="J3" t="n">
-        <v>10408.38</v>
+        <v>10478.45</v>
       </c>
       <c r="K3" t="n">
-        <v>10446.75</v>
+        <v>10488.5</v>
       </c>
       <c r="L3" t="n">
-        <v>10485.12</v>
+        <v>10498.55</v>
       </c>
       <c r="M3" t="n">
-        <v>10541.65</v>
+        <v>10528.7</v>
       </c>
       <c r="N3" t="n">
-        <v>10598.18</v>
+        <v>10558.85</v>
       </c>
       <c r="O3" t="n">
-        <v>10618.4</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10548.8</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,9 +797,9 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -807,66 +811,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10510.2</v>
+        <v>10400.5</v>
       </c>
       <c r="C4" t="n">
-        <v>10510.2</v>
+        <v>10418.6</v>
       </c>
       <c r="D4" t="n">
-        <v>10376.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E4" t="n">
-        <v>10399.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-108.9</v>
+        <v>-36.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0104</v>
+        <v>-0.0035</v>
       </c>
       <c r="H4" t="n">
-        <v>133.6</v>
+        <v>65.7</v>
       </c>
       <c r="I4" t="n">
-        <v>10428.2</v>
+        <v>10243</v>
       </c>
       <c r="J4" t="n">
-        <v>10478.45</v>
+        <v>10244.25</v>
       </c>
       <c r="K4" t="n">
-        <v>10488.5</v>
+        <v>10332.9</v>
       </c>
       <c r="L4" t="n">
-        <v>10498.55</v>
+        <v>10421.55</v>
       </c>
       <c r="M4" t="n">
-        <v>10528.7</v>
+        <v>10466.5</v>
       </c>
       <c r="N4" t="n">
-        <v>10558.85</v>
+        <v>10511.45</v>
       </c>
       <c r="O4" t="n">
-        <v>10548.8</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>10643.8</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -886,59 +886,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10400.5</v>
+        <v>10363.6</v>
       </c>
       <c r="C5" t="n">
-        <v>10418.6</v>
+        <v>10443.2</v>
       </c>
       <c r="D5" t="n">
-        <v>10352.9</v>
+        <v>10346.6</v>
       </c>
       <c r="E5" t="n">
-        <v>10363.3</v>
+        <v>10437.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-36.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0072</v>
       </c>
       <c r="H5" t="n">
-        <v>65.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>10243</v>
+        <v>10287.2</v>
       </c>
       <c r="J5" t="n">
-        <v>10244.25</v>
+        <v>10286.38</v>
       </c>
       <c r="K5" t="n">
-        <v>10332.9</v>
+        <v>10330.45</v>
       </c>
       <c r="L5" t="n">
-        <v>10421.55</v>
+        <v>10374.52</v>
       </c>
       <c r="M5" t="n">
-        <v>10466.5</v>
+        <v>10396.15</v>
       </c>
       <c r="N5" t="n">
-        <v>10511.45</v>
+        <v>10417.77</v>
       </c>
       <c r="O5" t="n">
-        <v>10643.8</v>
+        <v>10484.3</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,103 +942,109 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10363.6</v>
+        <v>10438.2</v>
       </c>
       <c r="C6" t="n">
-        <v>10443.2</v>
+        <v>10462.2</v>
       </c>
       <c r="D6" t="n">
-        <v>10346.6</v>
+        <v>10332.4</v>
       </c>
       <c r="E6" t="n">
-        <v>10437.9</v>
+        <v>10428.9</v>
       </c>
       <c r="F6" t="n">
-        <v>74.59999999999999</v>
+        <v>-9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0009</v>
       </c>
       <c r="H6" t="n">
-        <v>96.59999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="I6" t="n">
-        <v>10287.2</v>
+        <v>10250</v>
       </c>
       <c r="J6" t="n">
-        <v>10286.38</v>
+        <v>10362.8</v>
       </c>
       <c r="K6" t="n">
-        <v>10330.45</v>
+        <v>10389.6</v>
       </c>
       <c r="L6" t="n">
-        <v>10374.52</v>
+        <v>10416.4</v>
       </c>
       <c r="M6" t="n">
-        <v>10396.15</v>
+        <v>10486.2</v>
       </c>
       <c r="N6" t="n">
-        <v>10417.77</v>
+        <v>10556</v>
       </c>
       <c r="O6" t="n">
-        <v>10484.3</v>
+        <v>10539.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1054,78 +1056,76 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10438.2</v>
+        <v>10429</v>
       </c>
       <c r="C7" t="n">
-        <v>10462.2</v>
+        <v>10469.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10332.4</v>
+        <v>10407</v>
       </c>
       <c r="E7" t="n">
-        <v>10428.9</v>
+        <v>10461.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-9</v>
+        <v>32.7</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0031</v>
       </c>
       <c r="H7" t="n">
-        <v>129.8</v>
+        <v>62.3</v>
       </c>
       <c r="I7" t="n">
-        <v>10250</v>
+        <v>10202.6</v>
       </c>
       <c r="J7" t="n">
-        <v>10362.8</v>
+        <v>10314.9</v>
       </c>
       <c r="K7" t="n">
-        <v>10389.6</v>
+        <v>10364</v>
       </c>
       <c r="L7" t="n">
-        <v>10416.4</v>
+        <v>10413.1</v>
       </c>
       <c r="M7" t="n">
-        <v>10486.2</v>
+        <v>10493.8</v>
       </c>
       <c r="N7" t="n">
-        <v>10556</v>
+        <v>10574.5</v>
       </c>
       <c r="O7" t="n">
-        <v>10539.8</v>
+        <v>10592</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1138,59 +1138,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C8" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D8" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E8" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F8" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H8" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I8" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J8" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K8" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L8" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M8" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N8" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O8" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1198,8 +1194,10 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
@@ -1208,14 +1206,18 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1227,50 +1229,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C9" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D9" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E9" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F9" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H9" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I9" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J9" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K9" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L9" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M9" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N9" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O9" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,80 +1285,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C10" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D10" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E10" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F10" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H10" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J10" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K10" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L10" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M10" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N10" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O10" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,10 +1364,8 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
@@ -1390,57 +1388,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C11" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D11" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E11" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H11" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I11" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J11" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K11" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L11" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M11" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N11" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O11" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1451,78 +1449,80 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C12" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D12" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E12" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F12" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H12" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J12" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K12" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L12" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M12" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N12" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O12" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,83 +1530,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C13" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D13" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E13" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H13" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I13" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J13" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K13" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L13" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M13" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N13" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O13" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1619,78 +1619,80 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C14" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D14" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E14" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F14" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I14" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J14" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K14" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L14" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M14" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N14" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O14" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1698,30 +1700,22 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1733,50 +1727,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C15" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D15" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E15" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F15" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H15" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I15" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J15" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K15" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L15" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M15" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N15" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O15" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1784,16 +1778,20 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1806,55 +1804,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C16" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D16" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E16" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H16" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I16" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J16" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K16" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L16" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M16" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N16" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O16" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1862,14 +1864,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1888,78 +1888,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C17" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D17" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E17" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F17" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H17" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I17" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J17" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K17" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L17" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M17" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N17" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O17" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10842.8</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1967,9 +1967,9 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1977,69 +1977,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C18" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D18" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E18" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H18" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I18" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J18" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K18" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L18" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M18" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N18" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O18" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2061,50 +2055,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C19" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D19" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E19" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H19" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I19" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J19" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K19" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L19" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M19" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N19" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O19" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2115,9 +2109,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2134,55 +2128,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C20" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D20" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E20" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F20" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H20" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J20" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K20" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L20" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M20" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N20" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O20" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,16 +2188,20 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2214,63 +2216,65 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C21" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D21" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E21" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I21" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J21" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K21" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L21" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M21" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N21" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O21" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
@@ -2279,12 +2283,12 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2300,65 +2304,63 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C22" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D22" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E22" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F22" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H22" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I22" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J22" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K22" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L22" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M22" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N22" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O22" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
@@ -2367,13 +2369,11 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2388,57 +2388,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C23" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D23" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E23" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H23" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I23" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J23" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K23" t="n">
         <v>10464.6</v>
       </c>
       <c r="L23" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M23" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N23" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O23" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2453,11 +2453,13 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2472,57 +2474,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C24" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D24" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E24" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F24" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H24" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I24" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J24" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K24" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L24" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M24" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N24" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O24" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,10 +2532,8 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
@@ -2565,70 +2565,72 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C25" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D25" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E25" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F25" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H25" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I25" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J25" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K25" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L25" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M25" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N25" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O25" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2640,84 +2642,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C26" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D26" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E26" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H26" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I26" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J26" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K26" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L26" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M26" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N26" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O26" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2726,55 +2724,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C27" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D27" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E27" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F27" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H27" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I27" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J27" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K27" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L27" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M27" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N27" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O27" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2800,67 +2802,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C28" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D28" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E28" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F28" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H28" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I28" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J28" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K28" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L28" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M28" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N28" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O28" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2868,83 +2868,83 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C29" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D29" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E29" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H29" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I29" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J29" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K29" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L29" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M29" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N29" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O29" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2952,22 +2952,24 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2978,57 +2980,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C30" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D30" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E30" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F30" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H30" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I30" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J30" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K30" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L30" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M30" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N30" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O30" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3046,14 +3048,12 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3062,59 +3062,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C31" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D31" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E31" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F31" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I31" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J31" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K31" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L31" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M31" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N31" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O31" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3132,11 +3128,13 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3151,50 +3149,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C32" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D32" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E32" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F32" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H32" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I32" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J32" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K32" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L32" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M32" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N32" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O32" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3212,13 +3210,11 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3233,50 +3229,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C33" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D33" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E33" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F33" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I33" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J33" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K33" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L33" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M33" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N33" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O33" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3287,14 +3283,14 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3308,55 +3304,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C34" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D34" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E34" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H34" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I34" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J34" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K34" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L34" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M34" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N34" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O34" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,12 +3364,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3390,57 +3392,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C35" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D35" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E35" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F35" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J35" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K35" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L35" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M35" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N35" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O35" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3448,20 +3450,16 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3483,50 +3481,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C36" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D36" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E36" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F36" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H36" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I36" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J36" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K36" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L36" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M36" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N36" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O36" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3537,13 +3535,15 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3556,59 +3556,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C37" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D37" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E37" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F37" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H37" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I37" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J37" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K37" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L37" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M37" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N37" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O37" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,8 +3612,10 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
@@ -3629,8 +3627,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3640,55 +3640,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C38" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D38" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E38" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F38" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H38" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I38" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J38" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K38" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L38" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M38" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N38" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O38" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3696,25 +3700,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3726,57 +3724,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C39" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D39" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E39" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H39" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I39" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J39" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K39" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L39" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M39" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N39" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O39" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3787,16 +3785,20 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3808,57 +3810,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C40" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D40" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E40" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F40" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H40" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K40" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L40" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M40" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N40" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O40" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3866,23 +3868,21 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3894,57 +3894,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C41" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D41" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E41" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F41" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H41" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I41" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J41" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K41" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L41" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M41" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N41" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O41" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3952,14 +3952,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3985,50 +3983,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C42" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D42" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F42" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I42" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J42" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K42" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L42" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M42" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N42" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O42" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4036,8 +4034,10 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
@@ -4067,56 +4067,58 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C43" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D43" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E43" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F43" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H43" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J43" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K43" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L43" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M43" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N43" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O43" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4125,7 +4127,7 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4137,76 +4139,70 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C44" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D44" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E44" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F44" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H44" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I44" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J44" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K44" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L44" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M44" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N44" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O44" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4233,50 +4229,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C45" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D45" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E45" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H45" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I45" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J45" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K45" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L45" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M45" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N45" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O45" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4294,8 +4290,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4308,55 +4306,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C46" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D46" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E46" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F46" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I46" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J46" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K46" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L46" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M46" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N46" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O46" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4364,14 +4366,12 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4379,8 +4379,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4399,50 +4401,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C47" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D47" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E47" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F47" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H47" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J47" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K47" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L47" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M47" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N47" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O47" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4453,20 +4455,16 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4485,50 +4483,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C48" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D48" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E48" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F48" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H48" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I48" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J48" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K48" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L48" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M48" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N48" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O48" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4536,8 +4534,10 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
@@ -4560,57 +4560,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C49" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D49" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E49" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F49" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H49" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I49" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J49" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K49" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L49" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M49" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N49" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O49" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4618,21 +4618,23 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4644,57 +4646,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C50" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D50" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E50" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F50" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H50" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I50" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J50" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K50" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L50" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M50" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N50" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O50" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4712,13 +4714,11 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4737,50 +4737,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C51" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D51" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E51" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F51" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H51" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I51" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J51" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K51" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L51" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M51" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N51" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O51" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4821,50 +4821,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C52" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D52" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E52" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F52" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J52" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K52" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L52" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M52" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N52" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O52" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4872,17 +4872,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4898,78 +4900,80 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C53" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D53" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E53" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I53" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J53" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K53" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L53" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M53" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N53" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O53" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4982,78 +4986,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C54" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D54" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E54" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H54" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I54" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J54" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K54" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L54" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M54" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N54" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O54" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5070,68 +5064,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C55" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D55" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E55" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F55" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H55" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I55" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J55" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K55" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L55" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M55" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N55" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O55" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5148,78 +5152,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C56" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D56" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E56" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H56" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I56" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J56" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K56" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L56" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M56" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N56" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O56" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5236,55 +5232,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C57" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D57" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H57" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I57" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J57" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K57" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L57" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M57" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N57" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O57" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5292,21 +5292,23 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5318,57 +5320,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C58" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D58" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E58" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F58" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H58" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I58" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J58" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K58" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L58" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M58" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N58" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O58" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5381,18 +5383,14 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5404,57 +5402,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C59" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D59" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E59" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H59" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J59" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K59" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L59" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M59" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N59" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O59" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5462,16 +5460,20 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5486,57 +5488,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C60" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D60" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E60" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F60" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H60" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J60" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K60" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L60" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M60" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N60" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O60" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5554,10 +5556,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5570,65 +5570,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C61" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D61" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E61" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F61" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H61" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I61" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J61" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K61" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L61" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M61" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N61" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O61" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5659,64 +5659,60 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C62" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D62" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E62" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F62" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H62" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I62" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J62" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K62" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L62" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M62" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N62" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O62" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
@@ -5743,50 +5739,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C63" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D63" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E63" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F63" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H63" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I63" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J63" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K63" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L63" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M63" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N63" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O63" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5794,21 +5790,23 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5818,55 +5816,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10609</v>
+        <v>10650.92</v>
       </c>
       <c r="C64" t="n">
-        <v>10714.7</v>
+        <v>10734.85</v>
       </c>
       <c r="D64" t="n">
-        <v>10602.1</v>
+        <v>10650.92</v>
       </c>
       <c r="E64" t="n">
-        <v>10650.4</v>
+        <v>10697.57</v>
       </c>
       <c r="F64" t="n">
-        <v>41.5</v>
+        <v>47.17</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H64" t="n">
-        <v>112.6</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J64" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K64" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L64" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M64" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N64" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O64" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5887,10 +5889,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5913,25 +5913,25 @@
         </is>
       </c>
       <c r="I65" s="13" t="n">
-        <v>10489.5</v>
+        <v>10566.99</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>10533.8</v>
+        <v>10615.98</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>10594.1</v>
+        <v>10655.61</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>10654.4</v>
+        <v>10695.23</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>10706.7</v>
+        <v>10739.54</v>
       </c>
       <c r="N65" s="13" t="n">
-        <v>10759</v>
+        <v>10783.84</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>10827.3</v>
+        <v>10818.78</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,63 +641,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10494.4</v>
+        <v>10510.2</v>
       </c>
       <c r="C2" t="n">
-        <v>10508.6</v>
+        <v>10510.2</v>
       </c>
       <c r="D2" t="n">
-        <v>10468.4</v>
+        <v>10376.6</v>
       </c>
       <c r="E2" t="n">
-        <v>10508.6</v>
+        <v>10399.7</v>
       </c>
       <c r="F2" t="n">
-        <v>14.4</v>
+        <v>-108.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0104</v>
       </c>
       <c r="H2" t="n">
-        <v>40.2</v>
+        <v>133.6</v>
       </c>
       <c r="I2" t="n">
-        <v>10333.7</v>
+        <v>10428.2</v>
       </c>
       <c r="J2" t="n">
-        <v>10408.38</v>
+        <v>10478.45</v>
       </c>
       <c r="K2" t="n">
-        <v>10446.75</v>
+        <v>10488.5</v>
       </c>
       <c r="L2" t="n">
-        <v>10485.12</v>
+        <v>10498.55</v>
       </c>
       <c r="M2" t="n">
-        <v>10541.65</v>
+        <v>10528.7</v>
       </c>
       <c r="N2" t="n">
-        <v>10598.18</v>
+        <v>10558.85</v>
       </c>
       <c r="O2" t="n">
-        <v>10618.4</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>10548.8</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,7 +717,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -723,67 +729,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10510.2</v>
+        <v>10400.5</v>
       </c>
       <c r="C3" t="n">
-        <v>10510.2</v>
+        <v>10418.6</v>
       </c>
       <c r="D3" t="n">
-        <v>10376.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E3" t="n">
-        <v>10399.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-108.9</v>
+        <v>-36.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0104</v>
+        <v>-0.0035</v>
       </c>
       <c r="H3" t="n">
-        <v>133.6</v>
+        <v>65.7</v>
       </c>
       <c r="I3" t="n">
-        <v>10428.2</v>
+        <v>10243</v>
       </c>
       <c r="J3" t="n">
-        <v>10478.45</v>
+        <v>10244.25</v>
       </c>
       <c r="K3" t="n">
-        <v>10488.5</v>
+        <v>10332.9</v>
       </c>
       <c r="L3" t="n">
-        <v>10498.55</v>
+        <v>10421.55</v>
       </c>
       <c r="M3" t="n">
-        <v>10528.7</v>
+        <v>10466.5</v>
       </c>
       <c r="N3" t="n">
-        <v>10558.85</v>
+        <v>10511.45</v>
       </c>
       <c r="O3" t="n">
-        <v>10548.8</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>10643.8</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -797,64 +799,60 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10400.5</v>
+        <v>10363.6</v>
       </c>
       <c r="C4" t="n">
-        <v>10418.6</v>
+        <v>10443.2</v>
       </c>
       <c r="D4" t="n">
-        <v>10352.9</v>
+        <v>10346.6</v>
       </c>
       <c r="E4" t="n">
-        <v>10363.3</v>
+        <v>10437.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-36.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0072</v>
       </c>
       <c r="H4" t="n">
-        <v>65.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10243</v>
+        <v>10287.2</v>
       </c>
       <c r="J4" t="n">
-        <v>10244.25</v>
+        <v>10286.38</v>
       </c>
       <c r="K4" t="n">
-        <v>10332.9</v>
+        <v>10330.45</v>
       </c>
       <c r="L4" t="n">
-        <v>10421.55</v>
+        <v>10374.52</v>
       </c>
       <c r="M4" t="n">
-        <v>10466.5</v>
+        <v>10396.15</v>
       </c>
       <c r="N4" t="n">
-        <v>10511.45</v>
+        <v>10417.77</v>
       </c>
       <c r="O4" t="n">
-        <v>10643.8</v>
+        <v>10484.3</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,186 +860,190 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10363.6</v>
+        <v>10438.2</v>
       </c>
       <c r="C5" t="n">
-        <v>10443.2</v>
+        <v>10462.2</v>
       </c>
       <c r="D5" t="n">
-        <v>10346.6</v>
+        <v>10332.4</v>
       </c>
       <c r="E5" t="n">
-        <v>10437.9</v>
+        <v>10428.9</v>
       </c>
       <c r="F5" t="n">
-        <v>74.59999999999999</v>
+        <v>-9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0009</v>
       </c>
       <c r="H5" t="n">
-        <v>96.59999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="I5" t="n">
-        <v>10287.2</v>
+        <v>10250</v>
       </c>
       <c r="J5" t="n">
-        <v>10286.38</v>
+        <v>10362.8</v>
       </c>
       <c r="K5" t="n">
-        <v>10330.45</v>
+        <v>10389.6</v>
       </c>
       <c r="L5" t="n">
-        <v>10374.52</v>
+        <v>10416.4</v>
       </c>
       <c r="M5" t="n">
-        <v>10396.15</v>
+        <v>10486.2</v>
       </c>
       <c r="N5" t="n">
-        <v>10417.77</v>
+        <v>10556</v>
       </c>
       <c r="O5" t="n">
-        <v>10484.3</v>
+        <v>10539.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10438.2</v>
+        <v>10429</v>
       </c>
       <c r="C6" t="n">
-        <v>10462.2</v>
+        <v>10469.3</v>
       </c>
       <c r="D6" t="n">
-        <v>10332.4</v>
+        <v>10407</v>
       </c>
       <c r="E6" t="n">
-        <v>10428.9</v>
+        <v>10461.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-9</v>
+        <v>32.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0031</v>
       </c>
       <c r="H6" t="n">
-        <v>129.8</v>
+        <v>62.3</v>
       </c>
       <c r="I6" t="n">
-        <v>10250</v>
+        <v>10202.6</v>
       </c>
       <c r="J6" t="n">
-        <v>10362.8</v>
+        <v>10314.9</v>
       </c>
       <c r="K6" t="n">
-        <v>10389.6</v>
+        <v>10364</v>
       </c>
       <c r="L6" t="n">
-        <v>10416.4</v>
+        <v>10413.1</v>
       </c>
       <c r="M6" t="n">
-        <v>10486.2</v>
+        <v>10493.8</v>
       </c>
       <c r="N6" t="n">
-        <v>10556</v>
+        <v>10574.5</v>
       </c>
       <c r="O6" t="n">
-        <v>10539.8</v>
+        <v>10592</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1049,64 +1051,60 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C7" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E7" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F7" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H7" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I7" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J7" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K7" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L7" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M7" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N7" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O7" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1114,26 +1112,32 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1143,50 +1147,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C8" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D8" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E8" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F8" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H8" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I8" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J8" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K8" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L8" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M8" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N8" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O8" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1201,78 +1205,76 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W8" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C9" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D9" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E9" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H9" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J9" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K9" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L9" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M9" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N9" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O9" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,12 +1282,10 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1299,64 +1299,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C10" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D10" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E10" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I10" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J10" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K10" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L10" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M10" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N10" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O10" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1369,76 +1369,78 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="9" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C11" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D11" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E11" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F11" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H11" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J11" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K11" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L11" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M11" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N11" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O11" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,83 +1448,83 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C12" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D12" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E12" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H12" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I12" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J12" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K12" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L12" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M12" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N12" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O12" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1537,76 +1539,78 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="9" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C13" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D13" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E13" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F13" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H13" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I13" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J13" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K13" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L13" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M13" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N13" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O13" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,32 +1618,24 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1649,50 +1645,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C14" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D14" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E14" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F14" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I14" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J14" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K14" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L14" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M14" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N14" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O14" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1700,16 +1696,20 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1717,60 +1717,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C15" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D15" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E15" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H15" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I15" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J15" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K15" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L15" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M15" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N15" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O15" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,14 +1782,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1799,83 +1801,83 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C16" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D16" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E16" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F16" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H16" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I16" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J16" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K16" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L16" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M16" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N16" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O16" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1885,7 +1887,7 @@
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1893,69 +1895,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C17" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D17" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E17" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H17" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I17" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J17" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K17" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L17" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M17" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N17" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O17" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1967,7 +1963,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1977,50 +1973,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C18" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D18" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E18" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H18" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I18" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J18" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K18" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L18" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M18" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N18" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O18" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,7 +2029,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2045,60 +2041,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C19" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D19" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E19" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F19" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H19" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J19" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K19" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L19" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M19" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N19" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O19" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,16 +2106,20 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2123,84 +2127,86 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C20" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D20" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E20" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H20" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I20" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J20" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K20" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L20" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M20" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N20" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O20" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2209,87 +2215,83 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C21" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D21" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E21" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F21" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H21" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I21" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J21" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K21" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L21" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M21" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N21" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O21" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2297,64 +2299,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C22" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D22" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E22" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H22" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I22" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J22" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K22" t="n">
         <v>10464.6</v>
       </c>
       <c r="L22" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M22" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N22" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O22" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,13 +2369,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2381,64 +2385,64 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C23" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D23" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E23" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F23" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H23" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I23" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J23" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K23" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L23" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M23" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N23" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O23" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,12 +2450,10 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2467,7 +2469,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2481,69 +2483,71 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C24" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D24" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E24" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F24" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H24" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I24" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J24" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K24" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L24" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M24" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N24" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O24" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2551,146 +2555,146 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C25" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D25" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E25" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H25" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I25" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J25" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K25" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L25" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M25" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N25" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O25" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C26" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D26" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E26" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F26" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H26" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I26" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J26" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K26" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L26" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M26" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N26" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O26" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2701,7 +2705,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2716,67 +2720,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C27" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D27" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E27" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F27" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H27" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I27" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J27" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K27" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L27" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M27" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N27" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O27" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,83 +2786,83 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C28" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D28" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E28" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H28" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I28" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J28" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K28" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L28" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M28" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N28" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O28" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2868,83 +2870,85 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C29" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D29" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E29" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F29" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H29" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I29" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J29" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K29" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L29" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M29" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N29" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O29" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2955,82 +2959,76 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C30" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D30" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E30" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F30" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I30" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J30" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K30" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L30" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M30" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N30" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O30" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,23 +3039,25 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3067,50 +3067,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C31" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D31" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E31" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F31" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H31" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I31" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J31" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K31" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L31" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M31" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N31" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O31" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,25 +3121,23 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3149,50 +3147,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C32" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D32" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E32" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F32" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I32" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J32" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K32" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L32" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M32" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N32" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O32" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,12 +3203,12 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3219,60 +3217,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C33" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D33" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E33" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H33" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I33" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J33" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K33" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L33" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M33" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N33" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O33" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,12 +3282,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3299,64 +3303,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C34" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D34" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E34" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F34" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J34" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K34" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L34" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M34" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N34" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O34" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,20 +3368,16 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3385,7 +3385,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3399,50 +3399,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C35" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D35" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E35" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F35" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H35" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I35" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J35" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K35" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L35" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M35" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N35" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O35" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3455,11 +3455,13 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3467,64 +3469,60 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C36" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D36" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E36" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F36" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H36" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I36" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J36" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K36" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L36" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M36" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N36" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O36" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,10 +3530,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3545,66 +3545,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C37" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D37" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E37" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F37" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H37" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I37" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J37" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K37" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L37" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M37" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N37" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O37" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3612,87 +3618,81 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C38" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D38" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E38" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H38" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I38" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J38" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K38" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L38" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M38" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N38" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O38" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,76 +3705,80 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C39" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D39" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E39" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F39" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H39" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J39" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K39" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L39" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M39" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N39" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O39" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,85 +3786,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C40" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D40" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E40" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F40" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H40" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I40" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J40" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K40" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L40" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M40" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N40" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O40" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3868,14 +3870,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3887,7 +3887,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3901,50 +3901,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C41" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D41" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E41" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F41" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J41" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K41" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L41" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M41" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N41" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O41" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3952,10 +3952,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3969,7 +3971,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3983,65 +3985,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C42" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D42" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E42" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F42" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H42" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J42" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K42" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L42" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M42" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N42" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O42" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4055,77 +4059,71 @@
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C43" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D43" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E43" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F43" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H43" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I43" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J43" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K43" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L43" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M43" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N43" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O43" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4139,7 +4137,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4149,50 +4147,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C44" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D44" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E44" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H44" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I44" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J44" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K44" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L44" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M44" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N44" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O44" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4205,13 +4203,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4219,60 +4219,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C45" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D45" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E45" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F45" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I45" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J45" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K45" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L45" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M45" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N45" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O45" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4280,14 +4284,12 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4295,13 +4297,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4315,50 +4319,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C46" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D46" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E46" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F46" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H46" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J46" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K46" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L46" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M46" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N46" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O46" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,23 +4375,19 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4401,50 +4401,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C47" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D47" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E47" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F47" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H47" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I47" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J47" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K47" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L47" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M47" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N47" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O47" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4452,10 +4452,12 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4469,64 +4471,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C48" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D48" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E48" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F48" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H48" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I48" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J48" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K48" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L48" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M48" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N48" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O48" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,83 +4536,85 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C49" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D49" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E49" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F49" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H49" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I49" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J49" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K49" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L49" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M49" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N49" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O49" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4621,25 +4625,23 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4653,50 +4655,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C50" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D50" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E50" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F50" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H50" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I50" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J50" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K50" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L50" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M50" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N50" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O50" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4707,7 +4709,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4723,7 +4725,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4737,50 +4739,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C51" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D51" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E51" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F51" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J51" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K51" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L51" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M51" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N51" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O51" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4788,17 +4790,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4807,70 +4811,74 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C52" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D52" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E52" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I52" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J52" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K52" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L52" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M52" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N52" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O52" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4879,13 +4887,11 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4893,83 +4899,73 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C53" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D53" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E53" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F53" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H53" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I53" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J53" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K53" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L53" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M53" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N53" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O53" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4981,73 +4977,83 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C54" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D54" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E54" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F54" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H54" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I54" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J54" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K54" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L54" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M54" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N54" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O54" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5059,83 +5065,75 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C55" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D55" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E55" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H55" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I55" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J55" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K55" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L55" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M55" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N55" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O55" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5147,60 +5145,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C56" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D56" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E56" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H56" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I56" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J56" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K56" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L56" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M56" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N56" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O56" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5208,83 +5210,85 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C57" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D57" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E57" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F57" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H57" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I57" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J57" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K57" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L57" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M57" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N57" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O57" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5295,82 +5299,78 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C58" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D58" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E58" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H58" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J58" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K58" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L58" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M58" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N58" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O58" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5378,16 +5378,20 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5395,64 +5399,64 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C59" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D59" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E59" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F59" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H59" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J59" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K59" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L59" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M59" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N59" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O59" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5465,15 +5469,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5481,79 +5483,79 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C60" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D60" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E60" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F60" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H60" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I60" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J60" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K60" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L60" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M60" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N60" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O60" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5565,7 +5567,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5575,67 +5577,63 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C61" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D61" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E61" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H61" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I61" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J61" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K61" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L61" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M61" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N61" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O61" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5649,7 +5647,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5659,50 +5657,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C62" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D62" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E62" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F62" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H62" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I62" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J62" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K62" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L62" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M62" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N62" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O62" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5710,79 +5708,85 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C63" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D63" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E63" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F63" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H63" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I63" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J63" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K63" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L63" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M63" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N63" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O63" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5793,7 +5797,7 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5803,15 +5807,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5823,115 +5825,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>10650.92</v>
-      </c>
-      <c r="C64" t="n">
-        <v>10734.85</v>
-      </c>
-      <c r="D64" t="n">
-        <v>10650.92</v>
-      </c>
-      <c r="E64" t="n">
-        <v>10697.57</v>
-      </c>
-      <c r="F64" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="H64" t="n">
-        <v>83.93000000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10489.5</v>
-      </c>
-      <c r="J64" t="n">
-        <v>10533.8</v>
-      </c>
-      <c r="K64" t="n">
-        <v>10594.1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>10654.4</v>
-      </c>
-      <c r="M64" t="n">
-        <v>10706.7</v>
-      </c>
-      <c r="N64" t="n">
-        <v>10759</v>
-      </c>
-      <c r="O64" t="n">
-        <v>10827.3</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
-        <v>10566.99</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>10615.98</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>10655.61</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>10695.23</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>10739.54</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>10783.84</v>
-      </c>
-      <c r="O65" s="13" t="n">
-        <v>10818.78</v>
+      <c r="I64" s="13" t="n">
+        <v>10566.9</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>10615.95</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>10655.6</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>10695.25</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>10739.6</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>10783.95</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>10818.9</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5825,31 +5825,113 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10697.76</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10697.76</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10586.39</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10658.13</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-39.47</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H64" t="n">
+        <v>111.37</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10566.9</v>
+      </c>
+      <c r="J64" t="n">
+        <v>10615.95</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10655.6</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10695.25</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10739.6</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10783.95</v>
+      </c>
+      <c r="O64" t="n">
+        <v>10818.9</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
-        <v>10566.9</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>10615.95</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>10655.6</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>10695.25</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>10739.6</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>10783.95</v>
-      </c>
-      <c r="O64" s="13" t="n">
-        <v>10818.9</v>
+      <c r="I65" s="13" t="n">
+        <v>10475.02</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>10554.79</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>10602.44</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>10650.1</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>10713.81</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>10777.53</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>10809.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,11 +115,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,66 +644,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10510.2</v>
+        <v>10400.5</v>
       </c>
       <c r="C2" t="n">
-        <v>10510.2</v>
+        <v>10418.6</v>
       </c>
       <c r="D2" t="n">
-        <v>10376.6</v>
+        <v>10352.9</v>
       </c>
       <c r="E2" t="n">
-        <v>10399.7</v>
+        <v>10363.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-108.9</v>
+        <v>-36.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0104</v>
+        <v>-0.0035</v>
       </c>
       <c r="H2" t="n">
-        <v>133.6</v>
+        <v>65.7</v>
       </c>
       <c r="I2" t="n">
-        <v>10428.2</v>
+        <v>10243</v>
       </c>
       <c r="J2" t="n">
-        <v>10478.45</v>
+        <v>10244.25</v>
       </c>
       <c r="K2" t="n">
-        <v>10488.5</v>
+        <v>10332.9</v>
       </c>
       <c r="L2" t="n">
-        <v>10498.55</v>
+        <v>10421.55</v>
       </c>
       <c r="M2" t="n">
-        <v>10528.7</v>
+        <v>10466.5</v>
       </c>
       <c r="N2" t="n">
-        <v>10558.85</v>
+        <v>10511.45</v>
       </c>
       <c r="O2" t="n">
-        <v>10548.8</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>10643.8</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -717,62 +716,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10400.5</v>
+        <v>10363.6</v>
       </c>
       <c r="C3" t="n">
-        <v>10418.6</v>
+        <v>10443.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10352.9</v>
+        <v>10346.6</v>
       </c>
       <c r="E3" t="n">
-        <v>10363.3</v>
+        <v>10437.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-36.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0072</v>
       </c>
       <c r="H3" t="n">
-        <v>65.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>10243</v>
+        <v>10287.2</v>
       </c>
       <c r="J3" t="n">
-        <v>10244.25</v>
+        <v>10286.38</v>
       </c>
       <c r="K3" t="n">
-        <v>10332.9</v>
+        <v>10330.45</v>
       </c>
       <c r="L3" t="n">
-        <v>10421.55</v>
+        <v>10374.52</v>
       </c>
       <c r="M3" t="n">
-        <v>10466.5</v>
+        <v>10396.15</v>
       </c>
       <c r="N3" t="n">
-        <v>10511.45</v>
+        <v>10417.77</v>
       </c>
       <c r="O3" t="n">
-        <v>10643.8</v>
+        <v>10484.3</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,186 +779,190 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10363.6</v>
+        <v>10438.2</v>
       </c>
       <c r="C4" t="n">
-        <v>10443.2</v>
+        <v>10462.2</v>
       </c>
       <c r="D4" t="n">
-        <v>10346.6</v>
+        <v>10332.4</v>
       </c>
       <c r="E4" t="n">
-        <v>10437.9</v>
+        <v>10428.9</v>
       </c>
       <c r="F4" t="n">
-        <v>74.59999999999999</v>
+        <v>-9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0009</v>
       </c>
       <c r="H4" t="n">
-        <v>96.59999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10287.2</v>
+        <v>10250</v>
       </c>
       <c r="J4" t="n">
-        <v>10286.38</v>
+        <v>10362.8</v>
       </c>
       <c r="K4" t="n">
-        <v>10330.45</v>
+        <v>10389.6</v>
       </c>
       <c r="L4" t="n">
-        <v>10374.52</v>
+        <v>10416.4</v>
       </c>
       <c r="M4" t="n">
-        <v>10396.15</v>
+        <v>10486.2</v>
       </c>
       <c r="N4" t="n">
-        <v>10417.77</v>
+        <v>10556</v>
       </c>
       <c r="O4" t="n">
-        <v>10484.3</v>
+        <v>10539.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10438.2</v>
+        <v>10429</v>
       </c>
       <c r="C5" t="n">
-        <v>10462.2</v>
+        <v>10469.3</v>
       </c>
       <c r="D5" t="n">
-        <v>10332.4</v>
+        <v>10407</v>
       </c>
       <c r="E5" t="n">
-        <v>10428.9</v>
+        <v>10461.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-9</v>
+        <v>32.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0031</v>
       </c>
       <c r="H5" t="n">
-        <v>129.8</v>
+        <v>62.3</v>
       </c>
       <c r="I5" t="n">
-        <v>10250</v>
+        <v>10202.6</v>
       </c>
       <c r="J5" t="n">
-        <v>10362.8</v>
+        <v>10314.9</v>
       </c>
       <c r="K5" t="n">
-        <v>10389.6</v>
+        <v>10364</v>
       </c>
       <c r="L5" t="n">
-        <v>10416.4</v>
+        <v>10413.1</v>
       </c>
       <c r="M5" t="n">
-        <v>10486.2</v>
+        <v>10493.8</v>
       </c>
       <c r="N5" t="n">
-        <v>10556</v>
+        <v>10574.5</v>
       </c>
       <c r="O5" t="n">
-        <v>10539.8</v>
+        <v>10592</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -967,64 +970,60 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C6" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D6" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E6" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F6" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H6" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I6" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J6" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K6" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L6" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M6" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N6" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O6" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1032,8 +1031,10 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
@@ -1042,16 +1043,20 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1061,50 +1066,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C7" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D7" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E7" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F7" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H7" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I7" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J7" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K7" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L7" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M7" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N7" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O7" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1117,80 +1122,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C8" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D8" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E8" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F8" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H8" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J8" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K8" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L8" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M8" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N8" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O8" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1198,10 +1201,8 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
@@ -1217,64 +1218,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C9" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D9" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E9" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I9" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J9" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K9" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L9" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M9" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N9" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O9" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1285,78 +1286,80 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C10" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E10" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F10" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H10" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J10" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K10" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L10" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M10" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N10" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O10" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,83 +1367,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C11" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D11" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E11" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H11" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I11" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J11" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K11" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L11" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M11" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N11" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O11" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1453,78 +1456,80 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C12" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D12" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E12" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F12" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H12" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I12" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J12" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K12" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L12" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M12" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N12" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O12" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1532,32 +1537,24 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W12" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1567,50 +1564,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C13" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D13" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E13" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F13" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H13" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I13" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J13" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K13" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L13" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M13" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N13" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O13" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1618,16 +1615,20 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1635,60 +1636,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C14" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D14" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E14" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H14" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I14" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J14" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K14" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L14" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M14" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N14" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O14" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1696,14 +1701,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1717,83 +1720,83 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C15" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D15" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E15" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F15" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H15" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I15" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J15" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K15" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L15" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M15" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N15" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O15" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10842.8</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1803,7 +1806,7 @@
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1811,69 +1814,63 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C16" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D16" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E16" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H16" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I16" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J16" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K16" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L16" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M16" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N16" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O16" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1885,7 +1882,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1895,50 +1892,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C17" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D17" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E17" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H17" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I17" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J17" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K17" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L17" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M17" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N17" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O17" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,9 +1946,9 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1963,60 +1960,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C18" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D18" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E18" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F18" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H18" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J18" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K18" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L18" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M18" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N18" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O18" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,16 +2025,20 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2041,70 +2046,72 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C19" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D19" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E19" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H19" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I19" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J19" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K19" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L19" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M19" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N19" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O19" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
@@ -2113,12 +2120,12 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2127,72 +2134,70 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C20" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D20" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E20" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F20" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H20" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I20" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J20" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K20" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L20" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M20" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N20" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O20" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2201,13 +2206,11 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2215,64 +2218,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C21" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D21" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E21" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H21" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I21" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J21" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K21" t="n">
         <v>10464.6</v>
       </c>
       <c r="L21" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M21" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N21" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O21" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,11 +2290,13 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2299,64 +2304,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C22" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D22" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E22" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F22" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H22" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I22" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J22" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K22" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L22" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M22" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N22" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O22" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2364,10 +2369,8 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
@@ -2385,7 +2388,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2399,216 +2402,218 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C23" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D23" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E23" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F23" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H23" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I23" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J23" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K23" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L23" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M23" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N23" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O23" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C24" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D24" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E24" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H24" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I24" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J24" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K24" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L24" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M24" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N24" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O24" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C25" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D25" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E25" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F25" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H25" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I25" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J25" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K25" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L25" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M25" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N25" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O25" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2634,67 +2639,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C26" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D26" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E26" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F26" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H26" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I26" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J26" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K26" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L26" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M26" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N26" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O26" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2702,83 +2705,83 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C27" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D27" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E27" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H27" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I27" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J27" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K27" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L27" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M27" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N27" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O27" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2786,83 +2789,85 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C28" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D28" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E28" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F28" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H28" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I28" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J28" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K28" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L28" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M28" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N28" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O28" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2880,75 +2885,69 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C29" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D29" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E29" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F29" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I29" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J29" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K29" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L29" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M29" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N29" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O29" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2966,16 +2965,18 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2985,50 +2986,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C30" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D30" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E30" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F30" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H30" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I30" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J30" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K30" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L30" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M30" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N30" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O30" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3046,18 +3047,16 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3067,50 +3066,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C31" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D31" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E31" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F31" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I31" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J31" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K31" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L31" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M31" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N31" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O31" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,14 +3120,14 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3137,60 +3136,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C32" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D32" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E32" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H32" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I32" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J32" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K32" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L32" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M32" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N32" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O32" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,12 +3201,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3217,64 +3222,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C33" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D33" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E33" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J33" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K33" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L33" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M33" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N33" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O33" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3282,20 +3287,16 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3303,7 +3304,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3317,50 +3318,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C34" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D34" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E34" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H34" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I34" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J34" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K34" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L34" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M34" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N34" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O34" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3371,13 +3372,15 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3385,64 +3388,60 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C35" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D35" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E35" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F35" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H35" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I35" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J35" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K35" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L35" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M35" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N35" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O35" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,8 +3449,10 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
@@ -3463,66 +3464,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C36" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D36" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E36" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F36" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H36" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I36" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J36" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K36" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L36" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M36" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N36" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O36" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3530,87 +3537,81 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C37" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D37" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E37" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H37" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I37" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J37" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K37" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L37" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M37" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N37" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O37" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3621,78 +3622,82 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C38" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D38" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E38" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F38" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H38" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J38" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K38" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L38" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M38" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N38" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O38" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3700,85 +3705,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C39" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D39" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E39" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F39" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H39" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I39" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J39" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K39" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L39" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M39" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N39" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O39" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,14 +3789,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3805,7 +3806,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3819,50 +3820,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C40" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D40" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E40" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F40" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J40" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K40" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L40" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M40" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N40" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O40" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,8 +3871,10 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
@@ -3887,7 +3890,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3901,56 +3904,58 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C41" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D41" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E41" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F41" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H41" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J41" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K41" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L41" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M41" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N41" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O41" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3959,7 +3964,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3973,76 +3978,70 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C42" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D42" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E42" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F42" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H42" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I42" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J42" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K42" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L42" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M42" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N42" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O42" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4057,7 +4056,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4067,50 +4066,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C43" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D43" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E43" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H43" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I43" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J43" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K43" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L43" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M43" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N43" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O43" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4128,8 +4127,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4137,60 +4138,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C44" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D44" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E44" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F44" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I44" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J44" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K44" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L44" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M44" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N44" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O44" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4198,14 +4203,12 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4213,13 +4216,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4233,50 +4238,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C45" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D45" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E45" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F45" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H45" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J45" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K45" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L45" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M45" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N45" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O45" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4287,25 +4292,21 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4319,50 +4320,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C46" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D46" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E46" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F46" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H46" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I46" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J46" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K46" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L46" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M46" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N46" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O46" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4370,8 +4371,10 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
@@ -4387,64 +4390,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C47" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D47" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E47" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F47" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H47" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I47" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J47" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K47" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L47" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M47" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N47" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O47" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4452,83 +4455,85 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C48" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D48" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E48" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F48" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H48" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I48" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J48" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K48" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L48" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M48" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N48" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O48" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4546,18 +4551,16 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4571,50 +4574,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C49" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D49" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E49" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F49" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H49" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I49" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J49" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K49" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L49" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M49" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N49" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O49" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4641,7 +4644,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4655,50 +4658,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C50" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D50" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E50" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F50" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J50" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K50" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L50" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M50" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N50" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O50" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4706,17 +4709,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4725,85 +4730,87 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C51" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D51" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E51" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I51" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J51" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K51" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L51" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M51" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N51" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O51" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4811,83 +4818,73 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C52" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D52" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E52" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F52" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H52" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I52" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J52" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K52" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L52" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M52" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N52" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O52" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4899,73 +4896,83 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C53" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D53" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E53" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F53" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H53" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I53" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J53" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K53" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L53" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M53" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N53" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O53" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4977,83 +4984,75 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C54" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D54" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E54" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H54" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I54" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J54" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K54" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L54" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M54" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N54" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O54" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5065,60 +5064,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C55" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D55" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E55" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H55" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I55" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J55" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K55" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L55" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M55" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N55" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O55" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5126,83 +5129,85 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C56" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D56" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E56" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F56" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H56" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I56" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J56" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K56" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L56" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M56" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N56" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O56" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5215,80 +5220,76 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C57" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D57" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E57" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H57" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J57" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K57" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L57" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M57" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N57" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O57" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5296,16 +5297,20 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5313,64 +5318,64 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C58" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D58" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E58" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H58" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J58" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K58" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L58" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M58" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N58" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O58" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5388,10 +5393,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5399,70 +5402,70 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C59" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D59" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E59" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F59" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H59" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I59" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J59" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K59" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L59" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M59" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N59" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O59" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5471,7 +5474,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5483,7 +5486,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5493,66 +5496,62 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C60" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D60" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E60" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F60" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H60" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I60" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J60" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K60" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L60" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M60" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N60" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O60" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5567,7 +5566,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5577,50 +5576,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C61" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D61" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E61" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F61" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H61" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I61" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J61" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K61" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L61" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M61" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N61" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O61" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5628,79 +5627,85 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C62" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D62" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E62" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F62" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H62" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I62" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J62" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K62" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L62" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M62" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N62" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O62" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5721,15 +5726,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5743,194 +5746,112 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10650.9</v>
+        <v>10697.76</v>
       </c>
       <c r="C63" t="n">
-        <v>10734.9</v>
+        <v>10697.76</v>
       </c>
       <c r="D63" t="n">
-        <v>10650.9</v>
+        <v>10586.39</v>
       </c>
       <c r="E63" t="n">
-        <v>10697.6</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>47.2</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0044</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>84</v>
+        <v>111.37</v>
       </c>
       <c r="I63" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J63" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K63" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L63" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M63" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N63" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O63" t="n">
-        <v>10827.3</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
+        <v>10818.9</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>10697.76</v>
-      </c>
-      <c r="C64" t="n">
-        <v>10697.76</v>
-      </c>
-      <c r="D64" t="n">
-        <v>10586.39</v>
-      </c>
-      <c r="E64" t="n">
-        <v>10658.13</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-39.47</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>-0.0037</v>
-      </c>
-      <c r="H64" t="n">
-        <v>111.37</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10566.9</v>
-      </c>
-      <c r="J64" t="n">
-        <v>10615.95</v>
-      </c>
-      <c r="K64" t="n">
-        <v>10655.6</v>
-      </c>
-      <c r="L64" t="n">
-        <v>10695.25</v>
-      </c>
-      <c r="M64" t="n">
-        <v>10739.6</v>
-      </c>
-      <c r="N64" t="n">
-        <v>10783.95</v>
-      </c>
-      <c r="O64" t="n">
-        <v>10818.9</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
+      <c r="I64" s="14" t="n">
         <v>10475.02</v>
       </c>
-      <c r="J65" s="13" t="n">
-        <v>10554.79</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>10602.44</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>10650.1</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>10713.81</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>10777.53</v>
-      </c>
-      <c r="O65" s="13" t="n">
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
         <v>10809.13</v>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5750,25 +5747,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10697.76</v>
+        <v>10697.8</v>
       </c>
       <c r="C63" t="n">
-        <v>10697.76</v>
+        <v>10697.8</v>
       </c>
       <c r="D63" t="n">
-        <v>10586.39</v>
+        <v>10586.4</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>10658.1</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>-39.5</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>-0.0037</v>
       </c>
       <c r="H63" t="n">
-        <v>111.37</v>
+        <v>111.4</v>
       </c>
       <c r="I63" t="n">
         <v>10566.9</v>
@@ -5791,24 +5788,22 @@
       <c r="O63" t="n">
         <v>10818.9</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5828,31 +5823,31 @@
       <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>10475.02</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>10809.13</v>
+      <c r="I64" s="13" t="n">
+        <v>10475</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>10554.7</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>10602.4</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>10650.1</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>10713.8</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>10777.5</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>10809.2</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5823,31 +5823,115 @@
       <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10658.22</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10731.31</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10655.82</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10722.09</v>
+      </c>
+      <c r="F64" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H64" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10475</v>
+      </c>
+      <c r="J64" t="n">
+        <v>10554.7</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10602.4</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10650.1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10713.8</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10777.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>10809.2</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
-        <v>10475</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>10554.7</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>10602.4</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>10650.1</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>10713.8</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>10777.5</v>
-      </c>
-      <c r="O64" s="13" t="n">
-        <v>10809.2</v>
+      <c r="I65" s="13" t="n">
+        <v>10580.33</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>10660.86</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>10684.35</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>10707.83</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>10759.83</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>10811.84</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>10806.8</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -5832,22 +5832,22 @@
         <v>10658.22</v>
       </c>
       <c r="C64" t="n">
-        <v>10731.31</v>
+        <v>10732.15</v>
       </c>
       <c r="D64" t="n">
         <v>10655.82</v>
       </c>
       <c r="E64" t="n">
-        <v>10722.09</v>
+        <v>10731.97</v>
       </c>
       <c r="F64" t="n">
-        <v>63.99</v>
+        <v>73.87</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0069</v>
       </c>
       <c r="H64" t="n">
-        <v>75.48999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="I64" t="n">
         <v>10475</v>
@@ -5913,25 +5913,25 @@
         </is>
       </c>
       <c r="I65" s="13" t="n">
-        <v>10580.33</v>
+        <v>10579.49</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>10660.86</v>
+        <v>10674.63</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>10684.35</v>
+        <v>10693.8</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>10707.83</v>
+        <v>10712.98</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>10759.83</v>
+        <v>10770.13</v>
       </c>
       <c r="N65" s="13" t="n">
-        <v>10811.84</v>
+        <v>10827.29</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>10806.8</v>
+        <v>10808.48</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -5832,22 +5832,22 @@
         <v>10658.22</v>
       </c>
       <c r="C64" t="n">
-        <v>10732.15</v>
+        <v>10735.34</v>
       </c>
       <c r="D64" t="n">
         <v>10655.82</v>
       </c>
       <c r="E64" t="n">
-        <v>10731.97</v>
+        <v>10734.64</v>
       </c>
       <c r="F64" t="n">
-        <v>73.87</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0072</v>
       </c>
       <c r="H64" t="n">
-        <v>76.33</v>
+        <v>79.52</v>
       </c>
       <c r="I64" t="n">
         <v>10475</v>
@@ -5913,25 +5913,25 @@
         </is>
       </c>
       <c r="I65" s="13" t="n">
-        <v>10579.49</v>
+        <v>10576.3</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>10674.63</v>
+        <v>10674.65</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>10693.8</v>
+        <v>10694.88</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>10712.98</v>
+        <v>10715.11</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>10770.13</v>
+        <v>10774.4</v>
       </c>
       <c r="N65" s="13" t="n">
-        <v>10827.29</v>
+        <v>10833.69</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>10808.48</v>
+        <v>10814.86</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -5838,13 +5838,13 @@
         <v>10655.82</v>
       </c>
       <c r="E64" t="n">
-        <v>10734.64</v>
+        <v>10688.47</v>
       </c>
       <c r="F64" t="n">
-        <v>76.54000000000001</v>
+        <v>30.37</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0072</v>
+        <v>0.0028</v>
       </c>
       <c r="H64" t="n">
         <v>79.52</v>
@@ -5916,19 +5916,19 @@
         <v>10576.3</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>10674.65</v>
+        <v>10605.4</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>10694.88</v>
+        <v>10648.71</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>10715.11</v>
+        <v>10692.02</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>10774.4</v>
+        <v>10728.23</v>
       </c>
       <c r="N65" s="13" t="n">
-        <v>10833.69</v>
+        <v>10764.43</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>10814.86</v>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,17 +109,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10400.5</v>
+        <v>10363.6</v>
       </c>
       <c r="C2" t="n">
-        <v>10418.6</v>
+        <v>10443.2</v>
       </c>
       <c r="D2" t="n">
-        <v>10352.9</v>
+        <v>10346.6</v>
       </c>
       <c r="E2" t="n">
-        <v>10363.3</v>
+        <v>10437.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-36.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0072</v>
       </c>
       <c r="H2" t="n">
-        <v>65.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>10243</v>
+        <v>10287.2</v>
       </c>
       <c r="J2" t="n">
-        <v>10244.25</v>
+        <v>10286.38</v>
       </c>
       <c r="K2" t="n">
-        <v>10332.9</v>
+        <v>10330.45</v>
       </c>
       <c r="L2" t="n">
-        <v>10421.55</v>
+        <v>10374.52</v>
       </c>
       <c r="M2" t="n">
-        <v>10466.5</v>
+        <v>10396.15</v>
       </c>
       <c r="N2" t="n">
-        <v>10511.45</v>
+        <v>10417.77</v>
       </c>
       <c r="O2" t="n">
-        <v>10643.8</v>
+        <v>10484.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,22 +695,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -718,81 +723,81 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10363.6</v>
+        <v>10438.2</v>
       </c>
       <c r="C3" t="n">
-        <v>10443.2</v>
+        <v>10462.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10346.6</v>
+        <v>10332.4</v>
       </c>
       <c r="E3" t="n">
-        <v>10437.9</v>
+        <v>10428.9</v>
       </c>
       <c r="F3" t="n">
-        <v>74.59999999999999</v>
+        <v>-9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0009</v>
       </c>
       <c r="H3" t="n">
-        <v>96.59999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="I3" t="n">
-        <v>10287.2</v>
+        <v>10250</v>
       </c>
       <c r="J3" t="n">
-        <v>10286.38</v>
+        <v>10362.8</v>
       </c>
       <c r="K3" t="n">
-        <v>10330.45</v>
+        <v>10389.6</v>
       </c>
       <c r="L3" t="n">
-        <v>10374.52</v>
+        <v>10416.4</v>
       </c>
       <c r="M3" t="n">
-        <v>10396.15</v>
+        <v>10486.2</v>
       </c>
       <c r="N3" t="n">
-        <v>10417.77</v>
+        <v>10556</v>
       </c>
       <c r="O3" t="n">
-        <v>10484.3</v>
+        <v>10539.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -804,78 +809,76 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10438.2</v>
+        <v>10429</v>
       </c>
       <c r="C4" t="n">
-        <v>10462.2</v>
+        <v>10469.3</v>
       </c>
       <c r="D4" t="n">
-        <v>10332.4</v>
+        <v>10407</v>
       </c>
       <c r="E4" t="n">
-        <v>10428.9</v>
+        <v>10461.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-9</v>
+        <v>32.7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0031</v>
       </c>
       <c r="H4" t="n">
-        <v>129.8</v>
+        <v>62.3</v>
       </c>
       <c r="I4" t="n">
-        <v>10250</v>
+        <v>10202.6</v>
       </c>
       <c r="J4" t="n">
-        <v>10362.8</v>
+        <v>10314.9</v>
       </c>
       <c r="K4" t="n">
-        <v>10389.6</v>
+        <v>10364</v>
       </c>
       <c r="L4" t="n">
-        <v>10416.4</v>
+        <v>10413.1</v>
       </c>
       <c r="M4" t="n">
-        <v>10486.2</v>
+        <v>10493.8</v>
       </c>
       <c r="N4" t="n">
-        <v>10556</v>
+        <v>10574.5</v>
       </c>
       <c r="O4" t="n">
-        <v>10539.8</v>
+        <v>10592</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -888,59 +891,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C5" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D5" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E5" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F5" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H5" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I5" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J5" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K5" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L5" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M5" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N5" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O5" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -948,24 +947,30 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -977,50 +982,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C6" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D6" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E6" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F6" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H6" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J6" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K6" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L6" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M6" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N6" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O6" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1035,78 +1040,76 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C7" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D7" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E7" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H7" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I7" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J7" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K7" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L7" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M7" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N7" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O7" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1114,12 +1117,10 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1140,57 +1141,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C8" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D8" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E8" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H8" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I8" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J8" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K8" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L8" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M8" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N8" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O8" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1203,76 +1204,78 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C9" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D9" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E9" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H9" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J9" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K9" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L9" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M9" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N9" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O9" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,83 +1283,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C10" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D10" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E10" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H10" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I10" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J10" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K10" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L10" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M10" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N10" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O10" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1371,76 +1374,78 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C11" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D11" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E11" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F11" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H11" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I11" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J11" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K11" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L11" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M11" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N11" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O11" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1448,30 +1453,22 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1483,50 +1480,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C12" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D12" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E12" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F12" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I12" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J12" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K12" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L12" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M12" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N12" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O12" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1534,16 +1531,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1556,55 +1557,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C13" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D13" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E13" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H13" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I13" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J13" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K13" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L13" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M13" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N13" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O13" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1612,14 +1617,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1638,78 +1641,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C14" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D14" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E14" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F14" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H14" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I14" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J14" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K14" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L14" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M14" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N14" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O14" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1717,9 +1720,9 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1727,69 +1730,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C15" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D15" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E15" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H15" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I15" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J15" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K15" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L15" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M15" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N15" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O15" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1811,50 +1808,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C16" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D16" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E16" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H16" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I16" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J16" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K16" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L16" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M16" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N16" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O16" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,7 +1864,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1884,55 +1881,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C17" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D17" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E17" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F17" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H17" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J17" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K17" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L17" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M17" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N17" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O17" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,16 +1941,20 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1964,77 +1969,79 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C18" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D18" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E18" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H18" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I18" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J18" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K18" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L18" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M18" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N18" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O18" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2050,80 +2057,76 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C19" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D19" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E19" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F19" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H19" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I19" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J19" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K19" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L19" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M19" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N19" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O19" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2138,57 +2141,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C20" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D20" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E20" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H20" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I20" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J20" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K20" t="n">
         <v>10464.6</v>
       </c>
       <c r="L20" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M20" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N20" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O20" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2201,13 +2204,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2222,57 +2227,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C21" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D21" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E21" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F21" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H21" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I21" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J21" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K21" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L21" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M21" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N21" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O21" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2280,12 +2285,10 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2315,69 +2318,71 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C22" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D22" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E22" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F22" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H22" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I22" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J22" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K22" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L22" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M22" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N22" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O22" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2390,84 +2395,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C23" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D23" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E23" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H23" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I23" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J23" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K23" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L23" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M23" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N23" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O23" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2476,55 +2477,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C24" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D24" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E24" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F24" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H24" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I24" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J24" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K24" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L24" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M24" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N24" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O24" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,7 +2540,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2550,67 +2555,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C25" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D25" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E25" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F25" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H25" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I25" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J25" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K25" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L25" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M25" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N25" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O25" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2618,83 +2621,83 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C26" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D26" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E26" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H26" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I26" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J26" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K26" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L26" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M26" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N26" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O26" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2702,22 +2705,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2728,57 +2733,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C27" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D27" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E27" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F27" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H27" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I27" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J27" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K27" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L27" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M27" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N27" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O27" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,21 +2794,19 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2812,59 +2815,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C28" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D28" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E28" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F28" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I28" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J28" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K28" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L28" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M28" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N28" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O28" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2875,18 +2874,20 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2901,50 +2902,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C29" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D29" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E29" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F29" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H29" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I29" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J29" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K29" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L29" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M29" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N29" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O29" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2955,20 +2956,18 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2983,50 +2982,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C30" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D30" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E30" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F30" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I30" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J30" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K30" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L30" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M30" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N30" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O30" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3039,12 +3038,12 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3058,55 +3057,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C31" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D31" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E31" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H31" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I31" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J31" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K31" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L31" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M31" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N31" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O31" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3114,12 +3117,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3140,57 +3145,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C32" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D32" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E32" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J32" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K32" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L32" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M32" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N32" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O32" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,20 +3203,16 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3233,50 +3234,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C33" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D33" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E33" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H33" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I33" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J33" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K33" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L33" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M33" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N33" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O33" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3289,11 +3290,13 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3306,59 +3309,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C34" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D34" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E34" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F34" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H34" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I34" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J34" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K34" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L34" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M34" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N34" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O34" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3366,10 +3365,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3379,8 +3380,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3390,55 +3393,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C35" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D35" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E35" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F35" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H35" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I35" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J35" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K35" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L35" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M35" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N35" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O35" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3446,25 +3453,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3476,57 +3477,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C36" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D36" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E36" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H36" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I36" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J36" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K36" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L36" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M36" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N36" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O36" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,14 +3540,18 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3558,57 +3563,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C37" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D37" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E37" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F37" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H37" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J37" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K37" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L37" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M37" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N37" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O37" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,23 +3621,21 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3644,57 +3647,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C38" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D38" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E38" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F38" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H38" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I38" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J38" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K38" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L38" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M38" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N38" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O38" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,14 +3705,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3735,50 +3736,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C39" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D39" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E39" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F39" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I39" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J39" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K39" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L39" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M39" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N39" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O39" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,10 +3787,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3817,65 +3820,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C40" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D40" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E40" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F40" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H40" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J40" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K40" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L40" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M40" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N40" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O40" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3887,79 +3892,73 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C41" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D41" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E41" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H41" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I41" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J41" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K41" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L41" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M41" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N41" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O41" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3983,50 +3982,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C42" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D42" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H42" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I42" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J42" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K42" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L42" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M42" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N42" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O42" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4039,13 +4038,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4058,55 +4059,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C43" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D43" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E43" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F43" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I43" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J43" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K43" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L43" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M43" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N43" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O43" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4114,14 +4119,12 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4129,8 +4132,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4149,50 +4154,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C44" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D44" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E44" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F44" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H44" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J44" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K44" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L44" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M44" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N44" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O44" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4205,18 +4210,14 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4235,50 +4236,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C45" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D45" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E45" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F45" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H45" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I45" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J45" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K45" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L45" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M45" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N45" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O45" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4286,10 +4287,12 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4310,57 +4313,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C46" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D46" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E46" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F46" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H46" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I46" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J46" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K46" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L46" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M46" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N46" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O46" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4368,21 +4371,23 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4394,57 +4399,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C47" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D47" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E47" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F47" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H47" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I47" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J47" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K47" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L47" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M47" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N47" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O47" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4455,20 +4460,18 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4487,50 +4490,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C48" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D48" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E48" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F48" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H48" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I48" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J48" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K48" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L48" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M48" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N48" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O48" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,7 +4544,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4571,50 +4574,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C49" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D49" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E49" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F49" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J49" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K49" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L49" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M49" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N49" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O49" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4622,17 +4625,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4648,63 +4653,67 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C50" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D50" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E50" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I50" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J50" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K50" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L50" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M50" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N50" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O50" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4713,13 +4722,11 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4732,78 +4739,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C51" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D51" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E51" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F51" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H51" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I51" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J51" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K51" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L51" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M51" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N51" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O51" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4820,68 +4817,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C52" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D52" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E52" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F52" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H52" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I52" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J52" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K52" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L52" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M52" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N52" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O52" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4898,78 +4905,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C53" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D53" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E53" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H53" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I53" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J53" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K53" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L53" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M53" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N53" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O53" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4986,55 +4985,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C54" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D54" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E54" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H54" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I54" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J54" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K54" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L54" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M54" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N54" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O54" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5042,21 +5045,23 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5068,57 +5073,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C55" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D55" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E55" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F55" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H55" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I55" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J55" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K55" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L55" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M55" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N55" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O55" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5129,20 +5134,16 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5154,57 +5155,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C56" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D56" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E56" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H56" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J56" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K56" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L56" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M56" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N56" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O56" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5212,16 +5213,20 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5236,57 +5241,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C57" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D57" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E57" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H57" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J57" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K57" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L57" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M57" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N57" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O57" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5299,15 +5304,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5320,74 +5323,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C58" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D58" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H58" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I58" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J58" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K58" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L58" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M58" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N58" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O58" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5409,67 +5412,63 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C59" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D59" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E59" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F59" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H59" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I59" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J59" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K59" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L59" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M59" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N59" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O59" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5493,50 +5492,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C60" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D60" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E60" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F60" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H60" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I60" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J60" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K60" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L60" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M60" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N60" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O60" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5544,21 +5543,23 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5568,55 +5569,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C61" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D61" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E61" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F61" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H61" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I61" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J61" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K61" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L61" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M61" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N61" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O61" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5627,7 +5632,7 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5637,10 +5642,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5659,69 +5662,71 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C62" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D62" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E62" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F62" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H62" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I62" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J62" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K62" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L62" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M62" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N62" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O62" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5734,80 +5739,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10697.8</v>
+        <v>10658.22</v>
       </c>
       <c r="C63" t="n">
-        <v>10697.8</v>
+        <v>10735.34</v>
       </c>
       <c r="D63" t="n">
-        <v>10586.4</v>
+        <v>10655.82</v>
       </c>
       <c r="E63" t="n">
-        <v>10658.1</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>-39.5</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0037</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>111.4</v>
+        <v>79.52</v>
       </c>
       <c r="I63" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J63" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K63" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L63" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M63" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N63" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O63" t="n">
-        <v>10818.9</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
+        <v>10809.2</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5820,117 +5821,37 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>10658.22</v>
-      </c>
-      <c r="C64" t="n">
-        <v>10735.34</v>
-      </c>
-      <c r="D64" t="n">
-        <v>10655.82</v>
-      </c>
-      <c r="E64" t="n">
-        <v>10688.47</v>
-      </c>
-      <c r="F64" t="n">
-        <v>30.37</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H64" t="n">
-        <v>79.52</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10475</v>
-      </c>
-      <c r="J64" t="n">
-        <v>10554.7</v>
-      </c>
-      <c r="K64" t="n">
-        <v>10602.4</v>
-      </c>
-      <c r="L64" t="n">
-        <v>10650.1</v>
-      </c>
-      <c r="M64" t="n">
-        <v>10713.8</v>
-      </c>
-      <c r="N64" t="n">
-        <v>10777.5</v>
-      </c>
-      <c r="O64" t="n">
-        <v>10809.2</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
+      <c r="I64" s="14" t="n">
         <v>10576.3</v>
       </c>
-      <c r="J65" s="13" t="n">
-        <v>10605.4</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>10648.71</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>10692.02</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>10728.23</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>10764.43</v>
-      </c>
-      <c r="O65" s="13" t="n">
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
         <v>10814.86</v>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -490,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5748,25 +5745,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10658.22</v>
+        <v>10658.2</v>
       </c>
       <c r="C63" t="n">
-        <v>10735.34</v>
+        <v>10735.3</v>
       </c>
       <c r="D63" t="n">
-        <v>10655.82</v>
+        <v>10655.8</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>10688.5</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>30.4</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>0.0029</v>
       </c>
       <c r="H63" t="n">
-        <v>79.52</v>
+        <v>79.5</v>
       </c>
       <c r="I63" t="n">
         <v>10475</v>
@@ -5789,27 +5786,25 @@
       <c r="O63" t="n">
         <v>10809.2</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
@@ -5823,36 +5818,120 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10689.27</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10823</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10688.91</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10816.14</v>
+      </c>
+      <c r="F64" t="n">
+        <v>127.64</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="H64" t="n">
+        <v>134.09</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10576.3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>10605.48</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10648.75</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10692.02</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10728.25</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10764.48</v>
+      </c>
+      <c r="O64" t="n">
+        <v>10814.8</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>10576.3</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>10814.86</v>
+      <c r="I65" s="13" t="n">
+        <v>10554.82</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>10712.14</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>10749.09</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>10786.05</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>10883.18</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>10980.32</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>10957.09</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5838,13 +5841,13 @@
         <v>10688.91</v>
       </c>
       <c r="E64" t="n">
-        <v>10816.14</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>127.64</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0119</v>
+        <v/>
       </c>
       <c r="H64" t="n">
         <v>134.09</v>
@@ -5870,8 +5873,10 @@
       <c r="O64" t="n">
         <v>10814.8</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
@@ -5879,9 +5884,9 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5896,41 +5901,45 @@
       </c>
       <c r="V64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W64" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
+      <c r="I65" s="14" t="n">
         <v>10554.82</v>
       </c>
-      <c r="J65" s="13" t="n">
-        <v>10712.14</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>10749.09</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>10786.05</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>10883.18</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>10980.32</v>
-      </c>
-      <c r="O65" s="13" t="n">
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
         <v>10957.09</v>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,74 +637,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10363.6</v>
+        <v>10438.2</v>
       </c>
       <c r="C2" t="n">
-        <v>10443.2</v>
+        <v>10462.2</v>
       </c>
       <c r="D2" t="n">
-        <v>10346.6</v>
+        <v>10332.4</v>
       </c>
       <c r="E2" t="n">
-        <v>10437.9</v>
+        <v>10428.9</v>
       </c>
       <c r="F2" t="n">
-        <v>74.59999999999999</v>
+        <v>-9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0009</v>
       </c>
       <c r="H2" t="n">
-        <v>96.59999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="I2" t="n">
-        <v>10287.2</v>
+        <v>10250</v>
       </c>
       <c r="J2" t="n">
-        <v>10286.38</v>
+        <v>10362.8</v>
       </c>
       <c r="K2" t="n">
-        <v>10330.45</v>
+        <v>10389.6</v>
       </c>
       <c r="L2" t="n">
-        <v>10374.52</v>
+        <v>10416.4</v>
       </c>
       <c r="M2" t="n">
-        <v>10396.15</v>
+        <v>10486.2</v>
       </c>
       <c r="N2" t="n">
-        <v>10417.77</v>
+        <v>10556</v>
       </c>
       <c r="O2" t="n">
-        <v>10484.3</v>
+        <v>10539.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -723,78 +716,76 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10438.2</v>
+        <v>10429</v>
       </c>
       <c r="C3" t="n">
-        <v>10462.2</v>
+        <v>10469.3</v>
       </c>
       <c r="D3" t="n">
-        <v>10332.4</v>
+        <v>10407</v>
       </c>
       <c r="E3" t="n">
-        <v>10428.9</v>
+        <v>10461.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-9</v>
+        <v>32.7</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0031</v>
       </c>
       <c r="H3" t="n">
-        <v>129.8</v>
+        <v>62.3</v>
       </c>
       <c r="I3" t="n">
-        <v>10250</v>
+        <v>10202.6</v>
       </c>
       <c r="J3" t="n">
-        <v>10362.8</v>
+        <v>10314.9</v>
       </c>
       <c r="K3" t="n">
-        <v>10389.6</v>
+        <v>10364</v>
       </c>
       <c r="L3" t="n">
-        <v>10416.4</v>
+        <v>10413.1</v>
       </c>
       <c r="M3" t="n">
-        <v>10486.2</v>
+        <v>10493.8</v>
       </c>
       <c r="N3" t="n">
-        <v>10556</v>
+        <v>10574.5</v>
       </c>
       <c r="O3" t="n">
-        <v>10539.8</v>
+        <v>10592</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -807,59 +798,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C4" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D4" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E4" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F4" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H4" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J4" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K4" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L4" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M4" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N4" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O4" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -867,8 +854,10 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
@@ -877,14 +866,18 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -896,50 +889,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C5" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D5" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E5" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F5" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H5" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I5" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J5" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K5" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L5" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M5" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N5" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O5" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -952,80 +945,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C6" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D6" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E6" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H6" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I6" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J6" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K6" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L6" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M6" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N6" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O6" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,10 +1024,8 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
@@ -1059,57 +1048,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C7" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D7" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E7" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H7" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I7" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J7" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K7" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L7" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M7" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N7" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O7" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1120,78 +1109,80 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C8" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D8" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E8" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F8" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H8" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J8" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K8" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L8" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M8" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N8" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O8" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1199,83 +1190,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C9" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D9" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E9" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H9" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I9" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J9" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K9" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L9" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M9" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N9" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O9" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1288,78 +1279,80 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C10" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E10" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F10" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H10" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I10" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J10" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K10" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L10" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M10" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N10" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O10" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1367,30 +1360,22 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1402,50 +1387,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C11" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D11" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E11" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F11" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I11" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J11" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K11" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L11" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M11" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N11" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O11" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1453,16 +1438,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1475,55 +1464,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C12" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D12" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E12" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H12" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I12" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J12" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K12" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L12" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M12" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N12" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O12" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1531,14 +1524,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1557,78 +1548,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C13" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D13" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E13" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F13" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H13" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I13" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J13" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K13" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L13" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M13" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N13" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O13" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10842.8</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1636,9 +1627,9 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1646,69 +1637,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C14" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D14" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E14" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H14" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I14" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J14" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K14" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L14" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M14" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N14" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O14" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1730,50 +1715,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C15" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D15" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E15" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H15" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I15" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J15" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K15" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L15" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M15" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N15" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O15" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1784,9 +1769,9 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1803,55 +1788,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C16" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D16" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E16" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F16" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H16" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J16" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K16" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L16" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M16" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N16" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O16" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,16 +1848,20 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1883,63 +1876,65 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C17" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D17" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E17" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H17" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I17" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J17" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K17" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L17" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M17" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N17" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O17" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
@@ -1948,12 +1943,12 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1969,65 +1964,63 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C18" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D18" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E18" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F18" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H18" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I18" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J18" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K18" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L18" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M18" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N18" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O18" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
@@ -2036,13 +2029,11 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2057,57 +2048,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C19" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D19" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E19" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H19" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I19" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J19" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K19" t="n">
         <v>10464.6</v>
       </c>
       <c r="L19" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M19" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N19" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O19" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2122,11 +2113,13 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2141,57 +2134,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C20" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D20" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E20" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F20" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H20" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I20" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J20" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K20" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L20" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M20" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N20" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O20" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2199,10 +2192,8 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
@@ -2234,70 +2225,72 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C21" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D21" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E21" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F21" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H21" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I21" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J21" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K21" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L21" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M21" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O21" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2309,84 +2302,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C22" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D22" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E22" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H22" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I22" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J22" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K22" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L22" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M22" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N22" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O22" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2395,55 +2384,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C23" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D23" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E23" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F23" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H23" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I23" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J23" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K23" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L23" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M23" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N23" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O23" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2469,67 +2462,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C24" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D24" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E24" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F24" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H24" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I24" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J24" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K24" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L24" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M24" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N24" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O24" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2537,83 +2528,83 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C25" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D25" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E25" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H25" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I25" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J25" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K25" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L25" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M25" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N25" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O25" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2621,22 +2612,24 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2647,57 +2640,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C26" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D26" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E26" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F26" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H26" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I26" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J26" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K26" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L26" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M26" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N26" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O26" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2715,14 +2708,12 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2731,59 +2722,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C27" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D27" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E27" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F27" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I27" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J27" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K27" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L27" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M27" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N27" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O27" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2801,11 +2788,13 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2820,50 +2809,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C28" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D28" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E28" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F28" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H28" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I28" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J28" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K28" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L28" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M28" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N28" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O28" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2881,13 +2870,11 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2902,50 +2889,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C29" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D29" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E29" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F29" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I29" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J29" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K29" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L29" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M29" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N29" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O29" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2956,14 +2943,14 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2977,55 +2964,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C30" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D30" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E30" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H30" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I30" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J30" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K30" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L30" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M30" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N30" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O30" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,12 +3024,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3059,57 +3052,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C31" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D31" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E31" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J31" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K31" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L31" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M31" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N31" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O31" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,20 +3110,16 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3152,50 +3141,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C32" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D32" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E32" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F32" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H32" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I32" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J32" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K32" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L32" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M32" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N32" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O32" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3206,13 +3195,15 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3225,59 +3216,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C33" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D33" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E33" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F33" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H33" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I33" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J33" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K33" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L33" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M33" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N33" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O33" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3285,8 +3272,10 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
@@ -3298,8 +3287,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3309,55 +3300,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C34" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D34" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E34" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F34" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H34" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I34" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J34" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K34" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L34" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M34" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N34" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O34" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3365,25 +3360,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3395,57 +3384,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C35" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D35" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E35" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H35" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I35" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J35" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K35" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L35" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M35" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N35" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O35" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3456,16 +3445,20 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3477,57 +3470,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C36" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D36" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E36" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F36" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H36" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J36" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K36" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L36" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M36" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N36" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O36" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3535,23 +3528,21 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3563,57 +3554,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C37" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D37" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E37" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H37" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I37" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J37" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K37" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L37" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M37" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N37" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O37" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3621,14 +3612,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3654,50 +3643,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C38" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D38" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E38" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F38" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I38" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J38" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K38" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L38" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M38" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N38" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O38" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,8 +3694,10 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
@@ -3736,56 +3727,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C39" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D39" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E39" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F39" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H39" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J39" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K39" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L39" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M39" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N39" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O39" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3794,7 +3787,7 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3806,76 +3799,70 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C40" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D40" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E40" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F40" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H40" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I40" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J40" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K40" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L40" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M40" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N40" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O40" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3902,50 +3889,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C41" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D41" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E41" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H41" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I41" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J41" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K41" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L41" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M41" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N41" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O41" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3963,8 +3950,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3977,55 +3966,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C42" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D42" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E42" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F42" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I42" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J42" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K42" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L42" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M42" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N42" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O42" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4033,14 +4026,12 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4048,8 +4039,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4068,50 +4061,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C43" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D43" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E43" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F43" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H43" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J43" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K43" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L43" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M43" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N43" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O43" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4122,20 +4115,16 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4154,50 +4143,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C44" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D44" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E44" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F44" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H44" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I44" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J44" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K44" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L44" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M44" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N44" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O44" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4205,8 +4194,10 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
@@ -4229,57 +4220,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C45" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D45" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E45" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F45" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H45" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I45" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J45" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K45" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L45" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M45" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N45" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O45" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4287,21 +4278,23 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4313,57 +4306,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C46" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D46" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E46" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F46" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H46" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I46" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J46" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K46" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L46" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M46" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N46" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O46" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4381,13 +4374,11 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4406,50 +4397,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C47" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D47" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E47" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F47" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H47" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I47" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J47" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K47" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L47" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M47" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N47" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O47" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4490,50 +4481,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C48" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D48" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E48" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F48" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J48" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K48" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L48" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M48" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N48" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O48" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,17 +4532,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4567,78 +4560,80 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C49" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D49" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E49" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I49" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J49" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K49" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L49" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M49" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N49" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O49" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4651,78 +4646,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C50" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D50" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E50" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F50" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H50" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I50" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J50" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K50" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L50" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M50" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N50" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O50" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4739,68 +4724,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C51" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D51" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E51" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F51" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H51" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I51" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J51" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K51" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L51" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M51" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N51" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O51" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4817,78 +4812,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C52" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D52" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E52" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H52" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I52" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J52" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K52" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L52" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M52" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N52" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O52" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4905,55 +4892,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C53" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D53" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E53" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H53" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I53" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J53" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K53" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L53" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M53" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N53" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O53" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4961,21 +4952,23 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4987,57 +4980,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C54" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D54" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E54" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F54" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H54" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I54" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J54" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K54" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L54" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M54" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N54" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O54" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5050,18 +5043,14 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5073,57 +5062,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C55" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D55" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E55" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H55" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J55" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K55" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L55" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M55" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N55" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O55" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5131,16 +5120,20 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5155,57 +5148,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C56" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D56" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E56" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F56" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H56" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J56" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K56" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L56" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M56" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N56" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O56" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5223,10 +5216,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5239,65 +5230,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C57" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D57" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H57" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I57" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J57" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K57" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L57" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M57" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N57" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O57" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5306,7 +5297,7 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5328,64 +5319,60 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C58" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D58" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E58" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H58" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I58" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J58" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K58" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L58" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M58" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N58" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O58" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5412,50 +5399,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C59" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D59" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E59" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F59" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H59" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I59" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J59" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K59" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L59" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M59" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N59" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O59" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5463,21 +5450,23 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5487,55 +5476,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C60" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D60" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E60" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F60" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H60" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I60" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J60" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K60" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L60" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M60" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N60" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O60" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5556,10 +5549,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5578,70 +5569,72 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C61" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D61" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E61" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F61" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H61" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I61" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J61" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K61" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L61" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M61" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N61" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O61" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5653,81 +5646,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C62" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D62" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E62" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F62" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H62" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I62" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J62" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K62" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L62" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M62" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N62" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O62" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5739,58 +5726,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10658.2</v>
+        <v>10689.27</v>
       </c>
       <c r="C63" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D63" t="n">
-        <v>10655.8</v>
+        <v>10688.91</v>
       </c>
       <c r="E63" t="n">
-        <v>10688.5</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>30.4</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0029</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>79.5</v>
+        <v>134.09</v>
       </c>
       <c r="I63" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J63" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K63" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L63" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M63" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N63" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O63" t="n">
-        <v>10809.2</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+        <v>10814.8</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="n">
         <v/>
@@ -5798,21 +5791,25 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W63" s="11" t="inlineStr">
         <is>
@@ -5821,126 +5818,8 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>10689.27</v>
-      </c>
-      <c r="C64" t="n">
-        <v>10823</v>
-      </c>
-      <c r="D64" t="n">
-        <v>10688.91</v>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v>134.09</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10576.3</v>
-      </c>
-      <c r="J64" t="n">
-        <v>10605.48</v>
-      </c>
-      <c r="K64" t="n">
-        <v>10648.75</v>
-      </c>
-      <c r="L64" t="n">
-        <v>10692.02</v>
-      </c>
-      <c r="M64" t="n">
-        <v>10728.25</v>
-      </c>
-      <c r="N64" t="n">
-        <v>10764.48</v>
-      </c>
-      <c r="O64" t="n">
-        <v>10814.8</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
           <t>中警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="n">
-        <v>10554.82</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
-        <v>10957.09</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5739,25 +5736,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10689.27</v>
+        <v>10689.3</v>
       </c>
       <c r="C63" t="n">
         <v>10823</v>
       </c>
       <c r="D63" t="n">
-        <v>10688.91</v>
+        <v>10688.9</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>10816.1</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>127.6</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>0.0119</v>
       </c>
       <c r="H63" t="n">
-        <v>134.09</v>
+        <v>134.1</v>
       </c>
       <c r="I63" t="n">
         <v>10576.3</v>
@@ -5780,47 +5777,123 @@
       <c r="O63" t="n">
         <v>10814.8</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10815.8</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10815.9</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10650.2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10659.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-157</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H64" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10554.8</v>
+      </c>
+      <c r="J64" t="n">
+        <v>10712.07</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10749.05</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10786.02</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10883.15</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10980.27</v>
+      </c>
+      <c r="O64" t="n">
+        <v>10957.1</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -634,71 +634,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10438.2</v>
+        <v>10429</v>
       </c>
       <c r="C2" t="n">
-        <v>10462.2</v>
+        <v>10469.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10332.4</v>
+        <v>10407</v>
       </c>
       <c r="E2" t="n">
-        <v>10428.9</v>
+        <v>10461.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-9</v>
+        <v>32.7</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0031</v>
       </c>
       <c r="H2" t="n">
-        <v>129.8</v>
+        <v>62.3</v>
       </c>
       <c r="I2" t="n">
-        <v>10250</v>
+        <v>10202.6</v>
       </c>
       <c r="J2" t="n">
-        <v>10362.8</v>
+        <v>10314.9</v>
       </c>
       <c r="K2" t="n">
-        <v>10389.6</v>
+        <v>10364</v>
       </c>
       <c r="L2" t="n">
-        <v>10416.4</v>
+        <v>10413.1</v>
       </c>
       <c r="M2" t="n">
-        <v>10486.2</v>
+        <v>10493.8</v>
       </c>
       <c r="N2" t="n">
-        <v>10556</v>
+        <v>10574.5</v>
       </c>
       <c r="O2" t="n">
-        <v>10539.8</v>
+        <v>10592</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C3" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D3" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E3" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F3" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H3" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I3" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J3" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K3" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L3" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M3" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N3" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O3" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,8 +765,10 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -781,14 +777,18 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -800,50 +800,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C4" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D4" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E4" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F4" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H4" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I4" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J4" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K4" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L4" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M4" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N4" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O4" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,80 +856,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C5" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D5" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E5" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F5" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H5" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J5" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K5" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L5" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M5" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N5" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O5" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,10 +935,8 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
@@ -963,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C6" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D6" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E6" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H6" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I6" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J6" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K6" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L6" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M6" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N6" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O6" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,78 +1020,80 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C7" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E7" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F7" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H7" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J7" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K7" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L7" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M7" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N7" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O7" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,83 +1101,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C8" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D8" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E8" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H8" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I8" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J8" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K8" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L8" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M8" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N8" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O8" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,78 +1190,80 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C9" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D9" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E9" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F9" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H9" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I9" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J9" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K9" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L9" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M9" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N9" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O9" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,30 +1271,22 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1306,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C10" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D10" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E10" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F10" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H10" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I10" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J10" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K10" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L10" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M10" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N10" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O10" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,16 +1349,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1379,55 +1375,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C11" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D11" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E11" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H11" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I11" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J11" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K11" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L11" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M11" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N11" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O11" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,14 +1435,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1461,78 +1459,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C12" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D12" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E12" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F12" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H12" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I12" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J12" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K12" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L12" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M12" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N12" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O12" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10842.8</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1540,9 +1538,9 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1550,69 +1548,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C13" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D13" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E13" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H13" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I13" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J13" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K13" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L13" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M13" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N13" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O13" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1634,50 +1626,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C14" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D14" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E14" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H14" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I14" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J14" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K14" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L14" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M14" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N14" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O14" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,9 +1680,9 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1707,55 +1699,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C15" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D15" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E15" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F15" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J15" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K15" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L15" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M15" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N15" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O15" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1763,16 +1759,20 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1787,63 +1787,65 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C16" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D16" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E16" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H16" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I16" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J16" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K16" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L16" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M16" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N16" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O16" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
@@ -1852,12 +1854,12 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1873,65 +1875,63 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C17" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D17" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E17" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F17" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H17" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I17" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J17" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K17" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L17" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M17" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N17" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O17" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
@@ -1940,13 +1940,11 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1961,57 +1959,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C18" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D18" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E18" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H18" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I18" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J18" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K18" t="n">
         <v>10464.6</v>
       </c>
       <c r="L18" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M18" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N18" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O18" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,11 +2024,13 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2045,57 +2045,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C19" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D19" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E19" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F19" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H19" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J19" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K19" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L19" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M19" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N19" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O19" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2103,10 +2103,8 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
@@ -2138,70 +2136,72 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C20" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D20" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E20" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F20" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H20" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I20" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J20" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K20" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L20" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M20" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N20" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O20" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2213,84 +2213,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C21" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D21" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E21" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H21" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I21" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J21" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K21" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L21" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M21" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N21" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O21" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2299,55 +2295,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C22" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D22" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E22" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F22" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H22" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I22" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J22" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K22" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L22" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M22" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N22" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O22" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2373,67 +2373,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C23" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D23" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E23" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F23" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H23" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I23" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J23" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K23" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L23" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M23" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N23" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O23" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,83 +2439,83 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C24" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D24" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E24" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H24" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I24" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J24" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K24" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L24" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M24" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N24" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O24" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,22 +2523,24 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C25" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D25" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E25" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F25" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I25" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J25" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K25" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L25" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M25" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N25" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O25" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,14 +2619,12 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2635,59 +2633,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C26" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D26" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E26" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F26" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H26" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I26" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J26" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K26" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L26" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M26" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N26" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O26" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2705,11 +2699,13 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2724,50 +2720,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C27" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D27" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E27" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F27" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H27" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I27" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J27" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K27" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L27" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M27" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N27" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O27" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2785,13 +2781,11 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2806,50 +2800,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C28" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D28" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E28" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F28" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I28" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J28" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K28" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L28" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M28" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N28" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O28" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,14 +2854,14 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2881,55 +2875,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C29" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D29" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E29" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H29" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I29" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J29" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K29" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L29" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M29" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N29" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O29" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2937,12 +2935,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2963,57 +2963,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C30" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D30" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E30" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J30" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K30" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L30" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M30" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N30" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O30" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,20 +3021,16 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3056,50 +3052,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C31" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D31" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E31" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H31" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I31" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J31" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K31" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L31" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M31" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N31" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O31" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3110,13 +3106,15 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3129,59 +3127,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C32" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D32" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E32" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F32" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H32" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I32" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J32" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K32" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L32" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M32" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N32" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O32" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,8 +3183,10 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
@@ -3202,8 +3198,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3213,55 +3211,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C33" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D33" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E33" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F33" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H33" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I33" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J33" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K33" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L33" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M33" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N33" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O33" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3269,25 +3271,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3299,57 +3295,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C34" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D34" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E34" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H34" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I34" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J34" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K34" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L34" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M34" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N34" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O34" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3360,16 +3356,20 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3381,57 +3381,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C35" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D35" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E35" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F35" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H35" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J35" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K35" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L35" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M35" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N35" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O35" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,23 +3439,21 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3467,57 +3465,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C36" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D36" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E36" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H36" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I36" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J36" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K36" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L36" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M36" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N36" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O36" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3525,14 +3523,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3558,50 +3554,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C37" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D37" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E37" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J37" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K37" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L37" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M37" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N37" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O37" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3609,8 +3605,10 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
@@ -3640,56 +3638,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C38" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D38" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E38" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F38" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H38" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J38" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K38" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L38" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M38" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N38" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O38" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3710,76 +3710,70 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C39" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D39" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E39" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H39" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I39" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J39" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K39" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L39" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M39" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N39" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O39" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3806,50 +3800,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C40" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D40" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E40" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H40" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I40" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J40" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K40" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L40" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M40" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N40" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O40" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,8 +3861,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3881,55 +3877,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C41" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D41" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E41" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F41" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J41" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K41" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L41" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M41" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N41" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O41" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3937,14 +3937,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3952,8 +3950,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3972,50 +3972,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C42" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D42" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E42" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F42" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H42" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J42" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K42" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L42" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M42" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N42" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O42" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4026,20 +4026,16 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4058,50 +4054,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C43" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D43" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E43" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F43" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H43" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I43" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J43" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K43" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L43" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M43" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N43" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O43" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4109,8 +4105,10 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
@@ -4133,57 +4131,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C44" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D44" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E44" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F44" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H44" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I44" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J44" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K44" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L44" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M44" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N44" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O44" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4191,21 +4189,23 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4217,57 +4217,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C45" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D45" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E45" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F45" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H45" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I45" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J45" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K45" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L45" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M45" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N45" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O45" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4285,13 +4285,11 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4310,50 +4308,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C46" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D46" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E46" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F46" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H46" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I46" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J46" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K46" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L46" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M46" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N46" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O46" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4394,50 +4392,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C47" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D47" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E47" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F47" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J47" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K47" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L47" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M47" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N47" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O47" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4445,17 +4443,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4471,78 +4471,80 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C48" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D48" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E48" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I48" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J48" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K48" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L48" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M48" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N48" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O48" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4555,78 +4557,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C49" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D49" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E49" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F49" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H49" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I49" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J49" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K49" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L49" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M49" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N49" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O49" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4643,68 +4635,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C50" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D50" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E50" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F50" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H50" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I50" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J50" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K50" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L50" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M50" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N50" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O50" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4721,78 +4723,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C51" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D51" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E51" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H51" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I51" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J51" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K51" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L51" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M51" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N51" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O51" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4809,55 +4803,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C52" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D52" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E52" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H52" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I52" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J52" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K52" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L52" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M52" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N52" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O52" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4865,21 +4863,23 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4891,57 +4891,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C53" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D53" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E53" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F53" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H53" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I53" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J53" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K53" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L53" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M53" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N53" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O53" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4954,18 +4954,14 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4977,57 +4973,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C54" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D54" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E54" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H54" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J54" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K54" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L54" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M54" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N54" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O54" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5035,16 +5031,20 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5059,57 +5059,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C55" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D55" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E55" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F55" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H55" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J55" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K55" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L55" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M55" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N55" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O55" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,10 +5127,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5143,65 +5141,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C56" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D56" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E56" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H56" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I56" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J56" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K56" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L56" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M56" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N56" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O56" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5210,7 +5208,7 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5232,64 +5230,60 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C57" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D57" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E57" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H57" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I57" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J57" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K57" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L57" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M57" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N57" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O57" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
@@ -5316,50 +5310,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C58" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D58" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E58" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H58" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I58" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J58" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K58" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L58" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M58" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N58" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O58" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5367,21 +5361,23 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5391,55 +5387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C59" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D59" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E59" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F59" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H59" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I59" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J59" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K59" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L59" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M59" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N59" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O59" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5460,10 +5460,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5482,70 +5480,72 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C60" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D60" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E60" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F60" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H60" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I60" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J60" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K60" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L60" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M60" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N60" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O60" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5557,81 +5557,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C61" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D61" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E61" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H61" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I61" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J61" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K61" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L61" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M61" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N61" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O61" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5643,55 +5637,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C62" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D62" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E62" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F62" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H62" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I62" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J62" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K62" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L62" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M62" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N62" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O62" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5709,106 +5707,104 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C63" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D63" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E63" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F63" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H63" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I63" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J63" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K63" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L63" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M63" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N63" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O63" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
+      <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
@@ -5816,72 +5812,70 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10815.8</v>
+        <v>10659.09</v>
       </c>
       <c r="C64" t="n">
-        <v>10815.9</v>
+        <v>10774.66</v>
       </c>
       <c r="D64" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E64" t="n">
-        <v>10659.1</v>
+        <v>10739.01</v>
       </c>
       <c r="F64" t="n">
-        <v>-157</v>
+        <v>79.91</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H64" t="n">
-        <v>165.7</v>
+        <v>117.96</v>
       </c>
       <c r="I64" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J64" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K64" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L64" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M64" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N64" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O64" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
       <c r="U64" s="8" t="n">
         <v/>
       </c>
@@ -5893,7 +5887,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10429</v>
+        <v>10461.5</v>
       </c>
       <c r="C2" t="n">
-        <v>10469.3</v>
+        <v>10575.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10407</v>
+        <v>10415.5</v>
       </c>
       <c r="E2" t="n">
-        <v>10461.6</v>
+        <v>10529.9</v>
       </c>
       <c r="F2" t="n">
-        <v>32.7</v>
+        <v>68.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0065</v>
       </c>
       <c r="H2" t="n">
-        <v>62.3</v>
+        <v>159.8</v>
       </c>
       <c r="I2" t="n">
-        <v>10202.6</v>
+        <v>10344.7</v>
       </c>
       <c r="J2" t="n">
-        <v>10314.9</v>
+        <v>10411.02</v>
       </c>
       <c r="K2" t="n">
-        <v>10364</v>
+        <v>10430.45</v>
       </c>
       <c r="L2" t="n">
-        <v>10413.1</v>
+        <v>10449.87</v>
       </c>
       <c r="M2" t="n">
-        <v>10493.8</v>
+        <v>10492.75</v>
       </c>
       <c r="N2" t="n">
-        <v>10574.5</v>
+        <v>10535.62</v>
       </c>
       <c r="O2" t="n">
-        <v>10592</v>
+        <v>10531.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,14 +697,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -714,50 +720,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C3" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E3" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F3" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H3" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I3" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J3" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K3" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L3" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M3" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N3" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O3" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,80 +776,78 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C4" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D4" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E4" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H4" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J4" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K4" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L4" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M4" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N4" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O4" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,10 +855,8 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
@@ -877,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C5" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D5" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E5" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I5" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J5" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K5" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L5" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M5" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N5" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O5" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,78 +940,80 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C6" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D6" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E6" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F6" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H6" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J6" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K6" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L6" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M6" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N6" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O6" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,83 +1021,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C7" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D7" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E7" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H7" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I7" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J7" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K7" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L7" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M7" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N7" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O7" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1106,78 +1110,80 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C8" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D8" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E8" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F8" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H8" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I8" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J8" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K8" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L8" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M8" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N8" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O8" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,30 +1191,22 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1220,50 +1218,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C9" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D9" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E9" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F9" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H9" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I9" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J9" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K9" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L9" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M9" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N9" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O9" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,16 +1269,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,55 +1295,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C10" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D10" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E10" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H10" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I10" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J10" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K10" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L10" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M10" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N10" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O10" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,21 +1355,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1375,88 +1379,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C11" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D11" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E11" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F11" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H11" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I11" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J11" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K11" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L11" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M11" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N11" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O11" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+        <v>10842.8</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1464,69 +1468,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C12" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D12" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E12" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H12" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I12" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J12" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K12" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L12" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M12" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N12" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O12" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1548,50 +1546,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C13" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D13" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E13" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H13" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I13" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J13" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K13" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L13" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M13" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N13" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O13" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,9 +1600,9 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1621,55 +1619,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C14" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D14" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E14" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F14" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J14" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K14" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L14" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M14" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N14" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O14" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1677,16 +1679,20 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1701,63 +1707,65 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C15" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D15" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E15" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H15" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I15" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J15" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K15" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L15" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M15" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N15" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O15" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1766,12 +1774,12 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1787,80 +1795,76 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C16" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D16" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E16" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F16" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H16" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I16" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J16" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K16" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L16" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M16" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N16" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O16" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1875,57 +1879,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C17" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D17" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E17" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H17" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I17" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J17" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K17" t="n">
         <v>10464.6</v>
       </c>
       <c r="L17" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M17" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N17" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O17" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,11 +1944,13 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1959,57 +1965,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C18" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D18" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E18" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F18" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H18" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I18" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J18" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K18" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L18" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M18" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N18" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O18" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,10 +2023,8 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
@@ -2052,70 +2056,72 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C19" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D19" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E19" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F19" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H19" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I19" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J19" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K19" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L19" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M19" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N19" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O19" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2127,84 +2133,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C20" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D20" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E20" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H20" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I20" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J20" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K20" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L20" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M20" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N20" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O20" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2213,55 +2215,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C21" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D21" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E21" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F21" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H21" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I21" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J21" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K21" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L21" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M21" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N21" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O21" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,67 +2293,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C22" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D22" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E22" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F22" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H22" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I22" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J22" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K22" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L22" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M22" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N22" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O22" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,83 +2359,83 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C23" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D23" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E23" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H23" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I23" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J23" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K23" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L23" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M23" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N23" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O23" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,22 +2443,24 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2465,57 +2471,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C24" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D24" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E24" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F24" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H24" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I24" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J24" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K24" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L24" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M24" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N24" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O24" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2533,14 +2539,12 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2549,59 +2553,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C25" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D25" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E25" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F25" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H25" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I25" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J25" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K25" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L25" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M25" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N25" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O25" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,11 +2619,13 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2638,50 +2640,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C26" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D26" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E26" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F26" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H26" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I26" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J26" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K26" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L26" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M26" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N26" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O26" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2699,13 +2701,11 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2720,50 +2720,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C27" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D27" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E27" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F27" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I27" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J27" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K27" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L27" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M27" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N27" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O27" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2774,14 +2774,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2795,55 +2795,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C28" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D28" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E28" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H28" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I28" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J28" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K28" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L28" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M28" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N28" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O28" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,12 +2855,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2877,57 +2883,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C29" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D29" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E29" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J29" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K29" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L29" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M29" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N29" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O29" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2935,20 +2941,16 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2970,50 +2972,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C30" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D30" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E30" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H30" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I30" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J30" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K30" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L30" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M30" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N30" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O30" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3024,13 +3026,15 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3043,59 +3047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C31" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D31" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E31" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F31" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H31" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I31" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J31" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K31" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L31" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M31" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N31" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O31" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,8 +3103,10 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
@@ -3116,8 +3118,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3127,55 +3131,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C32" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D32" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E32" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F32" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H32" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I32" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J32" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K32" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L32" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M32" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N32" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O32" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,25 +3191,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3213,57 +3215,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C33" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D33" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E33" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H33" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I33" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J33" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K33" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L33" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M33" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N33" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O33" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,16 +3276,20 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3295,57 +3301,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C34" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D34" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E34" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F34" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H34" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J34" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K34" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L34" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M34" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N34" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O34" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3353,23 +3359,21 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3381,57 +3385,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C35" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D35" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E35" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F35" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H35" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I35" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J35" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K35" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L35" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M35" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N35" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O35" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,14 +3443,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3472,50 +3474,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C36" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D36" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E36" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I36" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J36" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K36" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L36" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M36" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N36" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O36" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3523,8 +3525,10 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
@@ -3554,56 +3558,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C37" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D37" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E37" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F37" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H37" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J37" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K37" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L37" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M37" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N37" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O37" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3612,7 +3618,7 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3624,76 +3630,70 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C38" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D38" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E38" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H38" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I38" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J38" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K38" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L38" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M38" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N38" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O38" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3720,50 +3720,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C39" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D39" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E39" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H39" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I39" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J39" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K39" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L39" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M39" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N39" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O39" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3781,8 +3781,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3795,55 +3797,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C40" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D40" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E40" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F40" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J40" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K40" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L40" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M40" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N40" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O40" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3851,14 +3857,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3866,8 +3870,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3886,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C41" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D41" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E41" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F41" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H41" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J41" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K41" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L41" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M41" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N41" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O41" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3940,20 +3946,16 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3972,50 +3974,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C42" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D42" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E42" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F42" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H42" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I42" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J42" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K42" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L42" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M42" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N42" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O42" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4023,8 +4025,10 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
@@ -4047,57 +4051,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C43" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D43" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E43" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F43" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H43" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I43" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J43" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K43" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L43" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M43" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N43" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O43" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4105,21 +4109,23 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4131,57 +4137,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C44" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D44" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E44" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F44" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H44" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I44" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J44" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K44" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L44" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M44" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N44" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O44" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,13 +4205,11 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4224,50 +4228,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C45" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D45" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E45" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F45" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H45" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I45" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J45" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K45" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L45" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M45" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N45" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O45" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4308,50 +4312,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C46" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D46" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E46" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F46" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J46" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K46" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L46" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M46" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N46" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O46" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4359,17 +4363,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U46" s="8" t="n">
@@ -4385,78 +4391,80 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C47" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D47" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E47" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I47" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J47" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K47" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L47" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M47" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N47" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O47" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4469,78 +4477,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C48" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D48" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E48" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F48" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H48" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I48" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J48" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K48" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L48" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M48" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N48" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O48" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4557,68 +4555,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C49" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D49" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E49" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F49" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H49" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I49" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J49" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K49" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L49" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M49" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N49" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O49" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4635,78 +4643,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C50" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D50" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E50" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I50" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J50" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K50" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L50" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M50" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N50" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O50" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4723,55 +4723,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C51" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D51" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E51" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H51" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I51" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J51" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K51" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L51" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M51" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N51" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O51" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,21 +4783,23 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4805,57 +4811,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C52" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D52" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E52" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F52" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H52" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I52" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J52" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K52" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L52" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M52" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N52" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O52" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4868,18 +4874,14 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4891,57 +4893,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C53" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D53" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E53" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H53" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J53" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K53" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L53" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M53" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N53" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O53" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4949,16 +4951,20 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4973,57 +4979,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C54" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D54" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E54" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F54" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H54" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J54" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K54" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L54" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M54" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N54" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O54" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,10 +5047,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5057,65 +5061,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C55" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D55" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E55" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H55" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I55" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J55" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K55" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L55" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M55" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N55" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O55" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5124,7 +5128,7 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5146,64 +5150,60 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C56" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D56" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E56" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H56" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I56" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J56" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K56" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L56" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M56" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N56" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O56" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5230,50 +5230,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C57" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D57" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E57" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H57" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I57" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J57" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K57" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L57" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M57" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N57" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O57" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5281,21 +5281,23 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5305,55 +5307,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C58" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E58" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F58" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I58" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J58" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K58" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L58" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M58" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N58" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O58" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5374,10 +5380,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5396,70 +5400,72 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C59" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D59" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E59" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F59" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H59" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I59" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J59" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K59" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L59" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M59" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N59" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O59" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5471,81 +5477,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C60" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D60" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E60" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H60" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I60" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J60" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K60" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L60" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M60" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N60" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O60" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5557,55 +5557,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C61" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D61" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E61" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F61" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H61" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I61" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J61" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K61" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L61" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M61" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N61" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O61" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5623,106 +5627,104 @@
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C62" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D62" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E62" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F62" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H62" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I62" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J62" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K62" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L62" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M62" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N62" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O62" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
@@ -5730,72 +5732,70 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C63" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D63" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E63" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F63" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H63" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I63" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J63" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K63" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L63" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M63" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N63" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O63" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
@@ -5807,55 +5807,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10659.09</v>
+        <v>10738.97</v>
       </c>
       <c r="C64" t="n">
-        <v>10774.66</v>
+        <v>10771.64</v>
       </c>
       <c r="D64" t="n">
-        <v>10656.7</v>
+        <v>10714.78</v>
       </c>
       <c r="E64" t="n">
-        <v>10739.01</v>
+        <v>10742.17</v>
       </c>
       <c r="F64" t="n">
-        <v>79.91</v>
+        <v>3.17</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0075</v>
+        <v>0.0003</v>
       </c>
       <c r="H64" t="n">
-        <v>117.96</v>
+        <v>56.86</v>
       </c>
       <c r="I64" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J64" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K64" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L64" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M64" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N64" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O64" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5868,13 +5872,11 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -5826,19 +5826,19 @@
         <v>10771.64</v>
       </c>
       <c r="D64" t="n">
-        <v>10714.78</v>
+        <v>10711.42</v>
       </c>
       <c r="E64" t="n">
-        <v>10742.17</v>
+        <v>10713.26</v>
       </c>
       <c r="F64" t="n">
-        <v>3.17</v>
+        <v>-25.74</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0024</v>
       </c>
       <c r="H64" t="n">
-        <v>56.86</v>
+        <v>60.22</v>
       </c>
       <c r="I64" t="n">
         <v>10538.7</v>
@@ -5870,9 +5870,9 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -5826,19 +5826,19 @@
         <v>10771.64</v>
       </c>
       <c r="D64" t="n">
-        <v>10711.42</v>
+        <v>10708.33</v>
       </c>
       <c r="E64" t="n">
-        <v>10713.26</v>
+        <v>10708.33</v>
       </c>
       <c r="F64" t="n">
-        <v>-25.74</v>
+        <v>-30.67</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0029</v>
       </c>
       <c r="H64" t="n">
-        <v>60.22</v>
+        <v>63.31</v>
       </c>
       <c r="I64" t="n">
         <v>10538.7</v>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,17 +104,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10461.5</v>
+        <v>10530.2</v>
       </c>
       <c r="C2" t="n">
-        <v>10575.3</v>
+        <v>10530.2</v>
       </c>
       <c r="D2" t="n">
-        <v>10415.5</v>
+        <v>10404.7</v>
       </c>
       <c r="E2" t="n">
-        <v>10529.9</v>
+        <v>10508</v>
       </c>
       <c r="F2" t="n">
-        <v>68.3</v>
+        <v>-21.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0021</v>
       </c>
       <c r="H2" t="n">
-        <v>159.8</v>
+        <v>125.5</v>
       </c>
       <c r="I2" t="n">
-        <v>10344.7</v>
+        <v>10255.7</v>
       </c>
       <c r="J2" t="n">
-        <v>10411.02</v>
+        <v>10387.35</v>
       </c>
       <c r="K2" t="n">
-        <v>10430.45</v>
+        <v>10450</v>
       </c>
       <c r="L2" t="n">
-        <v>10449.87</v>
+        <v>10512.65</v>
       </c>
       <c r="M2" t="n">
-        <v>10492.75</v>
+        <v>10609.8</v>
       </c>
       <c r="N2" t="n">
-        <v>10535.62</v>
+        <v>10706.95</v>
       </c>
       <c r="O2" t="n">
-        <v>10531.6</v>
+        <v>10735.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,78 +695,76 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C3" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D3" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E3" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H3" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J3" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K3" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L3" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M3" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N3" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O3" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,12 +772,10 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -797,57 +796,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C4" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D4" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E4" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H4" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I4" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J4" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K4" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L4" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M4" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N4" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O4" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,76 +859,78 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C5" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D5" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E5" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F5" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H5" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J5" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K5" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L5" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M5" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N5" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O5" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,83 +938,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C6" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D6" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E6" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H6" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I6" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J6" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K6" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L6" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M6" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N6" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O6" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,76 +1029,78 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C7" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E7" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F7" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H7" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J7" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K7" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L7" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M7" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N7" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O7" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,30 +1108,22 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1140,50 +1135,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C8" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D8" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E8" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F8" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H8" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I8" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J8" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K8" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L8" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M8" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N8" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O8" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,16 +1186,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,55 +1212,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C9" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D9" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E9" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H9" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I9" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J9" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K9" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L9" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M9" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N9" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O9" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1269,21 +1272,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1295,78 +1296,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C10" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D10" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E10" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F10" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H10" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I10" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J10" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K10" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L10" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M10" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N10" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O10" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1374,9 +1375,9 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1384,69 +1385,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C11" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D11" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E11" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H11" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I11" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J11" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K11" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L11" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M11" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N11" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O11" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1468,50 +1463,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C12" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D12" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E12" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F12" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H12" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I12" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J12" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K12" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L12" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M12" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N12" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O12" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,7 +1519,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1541,55 +1536,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C13" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D13" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E13" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F13" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H13" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J13" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K13" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L13" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M13" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N13" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O13" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,16 +1596,20 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1621,77 +1624,79 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C14" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D14" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E14" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H14" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I14" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J14" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K14" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L14" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M14" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N14" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O14" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1707,80 +1712,76 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C15" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D15" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E15" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F15" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H15" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I15" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J15" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K15" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L15" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M15" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N15" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O15" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1795,57 +1796,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C16" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D16" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E16" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H16" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I16" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J16" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K16" t="n">
         <v>10464.6</v>
       </c>
       <c r="L16" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M16" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N16" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O16" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,13 +1859,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1879,57 +1882,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C17" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D17" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E17" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F17" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H17" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I17" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J17" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K17" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L17" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M17" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N17" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O17" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,12 +1940,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1972,69 +1973,71 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C18" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D18" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E18" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F18" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H18" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I18" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J18" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K18" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L18" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M18" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N18" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O18" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2047,84 +2050,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C19" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D19" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E19" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H19" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I19" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J19" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K19" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L19" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M19" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N19" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O19" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2133,55 +2132,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C20" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D20" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E20" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F20" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H20" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I20" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J20" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K20" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L20" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M20" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N20" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O20" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2192,7 +2195,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2207,67 +2210,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C21" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D21" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E21" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F21" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H21" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I21" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J21" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K21" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L21" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M21" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N21" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O21" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2275,83 +2276,83 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C22" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D22" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E22" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H22" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I22" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J22" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K22" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L22" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M22" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N22" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O22" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2359,22 +2360,24 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2385,57 +2388,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C23" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D23" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E23" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F23" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H23" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I23" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J23" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K23" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L23" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M23" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N23" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O23" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,21 +2449,19 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2469,59 +2470,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C24" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D24" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E24" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F24" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H24" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I24" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J24" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K24" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L24" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M24" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N24" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O24" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2532,18 +2529,20 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2558,50 +2557,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C25" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D25" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E25" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F25" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H25" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I25" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J25" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K25" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L25" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M25" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N25" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O25" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2612,20 +2611,18 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2640,50 +2637,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C26" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D26" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E26" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F26" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I26" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J26" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K26" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L26" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M26" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N26" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O26" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2696,12 +2693,12 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2715,55 +2712,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C27" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D27" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E27" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H27" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I27" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J27" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K27" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L27" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M27" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N27" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O27" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2771,12 +2772,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2797,57 +2800,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C28" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D28" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E28" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J28" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K28" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L28" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M28" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N28" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O28" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2855,20 +2858,16 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2890,50 +2889,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C29" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D29" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E29" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I29" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J29" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K29" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L29" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M29" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N29" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O29" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2946,11 +2945,13 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2963,59 +2964,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C30" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D30" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E30" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F30" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H30" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I30" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J30" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K30" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L30" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M30" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N30" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O30" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,10 +3020,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3036,8 +3035,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3047,55 +3048,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D31" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E31" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F31" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H31" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I31" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J31" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K31" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L31" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M31" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N31" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O31" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,25 +3108,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3133,57 +3132,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C32" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D32" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E32" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H32" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I32" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J32" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K32" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L32" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M32" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N32" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O32" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,14 +3195,18 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3215,57 +3218,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C33" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D33" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E33" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F33" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H33" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J33" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K33" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L33" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M33" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N33" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O33" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,23 +3276,21 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3301,57 +3302,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C34" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D34" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E34" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H34" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I34" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J34" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K34" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L34" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M34" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N34" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O34" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3359,14 +3360,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3392,50 +3391,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C35" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D35" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E35" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F35" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I35" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J35" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K35" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L35" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M35" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N35" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O35" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,10 +3442,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3474,65 +3475,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C36" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D36" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E36" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F36" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H36" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J36" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K36" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L36" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M36" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N36" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O36" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3544,79 +3547,73 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C37" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D37" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E37" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H37" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I37" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J37" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K37" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L37" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M37" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N37" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O37" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3640,50 +3637,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C38" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D38" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E38" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F38" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H38" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I38" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J38" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K38" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L38" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M38" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N38" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O38" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3696,13 +3693,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3715,55 +3714,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C39" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D39" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E39" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F39" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I39" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J39" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K39" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L39" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M39" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N39" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O39" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3771,14 +3774,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3786,8 +3787,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3806,50 +3809,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C40" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D40" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E40" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F40" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H40" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J40" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K40" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L40" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M40" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N40" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O40" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3862,18 +3865,14 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3892,50 +3891,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C41" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D41" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E41" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F41" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H41" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I41" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J41" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K41" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L41" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M41" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N41" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O41" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3943,10 +3942,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3967,57 +3968,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C42" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D42" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E42" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F42" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H42" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I42" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J42" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K42" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L42" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M42" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N42" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O42" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4025,21 +4026,23 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4051,57 +4054,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C43" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D43" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E43" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F43" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H43" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I43" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J43" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K43" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L43" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M43" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N43" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O43" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4112,20 +4115,18 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4144,50 +4145,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C44" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D44" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E44" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F44" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H44" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I44" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J44" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K44" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L44" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M44" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N44" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O44" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4198,7 +4199,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4228,50 +4229,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C45" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D45" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E45" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F45" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J45" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K45" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L45" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M45" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N45" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O45" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4279,17 +4280,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4305,63 +4308,67 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C46" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D46" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E46" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I46" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J46" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K46" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L46" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M46" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N46" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O46" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
@@ -4370,13 +4377,11 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4389,78 +4394,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C47" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D47" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E47" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H47" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I47" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J47" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K47" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L47" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M47" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N47" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O47" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4477,68 +4472,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C48" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D48" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E48" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F48" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H48" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I48" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J48" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K48" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L48" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M48" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N48" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O48" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4555,78 +4560,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C49" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D49" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E49" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H49" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I49" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J49" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K49" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L49" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M49" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N49" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O49" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4643,55 +4640,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C50" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D50" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E50" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H50" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I50" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J50" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K50" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L50" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M50" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N50" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O50" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,21 +4700,23 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4725,57 +4728,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C51" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D51" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E51" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F51" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H51" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I51" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J51" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K51" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L51" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M51" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N51" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O51" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4786,20 +4789,16 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4811,57 +4810,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C52" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D52" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E52" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H52" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J52" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K52" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L52" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M52" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N52" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O52" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4869,16 +4868,20 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4893,57 +4896,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C53" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D53" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E53" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H53" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J53" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K53" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L53" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M53" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N53" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O53" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4956,15 +4959,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4977,74 +4978,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C54" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D54" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E54" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H54" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I54" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J54" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K54" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L54" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M54" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N54" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O54" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5066,67 +5067,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C55" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D55" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E55" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H55" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I55" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J55" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K55" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L55" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M55" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N55" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O55" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5150,50 +5147,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C56" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D56" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E56" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F56" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H56" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I56" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J56" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K56" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L56" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M56" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N56" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O56" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5201,21 +5198,23 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5225,55 +5224,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C57" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D57" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E57" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F57" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H57" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I57" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J57" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K57" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L57" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M57" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N57" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O57" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5284,7 +5287,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5294,10 +5297,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5316,69 +5317,71 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C58" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D58" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E58" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F58" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H58" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I58" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J58" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K58" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L58" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M58" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N58" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O58" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5391,81 +5394,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C59" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D59" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E59" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H59" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I59" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J59" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K59" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L59" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M59" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N59" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O59" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5477,55 +5474,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C60" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D60" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E60" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F60" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H60" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I60" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J60" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K60" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L60" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M60" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N60" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O60" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5536,113 +5537,111 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C61" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D61" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E61" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F61" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H61" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I61" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J61" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K61" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L61" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M61" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N61" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O61" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5650,72 +5649,70 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C62" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D62" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E62" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F62" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H62" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I62" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J62" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K62" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L62" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M62" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N62" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O62" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5727,58 +5724,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10659.1</v>
+        <v>10738.97</v>
       </c>
       <c r="C63" t="n">
-        <v>10774.7</v>
+        <v>10771.64</v>
       </c>
       <c r="D63" t="n">
-        <v>10656.7</v>
+        <v>10708.33</v>
       </c>
       <c r="E63" t="n">
-        <v>10739</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>79.90000000000001</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0075</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>118</v>
+        <v>63.31</v>
       </c>
       <c r="I63" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J63" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K63" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L63" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M63" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N63" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O63" t="n">
-        <v>10981.6</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+        <v>10892.7</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="n">
         <v/>
@@ -5786,15 +5789,13 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5808,88 +5809,6 @@
         </is>
       </c>
       <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>10738.97</v>
-      </c>
-      <c r="C64" t="n">
-        <v>10771.64</v>
-      </c>
-      <c r="D64" t="n">
-        <v>10708.33</v>
-      </c>
-      <c r="E64" t="n">
-        <v>10708.33</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-30.67</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>-0.0029</v>
-      </c>
-      <c r="H64" t="n">
-        <v>63.31</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10538.7</v>
-      </c>
-      <c r="J64" t="n">
-        <v>10632.65</v>
-      </c>
-      <c r="K64" t="n">
-        <v>10680</v>
-      </c>
-      <c r="L64" t="n">
-        <v>10727.35</v>
-      </c>
-      <c r="M64" t="n">
-        <v>10798</v>
-      </c>
-      <c r="N64" t="n">
-        <v>10868.65</v>
-      </c>
-      <c r="O64" t="n">
-        <v>10892.7</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5733,29 +5730,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10738.97</v>
+        <v>10708.79</v>
       </c>
       <c r="C63" t="n">
-        <v>10771.64</v>
+        <v>10762.52</v>
       </c>
       <c r="D63" t="n">
-        <v>10708.33</v>
+        <v>10682.73</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>10709.46</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>-29.54</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>-0.0028</v>
       </c>
       <c r="H63" t="n">
-        <v>63.31</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>10538.7</v>
@@ -5778,10 +5775,8 @@
       <c r="O63" t="n">
         <v>10892.7</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P63" s="6" t="n">
+        <v/>
       </c>
       <c r="Q63" s="6" t="n">
         <v/>
@@ -5789,9 +5784,9 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -5743,13 +5743,13 @@
         <v>10682.73</v>
       </c>
       <c r="E63" t="n">
-        <v>10709.46</v>
+        <v>10705.26</v>
       </c>
       <c r="F63" t="n">
-        <v>-29.54</v>
+        <v>-33.74</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0031</v>
       </c>
       <c r="H63" t="n">
         <v>79.79000000000001</v>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10530.2</v>
+        <v>10507.8</v>
       </c>
       <c r="C2" t="n">
-        <v>10530.2</v>
+        <v>10521</v>
       </c>
       <c r="D2" t="n">
-        <v>10404.7</v>
+        <v>10472</v>
       </c>
       <c r="E2" t="n">
-        <v>10508</v>
+        <v>10484.2</v>
       </c>
       <c r="F2" t="n">
-        <v>-21.9</v>
+        <v>-23.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0023</v>
       </c>
       <c r="H2" t="n">
-        <v>125.5</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>10255.7</v>
+        <v>10279.2</v>
       </c>
       <c r="J2" t="n">
-        <v>10387.35</v>
+        <v>10402.77</v>
       </c>
       <c r="K2" t="n">
-        <v>10450</v>
+        <v>10445.25</v>
       </c>
       <c r="L2" t="n">
-        <v>10512.65</v>
+        <v>10487.73</v>
       </c>
       <c r="M2" t="n">
-        <v>10609.8</v>
+        <v>10570.75</v>
       </c>
       <c r="N2" t="n">
-        <v>10706.95</v>
+        <v>10653.77</v>
       </c>
       <c r="O2" t="n">
-        <v>10735.1</v>
+        <v>10655.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -711,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C3" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D3" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E3" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I3" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J3" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K3" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L3" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M3" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N3" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O3" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,78 +770,80 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C4" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D4" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E4" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H4" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J4" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K4" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L4" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M4" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N4" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O4" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,83 +851,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C5" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D5" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E5" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H5" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J5" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K5" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L5" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M5" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N5" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O5" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,78 +940,80 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C6" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D6" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E6" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F6" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H6" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I6" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J6" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K6" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L6" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M6" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N6" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O6" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,30 +1021,22 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1054,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C7" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D7" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E7" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F7" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H7" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I7" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J7" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K7" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L7" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M7" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N7" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O7" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,16 +1099,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,55 +1125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C8" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D8" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E8" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H8" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I8" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J8" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K8" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L8" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M8" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N8" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O8" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1183,21 +1185,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1209,88 +1209,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C9" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D9" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E9" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F9" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H9" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I9" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J9" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K9" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L9" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M9" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N9" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O9" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+        <v>10842.8</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1298,69 +1298,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C10" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D10" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E10" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H10" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I10" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J10" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K10" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L10" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M10" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N10" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O10" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1382,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C11" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D11" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E11" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H11" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I11" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J11" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K11" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L11" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M11" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N11" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O11" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,9 +1430,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1455,55 +1449,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C12" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D12" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E12" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F12" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J12" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K12" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L12" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M12" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N12" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O12" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1511,16 +1509,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1535,63 +1537,65 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C13" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D13" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E13" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H13" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I13" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J13" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K13" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L13" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M13" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N13" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O13" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
@@ -1600,12 +1604,12 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1621,80 +1625,76 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C14" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D14" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E14" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F14" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H14" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I14" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J14" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K14" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L14" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M14" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N14" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O14" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1709,57 +1709,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C15" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D15" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E15" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H15" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I15" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J15" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K15" t="n">
         <v>10464.6</v>
       </c>
       <c r="L15" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M15" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N15" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O15" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,11 +1774,13 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1793,57 +1795,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C16" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D16" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E16" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F16" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H16" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I16" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J16" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K16" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L16" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M16" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N16" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O16" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,10 +1853,8 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1886,70 +1886,72 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C17" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D17" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E17" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F17" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H17" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I17" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J17" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K17" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L17" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M17" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N17" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O17" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1961,84 +1963,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C18" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D18" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H18" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I18" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J18" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K18" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L18" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M18" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N18" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O18" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2047,55 +2045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C19" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D19" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E19" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F19" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H19" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I19" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J19" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K19" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L19" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M19" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N19" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O19" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2121,67 +2123,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C20" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D20" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E20" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F20" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H20" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I20" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J20" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K20" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L20" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M20" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N20" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O20" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,83 +2189,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C21" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D21" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E21" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H21" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I21" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J21" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K21" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L21" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M21" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N21" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O21" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,22 +2273,24 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2299,57 +2301,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C22" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D22" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E22" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H22" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I22" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J22" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K22" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L22" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M22" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N22" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O22" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,14 +2369,12 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2383,59 +2383,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C23" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D23" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E23" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F23" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H23" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I23" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J23" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K23" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L23" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M23" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N23" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O23" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2453,11 +2449,13 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2472,50 +2470,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C24" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D24" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E24" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F24" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H24" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I24" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J24" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K24" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L24" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M24" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N24" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O24" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2533,13 +2531,11 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2554,50 +2550,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C25" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D25" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E25" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F25" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I25" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J25" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K25" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L25" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M25" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N25" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O25" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2608,14 +2604,14 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2629,55 +2625,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C26" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D26" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E26" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H26" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I26" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J26" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K26" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L26" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M26" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N26" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O26" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2685,12 +2685,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2711,57 +2713,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C27" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D27" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E27" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J27" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K27" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L27" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M27" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N27" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O27" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2769,20 +2771,16 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2804,50 +2802,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C28" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D28" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E28" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H28" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I28" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J28" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K28" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L28" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M28" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N28" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O28" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2858,13 +2856,15 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2877,59 +2877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C29" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D29" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E29" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F29" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H29" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I29" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J29" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K29" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L29" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M29" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N29" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O29" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2937,8 +2933,10 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2950,8 +2948,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2961,55 +2961,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C30" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D30" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E30" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F30" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H30" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I30" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J30" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K30" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L30" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M30" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N30" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O30" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3017,25 +3021,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3047,57 +3045,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C31" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D31" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E31" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H31" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I31" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J31" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K31" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L31" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M31" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N31" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O31" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3108,16 +3106,20 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3129,57 +3131,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C32" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D32" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E32" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F32" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H32" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J32" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K32" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L32" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M32" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N32" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O32" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,23 +3189,21 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3215,57 +3215,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C33" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D33" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E33" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F33" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H33" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I33" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J33" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K33" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L33" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M33" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N33" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O33" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,14 +3273,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3306,50 +3304,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C34" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D34" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E34" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I34" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J34" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K34" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L34" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M34" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N34" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O34" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,8 +3355,10 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
@@ -3388,56 +3388,58 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C35" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D35" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E35" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F35" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H35" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J35" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K35" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L35" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M35" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N35" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O35" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3446,7 +3448,7 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3458,76 +3460,70 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C36" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D36" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E36" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H36" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I36" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J36" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K36" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L36" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M36" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N36" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O36" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
@@ -3554,50 +3550,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C37" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D37" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E37" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F37" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H37" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I37" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J37" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K37" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L37" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M37" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N37" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O37" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3615,8 +3611,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3629,55 +3627,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C38" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D38" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E38" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F38" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I38" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J38" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K38" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L38" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M38" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N38" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O38" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3685,14 +3687,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3700,8 +3700,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3720,50 +3722,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C39" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D39" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E39" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F39" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H39" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J39" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K39" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L39" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M39" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N39" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O39" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3774,20 +3776,16 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3806,50 +3804,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C40" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D40" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E40" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F40" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H40" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I40" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J40" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K40" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L40" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M40" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N40" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O40" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,8 +3855,10 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
@@ -3881,57 +3881,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C41" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D41" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E41" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F41" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H41" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I41" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J41" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K41" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L41" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M41" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N41" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O41" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3939,21 +3939,23 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3965,57 +3967,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C42" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D42" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E42" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F42" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H42" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I42" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J42" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K42" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L42" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M42" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N42" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O42" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4033,13 +4035,11 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4058,50 +4058,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C43" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D43" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E43" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F43" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H43" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I43" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J43" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K43" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L43" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M43" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N43" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O43" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4142,50 +4142,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C44" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D44" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E44" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F44" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J44" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K44" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L44" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M44" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N44" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O44" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4193,17 +4193,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4219,78 +4221,80 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C45" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D45" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E45" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I45" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J45" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K45" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L45" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M45" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N45" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O45" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4303,78 +4307,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C46" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D46" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E46" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H46" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I46" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J46" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K46" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L46" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M46" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N46" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O46" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4391,68 +4385,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C47" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D47" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E47" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F47" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H47" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I47" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J47" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K47" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L47" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M47" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N47" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O47" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4469,78 +4473,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C48" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D48" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E48" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H48" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I48" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J48" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K48" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L48" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M48" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N48" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O48" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4557,55 +4553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C49" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D49" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E49" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H49" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I49" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J49" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K49" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L49" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M49" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N49" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O49" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4613,21 +4613,23 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4639,57 +4641,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C50" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D50" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E50" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F50" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H50" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I50" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J50" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K50" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L50" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M50" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N50" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O50" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4702,18 +4704,14 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4725,57 +4723,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C51" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D51" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E51" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H51" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J51" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K51" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L51" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M51" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N51" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O51" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4783,16 +4781,20 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4807,57 +4809,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C52" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D52" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E52" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F52" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H52" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J52" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K52" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L52" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M52" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N52" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O52" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4875,10 +4877,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4891,65 +4891,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C53" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D53" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E53" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H53" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I53" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J53" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K53" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L53" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M53" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N53" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O53" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4980,64 +4980,60 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C54" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D54" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E54" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H54" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I54" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J54" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K54" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L54" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M54" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N54" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O54" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
@@ -5064,50 +5060,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C55" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D55" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E55" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F55" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H55" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I55" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J55" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K55" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L55" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M55" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N55" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O55" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5115,21 +5111,23 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5139,55 +5137,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C56" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D56" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E56" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F56" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H56" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I56" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J56" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K56" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L56" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M56" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N56" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O56" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5208,10 +5210,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5230,70 +5230,72 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C57" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D57" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E57" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F57" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H57" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I57" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J57" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K57" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L57" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M57" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N57" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O57" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5305,81 +5307,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C58" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D58" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E58" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H58" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I58" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J58" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K58" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L58" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M58" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N58" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O58" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5391,55 +5387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C59" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D59" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E59" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F59" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H59" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I59" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J59" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K59" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L59" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M59" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N59" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O59" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5457,106 +5457,104 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C60" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D60" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E60" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F60" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H60" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I60" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J60" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K60" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L60" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M60" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N60" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O60" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5564,72 +5562,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C61" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D61" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E61" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F61" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H61" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I61" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J61" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K61" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L61" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M61" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N61" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O61" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5641,55 +5637,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10659.1</v>
+        <v>10708.8</v>
       </c>
       <c r="C62" t="n">
-        <v>10774.7</v>
+        <v>10762.5</v>
       </c>
       <c r="D62" t="n">
-        <v>10656.7</v>
+        <v>10682.7</v>
       </c>
       <c r="E62" t="n">
-        <v>10739</v>
+        <v>10705.3</v>
       </c>
       <c r="F62" t="n">
-        <v>79.90000000000001</v>
+        <v>-33.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0031</v>
       </c>
       <c r="H62" t="n">
-        <v>118</v>
+        <v>79.8</v>
       </c>
       <c r="I62" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J62" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K62" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L62" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M62" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N62" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O62" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5700,15 +5700,13 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5723,57 +5721,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10708.79</v>
+        <v>10705.47</v>
       </c>
       <c r="C63" t="n">
-        <v>10762.52</v>
+        <v>10741.11</v>
       </c>
       <c r="D63" t="n">
-        <v>10682.73</v>
+        <v>10666.91</v>
       </c>
       <c r="E63" t="n">
-        <v>10705.26</v>
+        <v>10679.99</v>
       </c>
       <c r="F63" t="n">
-        <v>-33.74</v>
+        <v>-25.31</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0024</v>
       </c>
       <c r="H63" t="n">
-        <v>79.79000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="I63" t="n">
-        <v>10538.7</v>
+        <v>10602.9</v>
       </c>
       <c r="J63" t="n">
-        <v>10632.65</v>
+        <v>10616.85</v>
       </c>
       <c r="K63" t="n">
-        <v>10680</v>
+        <v>10665.4</v>
       </c>
       <c r="L63" t="n">
-        <v>10727.35</v>
+        <v>10713.95</v>
       </c>
       <c r="M63" t="n">
-        <v>10798</v>
+        <v>10745.2</v>
       </c>
       <c r="N63" t="n">
-        <v>10868.65</v>
+        <v>10776.45</v>
       </c>
       <c r="O63" t="n">
-        <v>10892.7</v>
+        <v>10842.3</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5781,12 +5779,14 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5803,11 +5803,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10507.8</v>
+        <v>10484.3</v>
       </c>
       <c r="C2" t="n">
-        <v>10521</v>
+        <v>10613.2</v>
       </c>
       <c r="D2" t="n">
-        <v>10472</v>
+        <v>10483.9</v>
       </c>
       <c r="E2" t="n">
-        <v>10484.2</v>
+        <v>10497.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-23.8</v>
+        <v>12.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>129.3</v>
       </c>
       <c r="I2" t="n">
-        <v>10279.2</v>
+        <v>10423</v>
       </c>
       <c r="J2" t="n">
-        <v>10402.77</v>
+        <v>10429.05</v>
       </c>
       <c r="K2" t="n">
-        <v>10445.25</v>
+        <v>10459.7</v>
       </c>
       <c r="L2" t="n">
-        <v>10487.73</v>
+        <v>10490.35</v>
       </c>
       <c r="M2" t="n">
-        <v>10570.75</v>
+        <v>10508.7</v>
       </c>
       <c r="N2" t="n">
-        <v>10653.77</v>
+        <v>10527.05</v>
       </c>
       <c r="O2" t="n">
-        <v>10655.7</v>
+        <v>10570</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,76 +690,78 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C3" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D3" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E3" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F3" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H3" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J3" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K3" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L3" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M3" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N3" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O3" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,83 +769,83 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C4" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D4" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E4" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H4" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I4" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J4" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K4" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L4" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M4" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N4" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O4" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,76 +860,78 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C5" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D5" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E5" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F5" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H5" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I5" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J5" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K5" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L5" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M5" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N5" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O5" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,30 +939,22 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -970,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C6" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D6" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E6" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F6" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H6" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I6" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J6" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K6" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L6" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M6" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N6" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O6" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,16 +1017,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1043,55 +1043,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C7" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D7" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E7" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H7" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I7" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J7" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K7" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L7" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M7" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N7" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O7" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,14 +1103,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1125,78 +1127,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C8" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D8" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E8" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F8" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H8" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I8" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J8" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K8" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L8" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M8" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N8" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O8" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1204,9 +1206,9 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1214,69 +1216,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C9" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D9" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E9" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H9" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I9" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J9" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K9" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L9" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M9" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N9" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O9" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1298,50 +1294,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C10" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D10" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E10" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H10" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I10" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J10" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K10" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L10" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M10" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N10" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O10" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,7 +1350,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1371,55 +1367,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C11" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D11" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E11" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F11" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J11" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K11" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L11" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M11" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N11" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O11" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1427,16 +1427,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1451,77 +1455,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C12" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D12" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E12" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H12" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I12" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J12" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K12" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L12" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M12" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N12" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O12" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1537,80 +1543,76 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C13" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D13" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E13" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F13" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H13" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I13" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J13" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K13" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L13" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M13" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N13" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O13" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1625,57 +1627,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C14" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D14" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E14" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H14" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I14" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J14" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K14" t="n">
         <v>10464.6</v>
       </c>
       <c r="L14" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M14" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N14" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O14" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,13 +1690,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1709,57 +1713,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C15" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D15" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E15" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F15" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I15" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J15" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K15" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L15" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M15" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N15" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O15" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,12 +1771,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1802,69 +1804,71 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C16" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D16" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E16" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F16" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H16" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I16" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J16" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K16" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L16" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M16" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N16" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O16" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1877,84 +1881,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C17" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D17" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E17" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H17" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I17" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J17" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K17" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L17" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M17" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N17" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O17" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1963,55 +1963,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C18" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D18" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E18" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F18" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H18" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I18" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J18" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K18" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L18" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M18" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N18" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O18" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,7 +2026,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2037,67 +2041,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C19" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D19" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E19" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F19" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H19" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I19" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J19" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K19" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L19" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M19" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N19" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O19" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2105,83 +2107,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C20" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D20" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E20" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H20" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I20" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J20" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K20" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L20" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M20" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N20" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O20" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,22 +2191,24 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2215,57 +2219,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C21" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D21" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E21" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F21" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H21" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I21" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J21" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K21" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L21" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M21" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N21" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O21" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,21 +2280,19 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2299,59 +2301,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C22" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D22" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E22" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F22" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H22" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I22" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J22" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K22" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L22" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M22" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N22" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O22" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,18 +2360,20 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2388,50 +2388,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C23" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D23" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E23" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F23" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H23" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I23" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J23" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K23" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L23" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M23" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N23" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O23" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,20 +2442,18 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2470,50 +2468,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C24" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D24" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E24" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F24" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I24" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J24" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K24" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L24" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M24" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N24" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O24" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2526,12 +2524,12 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2545,55 +2543,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C25" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D25" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E25" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H25" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I25" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J25" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K25" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L25" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M25" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N25" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O25" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2601,12 +2603,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2627,57 +2631,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C26" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D26" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E26" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J26" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K26" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L26" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M26" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N26" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O26" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2685,20 +2689,16 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2720,50 +2720,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C27" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D27" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E27" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H27" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I27" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J27" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K27" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L27" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M27" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N27" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O27" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2776,11 +2776,13 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2793,59 +2795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C28" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D28" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E28" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F28" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H28" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I28" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J28" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K28" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L28" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M28" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N28" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O28" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,10 +2851,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2866,8 +2866,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2877,55 +2879,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C29" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D29" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E29" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F29" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H29" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I29" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J29" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K29" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L29" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M29" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N29" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O29" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2933,25 +2939,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2963,57 +2963,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C30" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D30" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E30" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H30" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I30" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J30" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K30" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L30" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M30" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N30" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O30" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3026,14 +3026,18 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3045,57 +3049,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C31" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D31" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E31" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F31" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H31" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J31" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K31" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L31" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M31" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N31" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O31" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,23 +3107,21 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3131,57 +3133,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C32" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D32" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E32" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F32" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H32" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I32" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J32" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K32" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L32" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M32" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N32" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O32" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,14 +3191,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3222,50 +3222,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C33" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D33" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E33" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F33" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I33" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J33" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K33" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L33" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M33" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N33" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O33" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,10 +3273,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3304,65 +3306,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C34" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D34" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E34" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F34" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H34" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J34" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K34" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L34" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M34" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N34" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O34" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3374,79 +3378,73 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C35" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D35" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E35" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H35" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I35" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J35" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K35" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L35" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M35" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N35" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O35" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3470,50 +3468,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C36" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D36" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E36" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F36" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H36" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I36" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J36" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K36" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L36" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M36" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N36" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O36" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,13 +3524,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3545,55 +3545,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C37" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D37" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E37" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F37" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H37" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J37" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K37" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L37" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M37" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N37" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O37" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3601,14 +3605,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3616,8 +3618,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3636,50 +3640,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C38" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D38" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E38" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F38" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H38" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J38" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K38" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L38" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M38" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N38" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O38" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3692,18 +3696,14 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3722,50 +3722,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C39" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D39" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E39" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F39" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H39" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I39" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J39" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K39" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L39" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M39" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N39" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O39" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,10 +3773,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3797,57 +3799,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C40" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D40" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E40" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F40" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H40" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I40" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J40" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K40" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L40" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M40" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N40" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O40" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,21 +3857,23 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3881,57 +3885,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C41" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D41" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E41" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F41" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H41" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I41" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J41" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K41" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L41" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M41" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N41" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O41" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3942,20 +3946,18 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3974,50 +3976,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C42" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D42" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E42" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F42" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H42" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I42" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J42" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K42" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L42" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M42" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N42" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O42" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4028,7 +4030,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4058,50 +4060,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C43" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D43" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E43" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F43" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J43" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K43" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L43" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M43" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N43" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O43" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4109,17 +4111,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4135,63 +4139,67 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C44" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D44" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E44" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I44" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J44" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K44" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L44" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M44" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N44" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O44" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
@@ -4200,13 +4208,11 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4219,78 +4225,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C45" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D45" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E45" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H45" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I45" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J45" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K45" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L45" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M45" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N45" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O45" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4307,68 +4303,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C46" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D46" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E46" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F46" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H46" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I46" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J46" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K46" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L46" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M46" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N46" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O46" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4385,78 +4391,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C47" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D47" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E47" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I47" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J47" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K47" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L47" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M47" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N47" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O47" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10968.8</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4473,55 +4471,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C48" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D48" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E48" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H48" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I48" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J48" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K48" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L48" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M48" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N48" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O48" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,21 +4531,23 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4555,57 +4559,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C49" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D49" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E49" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F49" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H49" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I49" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J49" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K49" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L49" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M49" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N49" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O49" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4616,20 +4620,16 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4641,57 +4641,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C50" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D50" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E50" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H50" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J50" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K50" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L50" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M50" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N50" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O50" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,16 +4699,20 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4723,57 +4727,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C51" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D51" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E51" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H51" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J51" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K51" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L51" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M51" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N51" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O51" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4786,15 +4790,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4807,74 +4809,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C52" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D52" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E52" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H52" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I52" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J52" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K52" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L52" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M52" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N52" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O52" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4896,67 +4898,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C53" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D53" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E53" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H53" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I53" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J53" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K53" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L53" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M53" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N53" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O53" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4980,50 +4978,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C54" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D54" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E54" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F54" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H54" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I54" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J54" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K54" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L54" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M54" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N54" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O54" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5031,21 +5029,23 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5055,55 +5055,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C55" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D55" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E55" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F55" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I55" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J55" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K55" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L55" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M55" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N55" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O55" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5114,7 +5118,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5124,10 +5128,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5146,69 +5148,71 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C56" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D56" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E56" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F56" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H56" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I56" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J56" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K56" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L56" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M56" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N56" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O56" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5221,81 +5225,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C57" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D57" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E57" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H57" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I57" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J57" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K57" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L57" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M57" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N57" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O57" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5307,55 +5305,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C58" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D58" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E58" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F58" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H58" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I58" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J58" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K58" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L58" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M58" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N58" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O58" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5366,113 +5368,111 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C59" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D59" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E59" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F59" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H59" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I59" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J59" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K59" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L59" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M59" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N59" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O59" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5480,72 +5480,70 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C60" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D60" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E60" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F60" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H60" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I60" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J60" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K60" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L60" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M60" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N60" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O60" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5557,55 +5555,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="C61" t="n">
-        <v>10774.7</v>
+        <v>10771.6</v>
       </c>
       <c r="D61" t="n">
-        <v>10656.7</v>
+        <v>10708.3</v>
       </c>
       <c r="E61" t="n">
-        <v>10739</v>
+        <v>10708.3</v>
       </c>
       <c r="F61" t="n">
-        <v>79.90000000000001</v>
+        <v>-30.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0029</v>
       </c>
       <c r="H61" t="n">
-        <v>118</v>
+        <v>63.3</v>
       </c>
       <c r="I61" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J61" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K61" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L61" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M61" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N61" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O61" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5618,13 +5620,11 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5662,34 +5662,34 @@
         <v>10705.3</v>
       </c>
       <c r="F62" t="n">
-        <v>-33.7</v>
+        <v>-3</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0003</v>
       </c>
       <c r="H62" t="n">
         <v>79.8</v>
       </c>
       <c r="I62" t="n">
-        <v>10538.7</v>
+        <v>10645</v>
       </c>
       <c r="J62" t="n">
-        <v>10632.65</v>
+        <v>10629.18</v>
       </c>
       <c r="K62" t="n">
-        <v>10680</v>
+        <v>10676.65</v>
       </c>
       <c r="L62" t="n">
-        <v>10727.35</v>
+        <v>10724.12</v>
       </c>
       <c r="M62" t="n">
-        <v>10798</v>
+        <v>10739.95</v>
       </c>
       <c r="N62" t="n">
-        <v>10868.65</v>
+        <v>10755.77</v>
       </c>
       <c r="O62" t="n">
-        <v>10892.7</v>
+        <v>10834.9</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5700,16 +5700,20 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5719,11 +5723,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5732,19 +5732,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10705.47</v>
+        <v>10705.5</v>
       </c>
       <c r="C63" t="n">
-        <v>10741.11</v>
+        <v>10741.1</v>
       </c>
       <c r="D63" t="n">
-        <v>10666.91</v>
+        <v>10666.9</v>
       </c>
       <c r="E63" t="n">
-        <v>10679.99</v>
+        <v>10680</v>
       </c>
       <c r="F63" t="n">
-        <v>-25.31</v>
+        <v>-25.3</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>-0.0024</v>
@@ -5784,7 +5784,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5804,6 +5804,92 @@
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>10679.9</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10753.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10667</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10695.3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H64" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10592.7</v>
+      </c>
+      <c r="J64" t="n">
+        <v>10593.8</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10642.9</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10692</v>
+      </c>
+      <c r="M64" t="n">
+        <v>10717.1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10742.2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>10815.3</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10484.3</v>
+        <v>10497.6</v>
       </c>
       <c r="C2" t="n">
-        <v>10613.2</v>
+        <v>10508.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10483.9</v>
+        <v>10429.2</v>
       </c>
       <c r="E2" t="n">
-        <v>10497.1</v>
+        <v>10478.3</v>
       </c>
       <c r="F2" t="n">
-        <v>12.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="H2" t="n">
-        <v>129.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>10423</v>
+        <v>10354.6</v>
       </c>
       <c r="J2" t="n">
-        <v>10429.05</v>
+        <v>10342.07</v>
       </c>
       <c r="K2" t="n">
-        <v>10459.7</v>
+        <v>10432.45</v>
       </c>
       <c r="L2" t="n">
-        <v>10490.35</v>
+        <v>10522.82</v>
       </c>
       <c r="M2" t="n">
-        <v>10508.7</v>
+        <v>10561.75</v>
       </c>
       <c r="N2" t="n">
-        <v>10527.05</v>
+        <v>10600.67</v>
       </c>
       <c r="O2" t="n">
-        <v>10570</v>
+        <v>10742.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,83 +685,83 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C3" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D3" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E3" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H3" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I3" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J3" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K3" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L3" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M3" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N3" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O3" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,76 +776,78 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C4" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D4" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E4" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F4" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H4" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I4" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J4" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K4" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L4" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M4" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N4" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O4" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,30 +855,22 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -888,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C5" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D5" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E5" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F5" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I5" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J5" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K5" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L5" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M5" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N5" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O5" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,16 +933,20 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -961,55 +959,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C6" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D6" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E6" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H6" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I6" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J6" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K6" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L6" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M6" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N6" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O6" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,21 +1019,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1043,78 +1043,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C7" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D7" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E7" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F7" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H7" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I7" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J7" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K7" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L7" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M7" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N7" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O7" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1122,9 +1122,9 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1132,69 +1132,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C8" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D8" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E8" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H8" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I8" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J8" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K8" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L8" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M8" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N8" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O8" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1216,50 +1210,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C9" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D9" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E9" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H9" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I9" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J9" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K9" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L9" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M9" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N9" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O9" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,7 +1266,7 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1289,55 +1283,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C10" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D10" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E10" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F10" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H10" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J10" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K10" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L10" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M10" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N10" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O10" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1345,16 +1343,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1369,77 +1371,79 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C11" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D11" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E11" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H11" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I11" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J11" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K11" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L11" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M11" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N11" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O11" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1455,80 +1459,76 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C12" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D12" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E12" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F12" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H12" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I12" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J12" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K12" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L12" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M12" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N12" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O12" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1543,57 +1543,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C13" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D13" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E13" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H13" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I13" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J13" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K13" t="n">
         <v>10464.6</v>
       </c>
       <c r="L13" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M13" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N13" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O13" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,13 +1606,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1627,57 +1629,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C14" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D14" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E14" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F14" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H14" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I14" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J14" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K14" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L14" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M14" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N14" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O14" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,12 +1687,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1720,69 +1720,71 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C15" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D15" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E15" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F15" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H15" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I15" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J15" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K15" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L15" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M15" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N15" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O15" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1795,84 +1797,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C16" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D16" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E16" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H16" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I16" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J16" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K16" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L16" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M16" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N16" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O16" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1881,55 +1879,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C17" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D17" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E17" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F17" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H17" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I17" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J17" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K17" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L17" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M17" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N17" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O17" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,7 +1942,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1955,67 +1957,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C18" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D18" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E18" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F18" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H18" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I18" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J18" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K18" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L18" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M18" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N18" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O18" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,83 +2023,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C19" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D19" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E19" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H19" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I19" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J19" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K19" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L19" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M19" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N19" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O19" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,22 +2107,24 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2133,57 +2135,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C20" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D20" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E20" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F20" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H20" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I20" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J20" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K20" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L20" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M20" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N20" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O20" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,21 +2196,19 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2217,59 +2217,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C21" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D21" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E21" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F21" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H21" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I21" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J21" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K21" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L21" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M21" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N21" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O21" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2280,18 +2276,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2306,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C22" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D22" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E22" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F22" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H22" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I22" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J22" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K22" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L22" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M22" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N22" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O22" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2360,20 +2358,18 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2388,50 +2384,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C23" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D23" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E23" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F23" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I23" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J23" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K23" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L23" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M23" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N23" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O23" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2444,12 +2440,12 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2463,55 +2459,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C24" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D24" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E24" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H24" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I24" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J24" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K24" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L24" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M24" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N24" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O24" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,12 +2519,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2545,57 +2547,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C25" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D25" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E25" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J25" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K25" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L25" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M25" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N25" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O25" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,20 +2605,16 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2638,50 +2636,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C26" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D26" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E26" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H26" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I26" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J26" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K26" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L26" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M26" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N26" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O26" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,11 +2692,13 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2711,59 +2711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C27" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D27" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E27" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F27" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H27" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J27" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K27" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L27" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M27" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N27" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O27" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2771,10 +2767,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2784,8 +2782,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2795,55 +2795,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C28" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D28" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E28" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F28" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H28" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I28" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J28" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K28" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L28" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M28" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N28" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O28" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,25 +2855,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2881,57 +2879,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C29" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D29" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E29" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H29" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I29" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J29" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K29" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L29" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M29" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N29" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O29" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2944,14 +2942,18 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2963,57 +2965,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C30" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D30" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E30" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F30" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H30" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J30" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K30" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L30" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M30" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N30" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O30" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,23 +3023,21 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3049,57 +3049,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C31" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D31" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E31" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H31" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I31" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J31" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K31" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L31" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M31" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N31" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O31" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3107,14 +3107,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3140,50 +3138,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C32" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D32" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E32" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F32" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I32" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J32" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K32" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L32" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M32" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N32" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O32" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3191,10 +3189,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3222,65 +3222,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C33" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D33" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E33" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H33" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J33" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K33" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L33" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M33" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N33" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O33" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3292,79 +3294,73 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C34" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D34" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E34" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H34" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I34" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J34" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K34" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L34" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M34" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N34" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O34" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3388,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C35" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D35" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E35" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F35" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H35" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I35" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J35" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K35" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L35" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M35" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N35" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O35" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3444,13 +3440,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3463,55 +3461,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C36" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D36" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E36" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F36" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H36" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I36" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J36" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K36" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L36" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M36" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N36" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O36" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3519,14 +3521,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3534,8 +3534,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3554,50 +3556,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C37" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D37" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E37" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F37" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H37" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J37" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K37" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L37" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M37" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N37" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O37" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3610,18 +3612,14 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3640,50 +3638,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C38" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D38" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E38" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F38" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H38" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I38" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J38" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K38" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L38" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M38" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N38" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O38" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3691,10 +3689,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3715,57 +3715,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C39" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D39" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E39" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F39" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H39" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I39" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J39" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K39" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L39" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M39" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N39" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O39" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,21 +3773,23 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3799,57 +3801,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C40" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D40" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E40" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F40" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H40" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I40" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J40" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K40" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L40" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M40" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N40" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O40" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3860,20 +3862,18 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3892,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C41" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D41" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E41" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F41" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H41" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J41" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K41" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L41" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M41" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N41" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O41" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3946,7 +3946,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3976,50 +3976,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C42" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D42" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F42" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J42" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K42" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L42" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M42" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N42" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O42" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4027,17 +4027,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4053,63 +4055,67 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C43" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D43" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E43" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I43" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J43" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K43" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L43" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M43" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N43" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O43" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4118,13 +4124,11 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4137,78 +4141,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C44" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D44" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E44" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H44" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I44" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J44" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K44" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L44" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M44" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N44" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O44" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4225,68 +4219,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C45" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D45" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E45" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F45" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H45" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I45" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J45" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K45" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L45" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M45" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N45" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O45" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4303,78 +4307,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C46" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D46" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E46" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I46" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J46" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K46" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L46" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M46" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N46" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O46" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4391,55 +4387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C47" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D47" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E47" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H47" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I47" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J47" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K47" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L47" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M47" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N47" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O47" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,21 +4447,23 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4473,57 +4475,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C48" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D48" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E48" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F48" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H48" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I48" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J48" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K48" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L48" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M48" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N48" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O48" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,20 +4536,16 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4559,57 +4557,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C49" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D49" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E49" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H49" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J49" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K49" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L49" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M49" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N49" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O49" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,16 +4615,20 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4641,57 +4643,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C50" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D50" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E50" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H50" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J50" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K50" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L50" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M50" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N50" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O50" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4704,15 +4706,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4725,74 +4725,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C51" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D51" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E51" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F51" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H51" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I51" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J51" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K51" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L51" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M51" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N51" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O51" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4814,67 +4814,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C52" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D52" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E52" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F52" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H52" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I52" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J52" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K52" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L52" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M52" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N52" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O52" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4898,50 +4894,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C53" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D53" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E53" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F53" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H53" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I53" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J53" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K53" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L53" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M53" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N53" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O53" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4949,21 +4945,23 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4973,55 +4971,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C54" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D54" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E54" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F54" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H54" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I54" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J54" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K54" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L54" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M54" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N54" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O54" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5032,7 +5034,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5042,10 +5044,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5064,69 +5064,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C55" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D55" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E55" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F55" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H55" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I55" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J55" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K55" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L55" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M55" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N55" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O55" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5139,81 +5141,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C56" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D56" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E56" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H56" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I56" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J56" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K56" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L56" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M56" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N56" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O56" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5225,55 +5221,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C57" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D57" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E57" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F57" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H57" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I57" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J57" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K57" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L57" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M57" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N57" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O57" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5284,113 +5284,111 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C58" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D58" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E58" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F58" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H58" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I58" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J58" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K58" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L58" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M58" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N58" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O58" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -5398,72 +5396,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C59" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D59" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E59" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F59" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H59" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I59" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J59" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K59" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L59" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M59" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N59" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O59" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5475,55 +5471,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="C60" t="n">
-        <v>10774.7</v>
+        <v>10771.6</v>
       </c>
       <c r="D60" t="n">
-        <v>10656.7</v>
+        <v>10708.3</v>
       </c>
       <c r="E60" t="n">
-        <v>10739</v>
+        <v>10708.3</v>
       </c>
       <c r="F60" t="n">
-        <v>79.90000000000001</v>
+        <v>-30.7</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0029</v>
       </c>
       <c r="H60" t="n">
-        <v>118</v>
+        <v>63.3</v>
       </c>
       <c r="I60" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J60" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K60" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L60" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M60" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N60" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O60" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5536,13 +5536,11 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5557,57 +5555,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10739</v>
+        <v>10708.8</v>
       </c>
       <c r="C61" t="n">
-        <v>10771.6</v>
+        <v>10762.5</v>
       </c>
       <c r="D61" t="n">
-        <v>10708.3</v>
+        <v>10682.7</v>
       </c>
       <c r="E61" t="n">
-        <v>10708.3</v>
+        <v>10705.3</v>
       </c>
       <c r="F61" t="n">
-        <v>-30.7</v>
+        <v>-3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H61" t="n">
-        <v>63.3</v>
+        <v>79.8</v>
       </c>
       <c r="I61" t="n">
-        <v>10538.7</v>
+        <v>10645</v>
       </c>
       <c r="J61" t="n">
-        <v>10632.65</v>
+        <v>10629.18</v>
       </c>
       <c r="K61" t="n">
-        <v>10680</v>
+        <v>10676.65</v>
       </c>
       <c r="L61" t="n">
-        <v>10727.35</v>
+        <v>10724.12</v>
       </c>
       <c r="M61" t="n">
-        <v>10798</v>
+        <v>10739.95</v>
       </c>
       <c r="N61" t="n">
-        <v>10868.65</v>
+        <v>10755.77</v>
       </c>
       <c r="O61" t="n">
-        <v>10892.7</v>
+        <v>10834.9</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5618,16 +5616,20 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5637,59 +5639,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10708.8</v>
+        <v>10705.5</v>
       </c>
       <c r="C62" t="n">
-        <v>10762.5</v>
+        <v>10741.1</v>
       </c>
       <c r="D62" t="n">
-        <v>10682.7</v>
+        <v>10666.9</v>
       </c>
       <c r="E62" t="n">
-        <v>10705.3</v>
+        <v>10680</v>
       </c>
       <c r="F62" t="n">
-        <v>-3</v>
+        <v>-25.3</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0024</v>
       </c>
       <c r="H62" t="n">
-        <v>79.8</v>
+        <v>74.2</v>
       </c>
       <c r="I62" t="n">
-        <v>10645</v>
+        <v>10602.9</v>
       </c>
       <c r="J62" t="n">
-        <v>10629.18</v>
+        <v>10616.85</v>
       </c>
       <c r="K62" t="n">
-        <v>10676.65</v>
+        <v>10665.4</v>
       </c>
       <c r="L62" t="n">
-        <v>10724.12</v>
+        <v>10713.95</v>
       </c>
       <c r="M62" t="n">
-        <v>10739.95</v>
+        <v>10745.2</v>
       </c>
       <c r="N62" t="n">
-        <v>10755.77</v>
+        <v>10776.45</v>
       </c>
       <c r="O62" t="n">
-        <v>10834.9</v>
+        <v>10842.3</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5697,23 +5695,21 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5728,50 +5724,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10705.5</v>
+        <v>10679.9</v>
       </c>
       <c r="C63" t="n">
-        <v>10741.1</v>
+        <v>10753.4</v>
       </c>
       <c r="D63" t="n">
-        <v>10666.9</v>
+        <v>10667</v>
       </c>
       <c r="E63" t="n">
-        <v>10680</v>
+        <v>10695.3</v>
       </c>
       <c r="F63" t="n">
-        <v>-25.3</v>
+        <v>15.3</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.0014</v>
       </c>
       <c r="H63" t="n">
-        <v>74.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>10602.9</v>
+        <v>10592.7</v>
       </c>
       <c r="J63" t="n">
-        <v>10616.85</v>
+        <v>10593.8</v>
       </c>
       <c r="K63" t="n">
-        <v>10665.4</v>
+        <v>10642.9</v>
       </c>
       <c r="L63" t="n">
-        <v>10713.95</v>
+        <v>10692</v>
       </c>
       <c r="M63" t="n">
-        <v>10745.2</v>
+        <v>10717.1</v>
       </c>
       <c r="N63" t="n">
-        <v>10776.45</v>
+        <v>10742.2</v>
       </c>
       <c r="O63" t="n">
-        <v>10842.3</v>
+        <v>10815.3</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5779,21 +5775,23 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R63" s="6" t="n">
+        <v/>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5803,55 +5801,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10679.9</v>
+        <v>10695.19</v>
       </c>
       <c r="C64" t="n">
-        <v>10753.4</v>
+        <v>10758.74</v>
       </c>
       <c r="D64" t="n">
-        <v>10667</v>
+        <v>10684.88</v>
       </c>
       <c r="E64" t="n">
-        <v>10695.3</v>
+        <v>10684.88</v>
       </c>
       <c r="F64" t="n">
-        <v>15.3</v>
+        <v>-10.42</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.001</v>
       </c>
       <c r="H64" t="n">
-        <v>86.40000000000001</v>
+        <v>73.86</v>
       </c>
       <c r="I64" t="n">
-        <v>10592.7</v>
+        <v>10580.6</v>
       </c>
       <c r="J64" t="n">
-        <v>10593.8</v>
+        <v>10601.45</v>
       </c>
       <c r="K64" t="n">
-        <v>10642.9</v>
+        <v>10652.1</v>
       </c>
       <c r="L64" t="n">
-        <v>10692</v>
+        <v>10702.75</v>
       </c>
       <c r="M64" t="n">
-        <v>10717.1</v>
+        <v>10738.5</v>
       </c>
       <c r="N64" t="n">
-        <v>10742.2</v>
+        <v>10774.25</v>
       </c>
       <c r="O64" t="n">
-        <v>10815.3</v>
+        <v>10839.8</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5864,7 +5866,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5872,10 +5874,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10497.6</v>
+        <v>10477.8</v>
       </c>
       <c r="C2" t="n">
-        <v>10508.3</v>
+        <v>10694.9</v>
       </c>
       <c r="D2" t="n">
-        <v>10429.2</v>
+        <v>10436.8</v>
       </c>
       <c r="E2" t="n">
-        <v>10478.3</v>
+        <v>10652.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-18.8</v>
+        <v>174.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0167</v>
       </c>
       <c r="H2" t="n">
-        <v>79.09999999999999</v>
+        <v>258.1</v>
       </c>
       <c r="I2" t="n">
-        <v>10354.6</v>
+        <v>10350.1</v>
       </c>
       <c r="J2" t="n">
-        <v>10342.07</v>
+        <v>10403.98</v>
       </c>
       <c r="K2" t="n">
-        <v>10432.45</v>
+        <v>10438.75</v>
       </c>
       <c r="L2" t="n">
-        <v>10522.82</v>
+        <v>10473.52</v>
       </c>
       <c r="M2" t="n">
-        <v>10561.75</v>
+        <v>10517.85</v>
       </c>
       <c r="N2" t="n">
-        <v>10600.67</v>
+        <v>10562.17</v>
       </c>
       <c r="O2" t="n">
-        <v>10742.5</v>
+        <v>10587.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,76 +692,78 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C3" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D3" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E3" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F3" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H3" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I3" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J3" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K3" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L3" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M3" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N3" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O3" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,30 +771,22 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -804,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C4" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D4" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E4" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F4" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H4" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I4" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J4" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K4" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L4" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M4" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N4" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O4" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,16 +849,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -877,55 +875,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C5" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D5" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E5" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H5" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I5" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J5" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K5" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L5" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M5" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N5" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O5" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,21 +935,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -959,78 +959,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C6" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D6" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E6" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F6" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H6" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I6" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J6" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K6" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L6" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M6" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N6" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O6" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1038,9 +1038,9 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1048,69 +1048,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C7" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D7" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E7" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H7" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I7" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J7" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K7" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L7" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M7" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N7" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O7" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1132,50 +1126,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C8" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D8" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E8" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H8" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I8" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J8" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K8" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L8" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M8" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N8" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O8" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,7 +1182,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1205,55 +1199,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C9" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D9" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E9" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F9" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H9" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J9" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K9" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L9" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M9" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N9" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O9" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1261,16 +1259,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1285,77 +1287,79 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C10" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D10" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E10" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H10" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J10" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K10" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L10" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M10" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N10" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O10" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1371,80 +1375,76 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C11" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D11" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E11" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F11" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H11" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I11" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J11" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K11" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L11" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M11" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N11" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O11" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1459,57 +1459,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C12" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D12" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E12" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H12" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I12" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J12" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K12" t="n">
         <v>10464.6</v>
       </c>
       <c r="L12" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M12" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N12" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O12" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,13 +1522,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1543,57 +1545,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C13" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D13" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E13" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F13" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H13" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J13" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K13" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L13" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M13" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N13" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O13" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,12 +1603,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1636,69 +1636,71 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C14" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D14" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E14" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F14" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H14" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I14" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J14" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K14" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L14" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M14" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N14" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O14" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1711,84 +1713,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C15" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D15" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E15" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H15" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I15" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J15" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K15" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L15" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M15" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N15" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O15" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1797,55 +1795,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C16" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D16" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E16" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F16" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H16" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I16" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J16" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K16" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L16" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M16" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N16" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O16" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,7 +1858,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1871,67 +1873,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C17" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D17" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E17" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F17" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H17" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I17" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J17" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K17" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L17" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M17" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N17" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O17" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,83 +1939,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C18" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D18" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H18" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I18" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J18" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K18" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L18" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M18" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N18" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O18" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,22 +2023,24 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2049,57 +2051,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C19" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D19" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E19" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F19" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H19" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I19" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J19" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K19" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L19" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M19" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N19" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O19" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,21 +2112,19 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2133,59 +2133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C20" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D20" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E20" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F20" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H20" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I20" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J20" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K20" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L20" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M20" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N20" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O20" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,18 +2192,20 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2222,50 +2220,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C21" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D21" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E21" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F21" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H21" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I21" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J21" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K21" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L21" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M21" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N21" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O21" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,20 +2274,18 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2304,50 +2300,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C22" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D22" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E22" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F22" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I22" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J22" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K22" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L22" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M22" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N22" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O22" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2360,12 +2356,12 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2379,55 +2375,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C23" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D23" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E23" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H23" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I23" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J23" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K23" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L23" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M23" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N23" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O23" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,12 +2435,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2461,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C24" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D24" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E24" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F24" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J24" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K24" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L24" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M24" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N24" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O24" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,20 +2521,16 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2554,50 +2552,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C25" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D25" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E25" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H25" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I25" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J25" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K25" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L25" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M25" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N25" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O25" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,11 +2608,13 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2627,59 +2627,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C26" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D26" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E26" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F26" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H26" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I26" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J26" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K26" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L26" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M26" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N26" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O26" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2687,10 +2683,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2700,8 +2698,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2711,55 +2711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C27" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D27" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E27" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F27" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H27" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I27" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J27" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K27" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L27" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M27" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N27" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O27" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,25 +2771,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2797,57 +2795,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C28" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D28" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E28" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H28" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I28" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J28" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K28" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L28" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M28" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N28" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O28" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,14 +2858,18 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2879,57 +2881,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C29" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D29" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E29" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F29" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H29" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J29" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K29" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L29" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M29" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N29" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O29" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2937,23 +2939,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2965,57 +2965,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C30" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D30" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E30" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F30" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H30" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I30" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J30" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K30" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L30" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M30" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N30" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O30" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,14 +3023,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3056,50 +3054,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C31" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D31" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E31" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I31" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J31" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K31" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L31" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M31" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N31" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O31" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3107,10 +3105,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3138,65 +3138,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C32" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D32" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E32" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H32" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J32" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K32" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L32" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M32" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N32" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O32" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3208,79 +3210,73 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C33" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D33" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E33" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H33" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I33" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J33" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K33" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L33" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M33" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N33" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O33" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3304,50 +3300,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C34" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D34" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E34" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F34" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H34" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I34" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J34" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K34" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L34" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M34" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N34" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O34" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3360,13 +3356,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3379,55 +3377,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C35" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D35" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E35" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F35" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H35" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I35" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J35" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K35" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L35" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M35" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N35" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O35" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3435,14 +3437,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3450,8 +3450,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3470,50 +3472,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C36" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D36" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E36" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F36" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H36" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J36" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K36" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L36" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M36" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N36" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O36" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,18 +3528,14 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3556,50 +3554,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C37" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D37" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E37" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F37" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H37" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I37" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J37" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K37" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L37" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M37" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N37" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O37" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,10 +3605,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3631,57 +3631,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C38" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D38" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E38" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F38" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H38" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I38" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J38" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K38" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L38" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M38" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N38" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O38" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3689,21 +3689,23 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3715,57 +3717,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C39" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D39" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E39" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F39" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H39" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I39" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J39" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K39" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L39" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M39" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N39" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O39" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3776,20 +3778,18 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3808,50 +3808,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C40" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D40" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E40" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F40" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H40" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J40" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K40" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L40" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M40" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N40" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O40" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3862,7 +3862,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3892,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C41" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D41" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E41" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F41" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J41" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K41" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L41" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M41" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N41" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O41" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3943,17 +3943,19 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3969,63 +3971,67 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C42" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D42" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I42" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J42" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K42" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L42" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M42" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N42" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O42" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4034,13 +4040,11 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4053,78 +4057,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C43" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D43" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E43" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H43" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I43" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J43" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K43" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L43" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M43" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N43" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O43" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4141,68 +4135,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C44" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D44" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E44" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F44" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H44" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I44" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J44" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K44" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L44" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M44" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N44" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O44" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4219,78 +4223,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C45" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D45" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E45" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I45" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J45" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K45" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L45" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M45" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N45" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O45" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4307,55 +4303,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C46" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D46" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E46" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H46" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I46" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J46" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K46" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L46" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M46" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N46" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O46" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4363,21 +4363,23 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4389,57 +4391,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C47" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D47" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E47" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F47" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H47" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I47" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J47" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K47" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L47" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M47" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N47" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O47" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4450,20 +4452,16 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4475,57 +4473,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C48" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D48" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E48" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H48" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J48" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K48" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L48" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M48" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N48" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O48" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4533,16 +4531,20 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4557,57 +4559,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C49" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D49" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E49" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F49" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J49" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K49" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L49" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M49" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N49" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O49" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4620,15 +4622,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4641,74 +4641,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C50" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D50" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E50" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F50" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H50" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I50" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J50" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K50" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L50" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M50" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N50" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O50" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4730,67 +4730,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C51" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D51" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E51" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F51" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H51" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I51" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J51" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K51" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L51" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M51" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N51" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O51" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4814,50 +4810,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C52" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D52" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E52" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F52" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H52" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I52" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J52" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K52" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L52" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M52" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N52" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O52" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4865,21 +4861,23 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4889,55 +4887,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C53" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D53" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E53" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F53" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H53" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I53" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J53" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K53" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L53" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M53" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N53" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O53" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4948,7 +4950,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4958,10 +4960,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4980,69 +4980,71 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C54" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D54" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E54" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F54" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H54" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I54" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J54" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K54" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L54" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M54" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N54" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O54" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5055,81 +5057,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C55" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D55" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E55" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H55" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I55" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J55" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K55" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L55" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M55" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N55" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O55" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5141,55 +5137,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C56" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D56" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E56" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F56" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H56" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I56" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J56" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K56" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L56" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M56" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N56" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O56" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5200,113 +5200,111 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C57" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D57" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E57" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F57" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H57" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I57" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J57" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K57" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L57" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M57" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N57" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O57" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -5314,72 +5312,70 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C58" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D58" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F58" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H58" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I58" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J58" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K58" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L58" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M58" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N58" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O58" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5391,55 +5387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="C59" t="n">
-        <v>10774.7</v>
+        <v>10771.6</v>
       </c>
       <c r="D59" t="n">
-        <v>10656.7</v>
+        <v>10708.3</v>
       </c>
       <c r="E59" t="n">
-        <v>10739</v>
+        <v>10708.3</v>
       </c>
       <c r="F59" t="n">
-        <v>79.90000000000001</v>
+        <v>-30.7</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0029</v>
       </c>
       <c r="H59" t="n">
-        <v>118</v>
+        <v>63.3</v>
       </c>
       <c r="I59" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J59" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K59" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L59" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M59" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N59" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O59" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5452,13 +5452,11 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5473,57 +5471,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10739</v>
+        <v>10708.8</v>
       </c>
       <c r="C60" t="n">
-        <v>10771.6</v>
+        <v>10762.5</v>
       </c>
       <c r="D60" t="n">
-        <v>10708.3</v>
+        <v>10682.7</v>
       </c>
       <c r="E60" t="n">
-        <v>10708.3</v>
+        <v>10705.3</v>
       </c>
       <c r="F60" t="n">
-        <v>-30.7</v>
+        <v>-3</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H60" t="n">
-        <v>63.3</v>
+        <v>79.8</v>
       </c>
       <c r="I60" t="n">
-        <v>10538.7</v>
+        <v>10645</v>
       </c>
       <c r="J60" t="n">
-        <v>10632.65</v>
+        <v>10629.18</v>
       </c>
       <c r="K60" t="n">
-        <v>10680</v>
+        <v>10676.65</v>
       </c>
       <c r="L60" t="n">
-        <v>10727.35</v>
+        <v>10724.12</v>
       </c>
       <c r="M60" t="n">
-        <v>10798</v>
+        <v>10739.95</v>
       </c>
       <c r="N60" t="n">
-        <v>10868.65</v>
+        <v>10755.77</v>
       </c>
       <c r="O60" t="n">
-        <v>10892.7</v>
+        <v>10834.9</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5534,16 +5532,20 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5553,59 +5555,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10708.8</v>
+        <v>10705.5</v>
       </c>
       <c r="C61" t="n">
-        <v>10762.5</v>
+        <v>10741.1</v>
       </c>
       <c r="D61" t="n">
-        <v>10682.7</v>
+        <v>10666.9</v>
       </c>
       <c r="E61" t="n">
-        <v>10705.3</v>
+        <v>10680</v>
       </c>
       <c r="F61" t="n">
-        <v>-3</v>
+        <v>-25.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0024</v>
       </c>
       <c r="H61" t="n">
-        <v>79.8</v>
+        <v>74.2</v>
       </c>
       <c r="I61" t="n">
-        <v>10645</v>
+        <v>10602.9</v>
       </c>
       <c r="J61" t="n">
-        <v>10629.18</v>
+        <v>10616.85</v>
       </c>
       <c r="K61" t="n">
-        <v>10676.65</v>
+        <v>10665.4</v>
       </c>
       <c r="L61" t="n">
-        <v>10724.12</v>
+        <v>10713.95</v>
       </c>
       <c r="M61" t="n">
-        <v>10739.95</v>
+        <v>10745.2</v>
       </c>
       <c r="N61" t="n">
-        <v>10755.77</v>
+        <v>10776.45</v>
       </c>
       <c r="O61" t="n">
-        <v>10834.9</v>
+        <v>10842.3</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5613,23 +5611,21 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5644,50 +5640,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10705.5</v>
+        <v>10679.9</v>
       </c>
       <c r="C62" t="n">
-        <v>10741.1</v>
+        <v>10753.4</v>
       </c>
       <c r="D62" t="n">
-        <v>10666.9</v>
+        <v>10667</v>
       </c>
       <c r="E62" t="n">
-        <v>10680</v>
+        <v>10695.3</v>
       </c>
       <c r="F62" t="n">
-        <v>-25.3</v>
+        <v>15.3</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.0014</v>
       </c>
       <c r="H62" t="n">
-        <v>74.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>10602.9</v>
+        <v>10592.7</v>
       </c>
       <c r="J62" t="n">
-        <v>10616.85</v>
+        <v>10593.8</v>
       </c>
       <c r="K62" t="n">
-        <v>10665.4</v>
+        <v>10642.9</v>
       </c>
       <c r="L62" t="n">
-        <v>10713.95</v>
+        <v>10692</v>
       </c>
       <c r="M62" t="n">
-        <v>10745.2</v>
+        <v>10717.1</v>
       </c>
       <c r="N62" t="n">
-        <v>10776.45</v>
+        <v>10742.2</v>
       </c>
       <c r="O62" t="n">
-        <v>10842.3</v>
+        <v>10815.3</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5695,21 +5691,23 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5719,55 +5717,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10679.9</v>
+        <v>10695.2</v>
       </c>
       <c r="C63" t="n">
-        <v>10753.4</v>
+        <v>10758.7</v>
       </c>
       <c r="D63" t="n">
-        <v>10667</v>
+        <v>10684.9</v>
       </c>
       <c r="E63" t="n">
-        <v>10695.3</v>
+        <v>10684.9</v>
       </c>
       <c r="F63" t="n">
-        <v>15.3</v>
+        <v>-10.4</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.001</v>
       </c>
       <c r="H63" t="n">
-        <v>86.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="I63" t="n">
-        <v>10592.7</v>
+        <v>10580.6</v>
       </c>
       <c r="J63" t="n">
-        <v>10593.8</v>
+        <v>10601.45</v>
       </c>
       <c r="K63" t="n">
-        <v>10642.9</v>
+        <v>10652.1</v>
       </c>
       <c r="L63" t="n">
-        <v>10692</v>
+        <v>10702.75</v>
       </c>
       <c r="M63" t="n">
-        <v>10717.1</v>
+        <v>10738.5</v>
       </c>
       <c r="N63" t="n">
-        <v>10742.2</v>
+        <v>10774.25</v>
       </c>
       <c r="O63" t="n">
-        <v>10815.3</v>
+        <v>10839.8</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5780,7 +5782,7 @@
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
@@ -5788,10 +5790,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5803,57 +5803,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10695.19</v>
+        <v>10685.19</v>
       </c>
       <c r="C64" t="n">
-        <v>10758.74</v>
+        <v>10756.15</v>
       </c>
       <c r="D64" t="n">
-        <v>10684.88</v>
+        <v>10622</v>
       </c>
       <c r="E64" t="n">
-        <v>10684.88</v>
+        <v>10636.71</v>
       </c>
       <c r="F64" t="n">
-        <v>-10.42</v>
+        <v>-48.19</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0045</v>
       </c>
       <c r="H64" t="n">
-        <v>73.86</v>
+        <v>134.15</v>
       </c>
       <c r="I64" t="n">
-        <v>10580.6</v>
+        <v>10611.1</v>
       </c>
       <c r="J64" t="n">
-        <v>10601.45</v>
+        <v>10592.65</v>
       </c>
       <c r="K64" t="n">
-        <v>10652.1</v>
+        <v>10648</v>
       </c>
       <c r="L64" t="n">
-        <v>10702.75</v>
+        <v>10703.35</v>
       </c>
       <c r="M64" t="n">
-        <v>10738.5</v>
+        <v>10721.8</v>
       </c>
       <c r="N64" t="n">
-        <v>10774.25</v>
+        <v>10740.25</v>
       </c>
       <c r="O64" t="n">
-        <v>10839.8</v>
+        <v>10832.5</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5861,12 +5861,14 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5874,8 +5876,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="n">
-        <v/>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
@@ -5885,11 +5889,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10477.8</v>
+        <v>10652.8</v>
       </c>
       <c r="C2" t="n">
-        <v>10694.9</v>
+        <v>10701.3</v>
       </c>
       <c r="D2" t="n">
-        <v>10436.8</v>
+        <v>10604.3</v>
       </c>
       <c r="E2" t="n">
-        <v>10652.9</v>
+        <v>10679</v>
       </c>
       <c r="F2" t="n">
-        <v>174.6</v>
+        <v>26.1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>258.1</v>
+        <v>97</v>
       </c>
       <c r="I2" t="n">
-        <v>10350.1</v>
+        <v>10178.7</v>
       </c>
       <c r="J2" t="n">
-        <v>10403.98</v>
+        <v>10438.32</v>
       </c>
       <c r="K2" t="n">
-        <v>10438.75</v>
+        <v>10523.85</v>
       </c>
       <c r="L2" t="n">
-        <v>10473.52</v>
+        <v>10609.38</v>
       </c>
       <c r="M2" t="n">
-        <v>10517.85</v>
+        <v>10781.95</v>
       </c>
       <c r="N2" t="n">
-        <v>10562.17</v>
+        <v>10954.53</v>
       </c>
       <c r="O2" t="n">
-        <v>10587.4</v>
+        <v>10953</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,30 +685,22 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -720,50 +712,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C3" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D3" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E3" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F3" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H3" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I3" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J3" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K3" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L3" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M3" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N3" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O3" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,16 +763,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C4" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D4" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E4" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H4" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J4" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K4" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L4" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M4" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N4" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O4" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,21 +849,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -875,88 +873,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C5" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D5" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E5" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F5" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H5" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J5" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K5" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L5" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M5" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N5" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O5" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>10842.8</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -964,69 +962,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C6" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D6" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E6" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H6" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I6" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J6" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K6" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L6" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M6" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N6" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O6" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10865.2</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1048,50 +1040,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C7" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D7" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E7" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F7" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H7" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I7" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J7" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K7" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L7" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M7" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N7" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O7" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,9 +1094,9 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1121,55 +1113,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C8" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D8" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E8" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F8" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H8" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J8" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K8" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L8" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M8" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N8" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O8" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1177,16 +1173,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1201,63 +1201,65 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C9" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D9" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E9" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H9" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J9" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K9" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L9" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M9" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N9" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O9" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1266,12 +1268,12 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1287,80 +1289,76 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C10" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D10" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E10" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F10" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H10" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J10" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K10" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L10" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M10" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N10" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O10" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1375,57 +1373,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C11" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D11" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E11" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H11" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I11" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J11" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K11" t="n">
         <v>10464.6</v>
       </c>
       <c r="L11" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M11" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N11" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O11" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,11 +1438,13 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1459,57 +1459,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C12" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D12" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E12" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F12" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H12" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I12" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J12" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K12" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L12" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M12" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N12" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O12" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,10 +1517,8 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1552,70 +1550,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C13" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D13" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E13" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F13" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H13" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I13" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J13" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K13" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L13" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M13" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N13" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O13" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1627,84 +1627,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C14" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D14" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E14" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H14" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I14" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J14" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K14" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L14" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M14" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N14" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O14" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1713,55 +1709,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C15" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D15" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E15" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F15" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H15" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I15" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J15" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K15" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L15" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M15" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N15" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O15" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,67 +1787,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C16" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D16" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E16" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F16" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H16" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I16" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J16" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K16" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L16" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M16" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N16" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O16" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,83 +1853,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C17" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D17" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E17" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H17" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I17" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J17" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K17" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L17" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M17" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N17" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O17" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,22 +1937,24 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1965,57 +1965,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C18" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D18" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F18" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H18" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I18" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J18" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K18" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L18" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M18" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N18" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O18" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,14 +2033,12 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2049,59 +2047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C19" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D19" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E19" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F19" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H19" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I19" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J19" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K19" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L19" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M19" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N19" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O19" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2119,11 +2113,13 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2138,50 +2134,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C20" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D20" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E20" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F20" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H20" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I20" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J20" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K20" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L20" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M20" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N20" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O20" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2199,13 +2195,11 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2220,50 +2214,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C21" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D21" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E21" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F21" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I21" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J21" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K21" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L21" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M21" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N21" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O21" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,14 +2268,14 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2295,55 +2289,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C22" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D22" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E22" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H22" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I22" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J22" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K22" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L22" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M22" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N22" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O22" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2351,12 +2349,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2377,57 +2377,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C23" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D23" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E23" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J23" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K23" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L23" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M23" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N23" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O23" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,20 +2435,16 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2470,50 +2466,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C24" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D24" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E24" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H24" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I24" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J24" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K24" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L24" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M24" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N24" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O24" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,13 +2520,15 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2543,59 +2541,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C25" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D25" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E25" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F25" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H25" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J25" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K25" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L25" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M25" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N25" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O25" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,8 +2597,10 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2616,8 +2612,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2627,55 +2625,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C26" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D26" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E26" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F26" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H26" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I26" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J26" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K26" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L26" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M26" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N26" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O26" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2683,25 +2685,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2713,57 +2709,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C27" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D27" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E27" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H27" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I27" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J27" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K27" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L27" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M27" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N27" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O27" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2774,16 +2770,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2795,57 +2795,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C28" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D28" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E28" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F28" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H28" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J28" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K28" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L28" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M28" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N28" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O28" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,23 +2853,21 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2881,57 +2879,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C29" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D29" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E29" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H29" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I29" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J29" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K29" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L29" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M29" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N29" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O29" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,14 +2937,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2972,50 +2968,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C30" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D30" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E30" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F30" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I30" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J30" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K30" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L30" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M30" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N30" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O30" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,8 +3019,10 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
@@ -3054,56 +3052,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C31" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D31" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E31" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H31" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J31" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K31" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L31" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M31" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N31" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O31" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3124,76 +3124,70 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C32" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D32" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E32" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F32" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H32" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I32" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J32" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K32" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L32" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M32" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N32" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O32" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
@@ -3220,50 +3214,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C33" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D33" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E33" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F33" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H33" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I33" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J33" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K33" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L33" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M33" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N33" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O33" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3281,8 +3275,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3295,55 +3291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C34" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D34" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E34" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F34" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H34" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I34" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J34" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K34" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L34" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M34" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N34" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O34" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3351,14 +3351,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3366,8 +3364,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3386,50 +3386,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C35" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D35" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E35" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F35" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H35" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J35" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K35" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L35" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M35" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N35" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O35" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3440,20 +3440,16 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3472,50 +3468,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C36" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D36" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E36" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F36" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H36" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I36" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J36" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K36" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L36" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M36" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N36" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O36" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3523,8 +3519,10 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3547,57 +3545,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C37" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D37" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E37" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F37" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H37" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I37" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J37" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K37" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L37" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M37" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N37" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O37" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,21 +3603,23 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3631,57 +3631,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C38" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D38" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E38" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F38" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H38" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I38" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J38" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K38" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L38" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M38" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N38" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O38" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,13 +3699,11 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3724,50 +3722,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C39" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D39" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E39" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F39" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H39" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I39" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J39" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K39" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L39" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M39" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N39" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O39" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3808,50 +3806,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C40" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D40" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E40" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F40" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J40" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K40" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L40" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M40" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N40" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O40" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3859,17 +3857,19 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3885,78 +3885,80 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C41" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D41" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E41" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I41" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J41" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K41" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L41" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M41" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N41" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O41" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3969,78 +3971,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C42" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D42" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E42" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H42" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I42" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J42" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K42" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L42" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M42" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N42" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O42" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10984.4</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4057,68 +4049,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C43" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D43" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E43" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F43" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H43" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I43" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J43" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K43" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L43" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M43" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N43" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O43" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>10897.6</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4135,78 +4137,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C44" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D44" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E44" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H44" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I44" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J44" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K44" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L44" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M44" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N44" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O44" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4223,55 +4217,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C45" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D45" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E45" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H45" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I45" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J45" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K45" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L45" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M45" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N45" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O45" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4279,21 +4277,23 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4305,57 +4305,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C46" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D46" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E46" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F46" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H46" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I46" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J46" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K46" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L46" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M46" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N46" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O46" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4368,18 +4368,14 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4391,57 +4387,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C47" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D47" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E47" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H47" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J47" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K47" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L47" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M47" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N47" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O47" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4449,16 +4445,20 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4473,57 +4473,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C48" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D48" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E48" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F48" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J48" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K48" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L48" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M48" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N48" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O48" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,10 +4541,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4557,65 +4555,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C49" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D49" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E49" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F49" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H49" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I49" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J49" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K49" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L49" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M49" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N49" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O49" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
@@ -4624,7 +4622,7 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4646,64 +4644,60 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C50" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D50" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E50" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F50" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H50" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I50" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J50" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K50" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L50" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M50" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N50" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O50" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4730,50 +4724,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C51" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D51" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E51" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F51" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H51" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I51" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J51" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K51" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L51" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M51" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N51" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O51" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4781,21 +4775,23 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4805,55 +4801,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C52" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D52" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E52" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F52" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H52" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I52" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J52" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K52" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L52" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M52" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N52" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O52" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4874,10 +4874,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4896,70 +4894,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C53" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D53" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E53" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F53" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H53" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I53" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J53" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K53" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L53" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M53" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N53" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O53" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4971,81 +4971,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C54" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D54" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E54" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H54" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I54" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J54" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K54" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L54" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M54" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N54" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O54" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5057,55 +5051,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C55" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D55" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E55" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F55" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H55" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I55" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J55" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K55" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L55" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M55" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N55" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O55" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5123,106 +5121,104 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C56" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D56" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E56" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F56" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H56" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I56" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J56" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K56" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L56" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M56" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N56" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O56" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -5230,72 +5226,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C57" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D57" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E57" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F57" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H57" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I57" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J57" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K57" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L57" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M57" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N57" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O57" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5307,55 +5301,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="C58" t="n">
-        <v>10774.7</v>
+        <v>10771.6</v>
       </c>
       <c r="D58" t="n">
-        <v>10656.7</v>
+        <v>10708.3</v>
       </c>
       <c r="E58" t="n">
-        <v>10739</v>
+        <v>10708.3</v>
       </c>
       <c r="F58" t="n">
-        <v>79.90000000000001</v>
+        <v>-30.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0029</v>
       </c>
       <c r="H58" t="n">
-        <v>118</v>
+        <v>63.3</v>
       </c>
       <c r="I58" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J58" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K58" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L58" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M58" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N58" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O58" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5366,15 +5364,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5389,57 +5385,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10739</v>
+        <v>10708.8</v>
       </c>
       <c r="C59" t="n">
-        <v>10771.6</v>
+        <v>10762.5</v>
       </c>
       <c r="D59" t="n">
-        <v>10708.3</v>
+        <v>10682.7</v>
       </c>
       <c r="E59" t="n">
-        <v>10708.3</v>
+        <v>10705.3</v>
       </c>
       <c r="F59" t="n">
-        <v>-30.7</v>
+        <v>-3</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H59" t="n">
-        <v>63.3</v>
+        <v>79.8</v>
       </c>
       <c r="I59" t="n">
-        <v>10538.7</v>
+        <v>10645</v>
       </c>
       <c r="J59" t="n">
-        <v>10632.65</v>
+        <v>10629.18</v>
       </c>
       <c r="K59" t="n">
-        <v>10680</v>
+        <v>10676.65</v>
       </c>
       <c r="L59" t="n">
-        <v>10727.35</v>
+        <v>10724.12</v>
       </c>
       <c r="M59" t="n">
-        <v>10798</v>
+        <v>10739.95</v>
       </c>
       <c r="N59" t="n">
-        <v>10868.65</v>
+        <v>10755.77</v>
       </c>
       <c r="O59" t="n">
-        <v>10892.7</v>
+        <v>10834.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5455,11 +5451,15 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5469,59 +5469,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10708.8</v>
+        <v>10705.5</v>
       </c>
       <c r="C60" t="n">
-        <v>10762.5</v>
+        <v>10741.1</v>
       </c>
       <c r="D60" t="n">
-        <v>10682.7</v>
+        <v>10666.9</v>
       </c>
       <c r="E60" t="n">
-        <v>10705.3</v>
+        <v>10680</v>
       </c>
       <c r="F60" t="n">
-        <v>-3</v>
+        <v>-25.3</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0024</v>
       </c>
       <c r="H60" t="n">
-        <v>79.8</v>
+        <v>74.2</v>
       </c>
       <c r="I60" t="n">
-        <v>10645</v>
+        <v>10602.9</v>
       </c>
       <c r="J60" t="n">
-        <v>10629.18</v>
+        <v>10616.85</v>
       </c>
       <c r="K60" t="n">
-        <v>10676.65</v>
+        <v>10665.4</v>
       </c>
       <c r="L60" t="n">
-        <v>10724.12</v>
+        <v>10713.95</v>
       </c>
       <c r="M60" t="n">
-        <v>10739.95</v>
+        <v>10745.2</v>
       </c>
       <c r="N60" t="n">
-        <v>10755.77</v>
+        <v>10776.45</v>
       </c>
       <c r="O60" t="n">
-        <v>10834.9</v>
+        <v>10842.3</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5529,23 +5525,21 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5560,50 +5554,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10705.5</v>
+        <v>10679.9</v>
       </c>
       <c r="C61" t="n">
-        <v>10741.1</v>
+        <v>10753.4</v>
       </c>
       <c r="D61" t="n">
-        <v>10666.9</v>
+        <v>10667</v>
       </c>
       <c r="E61" t="n">
-        <v>10680</v>
+        <v>10695.3</v>
       </c>
       <c r="F61" t="n">
-        <v>-25.3</v>
+        <v>15.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.0014</v>
       </c>
       <c r="H61" t="n">
-        <v>74.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>10602.9</v>
+        <v>10592.7</v>
       </c>
       <c r="J61" t="n">
-        <v>10616.85</v>
+        <v>10593.8</v>
       </c>
       <c r="K61" t="n">
-        <v>10665.4</v>
+        <v>10642.9</v>
       </c>
       <c r="L61" t="n">
-        <v>10713.95</v>
+        <v>10692</v>
       </c>
       <c r="M61" t="n">
-        <v>10745.2</v>
+        <v>10717.1</v>
       </c>
       <c r="N61" t="n">
-        <v>10776.45</v>
+        <v>10742.2</v>
       </c>
       <c r="O61" t="n">
-        <v>10842.3</v>
+        <v>10815.3</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5611,21 +5605,23 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5635,55 +5631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10679.9</v>
+        <v>10695.2</v>
       </c>
       <c r="C62" t="n">
-        <v>10753.4</v>
+        <v>10758.7</v>
       </c>
       <c r="D62" t="n">
-        <v>10667</v>
+        <v>10684.9</v>
       </c>
       <c r="E62" t="n">
-        <v>10695.3</v>
+        <v>10684.9</v>
       </c>
       <c r="F62" t="n">
-        <v>15.3</v>
+        <v>-10.4</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.001</v>
       </c>
       <c r="H62" t="n">
-        <v>86.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="I62" t="n">
-        <v>10592.7</v>
+        <v>10580.6</v>
       </c>
       <c r="J62" t="n">
-        <v>10593.8</v>
+        <v>10601.45</v>
       </c>
       <c r="K62" t="n">
-        <v>10642.9</v>
+        <v>10652.1</v>
       </c>
       <c r="L62" t="n">
-        <v>10692</v>
+        <v>10702.75</v>
       </c>
       <c r="M62" t="n">
-        <v>10717.1</v>
+        <v>10738.5</v>
       </c>
       <c r="N62" t="n">
-        <v>10742.2</v>
+        <v>10774.25</v>
       </c>
       <c r="O62" t="n">
-        <v>10815.3</v>
+        <v>10839.8</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5694,9 +5694,9 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5704,10 +5704,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5719,57 +5717,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10695.2</v>
+        <v>10685.2</v>
       </c>
       <c r="C63" t="n">
-        <v>10758.7</v>
+        <v>10756.2</v>
       </c>
       <c r="D63" t="n">
-        <v>10684.9</v>
+        <v>10622</v>
       </c>
       <c r="E63" t="n">
-        <v>10684.9</v>
+        <v>10636.7</v>
       </c>
       <c r="F63" t="n">
-        <v>-10.4</v>
+        <v>-48.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0045</v>
       </c>
       <c r="H63" t="n">
-        <v>73.8</v>
+        <v>134.2</v>
       </c>
       <c r="I63" t="n">
-        <v>10580.6</v>
+        <v>10611.1</v>
       </c>
       <c r="J63" t="n">
-        <v>10601.45</v>
+        <v>10592.65</v>
       </c>
       <c r="K63" t="n">
-        <v>10652.1</v>
+        <v>10648</v>
       </c>
       <c r="L63" t="n">
-        <v>10702.75</v>
+        <v>10703.35</v>
       </c>
       <c r="M63" t="n">
-        <v>10738.5</v>
+        <v>10721.8</v>
       </c>
       <c r="N63" t="n">
-        <v>10774.25</v>
+        <v>10740.25</v>
       </c>
       <c r="O63" t="n">
-        <v>10839.8</v>
+        <v>10832.5</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5777,12 +5775,14 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
@@ -5790,8 +5790,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5801,59 +5803,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10685.19</v>
+        <v>10635.82</v>
       </c>
       <c r="C64" t="n">
-        <v>10756.15</v>
+        <v>10725.31</v>
       </c>
       <c r="D64" t="n">
-        <v>10622</v>
+        <v>10599.21</v>
       </c>
       <c r="E64" t="n">
-        <v>10636.71</v>
+        <v>10606</v>
       </c>
       <c r="F64" t="n">
-        <v>-48.19</v>
+        <v>-30.7</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0029</v>
       </c>
       <c r="H64" t="n">
-        <v>134.15</v>
+        <v>126.1</v>
       </c>
       <c r="I64" t="n">
-        <v>10611.1</v>
+        <v>10487.8</v>
       </c>
       <c r="J64" t="n">
-        <v>10592.65</v>
+        <v>10476.3</v>
       </c>
       <c r="K64" t="n">
-        <v>10648</v>
+        <v>10569.6</v>
       </c>
       <c r="L64" t="n">
-        <v>10703.35</v>
+        <v>10662.9</v>
       </c>
       <c r="M64" t="n">
-        <v>10721.8</v>
+        <v>10703.8</v>
       </c>
       <c r="N64" t="n">
-        <v>10740.25</v>
+        <v>10744.7</v>
       </c>
       <c r="O64" t="n">
-        <v>10832.5</v>
+        <v>10890.4</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5876,10 +5874,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U64" s="8" t="n">
+        <v/>
       </c>
       <c r="V64" s="8" t="n">
         <v/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10652.8</v>
+        <v>10679.4</v>
       </c>
       <c r="C2" t="n">
-        <v>10701.3</v>
+        <v>10733.4</v>
       </c>
       <c r="D2" t="n">
-        <v>10604.3</v>
+        <v>10618.4</v>
       </c>
       <c r="E2" t="n">
-        <v>10679</v>
+        <v>10651.8</v>
       </c>
       <c r="F2" t="n">
-        <v>26.1</v>
+        <v>-27.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I2" t="n">
-        <v>10178.7</v>
+        <v>10507.3</v>
       </c>
       <c r="J2" t="n">
-        <v>10438.32</v>
+        <v>10595.1</v>
       </c>
       <c r="K2" t="n">
-        <v>10523.85</v>
+        <v>10630.5</v>
       </c>
       <c r="L2" t="n">
-        <v>10609.38</v>
+        <v>10665.9</v>
       </c>
       <c r="M2" t="n">
-        <v>10781.95</v>
+        <v>10727.5</v>
       </c>
       <c r="N2" t="n">
-        <v>10954.53</v>
+        <v>10789.1</v>
       </c>
       <c r="O2" t="n">
-        <v>10953</v>
+        <v>10798.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +685,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -707,55 +711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C3" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D3" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E3" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H3" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I3" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J3" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K3" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L3" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M3" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N3" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O3" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -763,21 +771,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -789,78 +795,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C4" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D4" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E4" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F4" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H4" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I4" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J4" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K4" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L4" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M4" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N4" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O4" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -868,9 +874,9 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -878,69 +884,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C5" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D5" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E5" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H5" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I5" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J5" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K5" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L5" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M5" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N5" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O5" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -962,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C6" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D6" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E6" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H6" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I6" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J6" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K6" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L6" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M6" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N6" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O6" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1035,55 +1035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C7" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D7" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E7" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F7" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H7" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J7" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K7" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L7" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M7" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N7" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O7" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1091,16 +1095,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1115,77 +1123,79 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C8" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D8" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E8" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H8" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I8" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J8" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K8" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L8" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M8" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N8" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O8" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1201,80 +1211,76 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C9" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D9" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E9" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F9" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H9" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J9" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K9" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L9" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M9" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N9" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O9" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1289,57 +1295,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C10" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D10" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E10" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F10" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H10" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J10" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K10" t="n">
         <v>10464.6</v>
       </c>
       <c r="L10" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M10" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N10" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O10" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,13 +1358,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,57 +1381,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C11" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D11" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E11" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F11" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H11" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J11" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K11" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L11" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M11" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N11" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O11" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1431,12 +1439,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1466,69 +1472,71 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C12" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D12" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E12" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F12" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I12" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J12" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K12" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L12" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M12" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N12" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O12" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,84 +1549,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C13" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D13" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E13" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H13" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I13" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J13" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K13" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L13" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M13" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N13" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O13" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1627,55 +1631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C14" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D14" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E14" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F14" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H14" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I14" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J14" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K14" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L14" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M14" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N14" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O14" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,7 +1694,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1701,67 +1709,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C15" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D15" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E15" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F15" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H15" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I15" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J15" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K15" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L15" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M15" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N15" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O15" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,83 +1775,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C16" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D16" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E16" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H16" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I16" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J16" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K16" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L16" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M16" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N16" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O16" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,22 +1859,24 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1879,57 +1887,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C17" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D17" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E17" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H17" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I17" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J17" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K17" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L17" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M17" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N17" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O17" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,21 +1948,19 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1963,59 +1969,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C18" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D18" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E18" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F18" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H18" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I18" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J18" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K18" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L18" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M18" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N18" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O18" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,18 +2028,20 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2052,50 +2056,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C19" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D19" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E19" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F19" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H19" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I19" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J19" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K19" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L19" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M19" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N19" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O19" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,20 +2110,18 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2134,50 +2136,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C20" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D20" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E20" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F20" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I20" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J20" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K20" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L20" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M20" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N20" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O20" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,12 +2192,12 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2209,55 +2211,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C21" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D21" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E21" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H21" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I21" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J21" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K21" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L21" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M21" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N21" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O21" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,12 +2271,14 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2291,57 +2299,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C22" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D22" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E22" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F22" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J22" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K22" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L22" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M22" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N22" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O22" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,20 +2357,16 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2384,50 +2388,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C23" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D23" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E23" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H23" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I23" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J23" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K23" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L23" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M23" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N23" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O23" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,11 +2444,13 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2457,59 +2463,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C24" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D24" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E24" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F24" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H24" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I24" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J24" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K24" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L24" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M24" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N24" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O24" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2517,10 +2519,12 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2530,8 +2534,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2541,55 +2547,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C25" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D25" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E25" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F25" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H25" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I25" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J25" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K25" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L25" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M25" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N25" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O25" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2597,25 +2607,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2627,57 +2631,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C26" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D26" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E26" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H26" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I26" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J26" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K26" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L26" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M26" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N26" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O26" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2690,14 +2694,18 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2709,57 +2717,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C27" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D27" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E27" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F27" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H27" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J27" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K27" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L27" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M27" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N27" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O27" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,23 +2775,21 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2795,57 +2801,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C28" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D28" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E28" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H28" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I28" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J28" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K28" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L28" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M28" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N28" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O28" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,14 +2859,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2886,50 +2890,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C29" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D29" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E29" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I29" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J29" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K29" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L29" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M29" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N29" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O29" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2937,10 +2941,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2968,65 +2974,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C30" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D30" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E30" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H30" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J30" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K30" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L30" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M30" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N30" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O30" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3038,79 +3046,73 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D31" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E31" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H31" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I31" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J31" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K31" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L31" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M31" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N31" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O31" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3134,50 +3136,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C32" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D32" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E32" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F32" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H32" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I32" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J32" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K32" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L32" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M32" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N32" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O32" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3190,13 +3192,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3209,55 +3213,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C33" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D33" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E33" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F33" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H33" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I33" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J33" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K33" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L33" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M33" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N33" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O33" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3265,14 +3273,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3280,8 +3286,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3300,50 +3308,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C34" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D34" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E34" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F34" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H34" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J34" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K34" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L34" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M34" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N34" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O34" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3356,18 +3364,14 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3386,50 +3390,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C35" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D35" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E35" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F35" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H35" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I35" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J35" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K35" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L35" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M35" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N35" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O35" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3437,10 +3441,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3461,57 +3467,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C36" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D36" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E36" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F36" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H36" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I36" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J36" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K36" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L36" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M36" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N36" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O36" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3519,21 +3525,23 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3545,57 +3553,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C37" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D37" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E37" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F37" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H37" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I37" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J37" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K37" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L37" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M37" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N37" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O37" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3606,20 +3614,18 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3638,50 +3644,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C38" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D38" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E38" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F38" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H38" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I38" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J38" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K38" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L38" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M38" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N38" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O38" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3692,7 +3698,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3722,50 +3728,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C39" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D39" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E39" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F39" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J39" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K39" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L39" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M39" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N39" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O39" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,17 +3779,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3799,63 +3807,67 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10886.2</v>
+        <v>10878.2</v>
       </c>
       <c r="C40" t="n">
-        <v>10920.5</v>
+        <v>10878.5</v>
       </c>
       <c r="D40" t="n">
-        <v>10855.6</v>
+        <v>10772.6</v>
       </c>
       <c r="E40" t="n">
-        <v>10878.1</v>
+        <v>10792.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-8.1</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>64.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="I40" t="n">
-        <v>10764.6</v>
+        <v>10790.7</v>
       </c>
       <c r="J40" t="n">
-        <v>10839.9</v>
+        <v>10808.22</v>
       </c>
       <c r="K40" t="n">
-        <v>10855.6</v>
+        <v>10845.65</v>
       </c>
       <c r="L40" t="n">
-        <v>10871.3</v>
+        <v>10883.07</v>
       </c>
       <c r="M40" t="n">
-        <v>10916.8</v>
+        <v>10910.55</v>
       </c>
       <c r="N40" t="n">
-        <v>10962.3</v>
+        <v>10938.02</v>
       </c>
       <c r="O40" t="n">
-        <v>10948.2</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>10985.4</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3864,13 +3876,11 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3883,78 +3893,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10878.2</v>
+        <v>10792.5</v>
       </c>
       <c r="C41" t="n">
-        <v>10878.5</v>
+        <v>10845</v>
       </c>
       <c r="D41" t="n">
-        <v>10772.6</v>
+        <v>10792.4</v>
       </c>
       <c r="E41" t="n">
-        <v>10792.5</v>
+        <v>10824.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-85.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0029</v>
       </c>
       <c r="H41" t="n">
-        <v>105.9</v>
+        <v>52.6</v>
       </c>
       <c r="I41" t="n">
-        <v>10790.7</v>
+        <v>10666.7</v>
       </c>
       <c r="J41" t="n">
-        <v>10808.22</v>
+        <v>10670.07</v>
       </c>
       <c r="K41" t="n">
-        <v>10845.65</v>
+        <v>10739.55</v>
       </c>
       <c r="L41" t="n">
-        <v>10883.07</v>
+        <v>10809.02</v>
       </c>
       <c r="M41" t="n">
-        <v>10910.55</v>
+        <v>10845.45</v>
       </c>
       <c r="N41" t="n">
-        <v>10938.02</v>
+        <v>10881.88</v>
       </c>
       <c r="O41" t="n">
-        <v>10985.4</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>10984.4</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3971,68 +3971,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10792.5</v>
+        <v>10824.6</v>
       </c>
       <c r="C42" t="n">
-        <v>10845</v>
+        <v>10829.2</v>
       </c>
       <c r="D42" t="n">
-        <v>10792.4</v>
+        <v>10689.6</v>
       </c>
       <c r="E42" t="n">
-        <v>10824.3</v>
+        <v>10789.3</v>
       </c>
       <c r="F42" t="n">
-        <v>31.8</v>
+        <v>-35</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0032</v>
       </c>
       <c r="H42" t="n">
-        <v>52.6</v>
+        <v>139.6</v>
       </c>
       <c r="I42" t="n">
-        <v>10666.7</v>
+        <v>10739.8</v>
       </c>
       <c r="J42" t="n">
-        <v>10670.07</v>
+        <v>10774.5</v>
       </c>
       <c r="K42" t="n">
-        <v>10739.55</v>
+        <v>10798</v>
       </c>
       <c r="L42" t="n">
-        <v>10809.02</v>
+        <v>10821.5</v>
       </c>
       <c r="M42" t="n">
-        <v>10845.45</v>
+        <v>10850.6</v>
       </c>
       <c r="N42" t="n">
-        <v>10881.88</v>
+        <v>10879.7</v>
       </c>
       <c r="O42" t="n">
-        <v>10984.4</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>10897.6</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4049,78 +4059,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10824.6</v>
+        <v>10789.9</v>
       </c>
       <c r="C43" t="n">
-        <v>10829.2</v>
+        <v>10800.8</v>
       </c>
       <c r="D43" t="n">
-        <v>10689.6</v>
+        <v>10713.1</v>
       </c>
       <c r="E43" t="n">
-        <v>10789.3</v>
+        <v>10756.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-35</v>
+        <v>-32.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.003</v>
       </c>
       <c r="H43" t="n">
-        <v>139.6</v>
+        <v>87.7</v>
       </c>
       <c r="I43" t="n">
-        <v>10739.8</v>
+        <v>10550</v>
       </c>
       <c r="J43" t="n">
-        <v>10774.5</v>
+        <v>10664.65</v>
       </c>
       <c r="K43" t="n">
-        <v>10798</v>
+        <v>10719.5</v>
       </c>
       <c r="L43" t="n">
-        <v>10821.5</v>
+        <v>10774.35</v>
       </c>
       <c r="M43" t="n">
-        <v>10850.6</v>
+        <v>10859.1</v>
       </c>
       <c r="N43" t="n">
-        <v>10879.7</v>
+        <v>10943.85</v>
       </c>
       <c r="O43" t="n">
-        <v>10897.6</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>10968.8</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4137,55 +4139,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10789.9</v>
+        <v>10756.8</v>
       </c>
       <c r="C44" t="n">
-        <v>10800.8</v>
+        <v>10866.8</v>
       </c>
       <c r="D44" t="n">
-        <v>10713.1</v>
+        <v>10742.7</v>
       </c>
       <c r="E44" t="n">
-        <v>10756.5</v>
+        <v>10831.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-32.8</v>
+        <v>75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H44" t="n">
-        <v>87.7</v>
+        <v>124.1</v>
       </c>
       <c r="I44" t="n">
-        <v>10550</v>
+        <v>10625.4</v>
       </c>
       <c r="J44" t="n">
-        <v>10664.65</v>
+        <v>10668.57</v>
       </c>
       <c r="K44" t="n">
-        <v>10719.5</v>
+        <v>10712.65</v>
       </c>
       <c r="L44" t="n">
-        <v>10774.35</v>
+        <v>10756.72</v>
       </c>
       <c r="M44" t="n">
-        <v>10859.1</v>
+        <v>10800.35</v>
       </c>
       <c r="N44" t="n">
-        <v>10943.85</v>
+        <v>10843.98</v>
       </c>
       <c r="O44" t="n">
-        <v>10968.8</v>
+        <v>10888.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4193,21 +4199,23 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4219,57 +4227,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10756.8</v>
+        <v>10831.5</v>
       </c>
       <c r="C45" t="n">
-        <v>10866.8</v>
+        <v>10843.1</v>
       </c>
       <c r="D45" t="n">
-        <v>10742.7</v>
+        <v>10791.4</v>
       </c>
       <c r="E45" t="n">
-        <v>10831.5</v>
+        <v>10831.1</v>
       </c>
       <c r="F45" t="n">
-        <v>75</v>
+        <v>-0.4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.007</v>
+        <v>-0</v>
       </c>
       <c r="H45" t="n">
-        <v>124.1</v>
+        <v>51.7</v>
       </c>
       <c r="I45" t="n">
-        <v>10625.4</v>
+        <v>10618.6</v>
       </c>
       <c r="J45" t="n">
-        <v>10668.57</v>
+        <v>10720.78</v>
       </c>
       <c r="K45" t="n">
-        <v>10712.65</v>
+        <v>10769.45</v>
       </c>
       <c r="L45" t="n">
-        <v>10756.72</v>
+        <v>10818.12</v>
       </c>
       <c r="M45" t="n">
-        <v>10800.35</v>
+        <v>10893.55</v>
       </c>
       <c r="N45" t="n">
-        <v>10843.98</v>
+        <v>10968.97</v>
       </c>
       <c r="O45" t="n">
-        <v>10888.5</v>
+        <v>10990.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4280,20 +4288,16 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4305,57 +4309,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10831.5</v>
+        <v>10831</v>
       </c>
       <c r="C46" t="n">
-        <v>10843.1</v>
+        <v>10868.3</v>
       </c>
       <c r="D46" t="n">
-        <v>10791.4</v>
+        <v>10794.2</v>
       </c>
       <c r="E46" t="n">
-        <v>10831.1</v>
+        <v>10822.1</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.4</v>
+        <v>-9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H46" t="n">
-        <v>51.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>10618.6</v>
+        <v>10739.7</v>
       </c>
       <c r="J46" t="n">
-        <v>10720.78</v>
+        <v>10786.33</v>
       </c>
       <c r="K46" t="n">
-        <v>10769.45</v>
+        <v>10805.25</v>
       </c>
       <c r="L46" t="n">
-        <v>10818.12</v>
+        <v>10824.17</v>
       </c>
       <c r="M46" t="n">
-        <v>10893.55</v>
+        <v>10856.95</v>
       </c>
       <c r="N46" t="n">
-        <v>10968.97</v>
+        <v>10889.72</v>
       </c>
       <c r="O46" t="n">
-        <v>10990.9</v>
+        <v>10894.8</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4363,16 +4367,20 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4387,57 +4395,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10831</v>
+        <v>10822.3</v>
       </c>
       <c r="C47" t="n">
-        <v>10868.3</v>
+        <v>10850.7</v>
       </c>
       <c r="D47" t="n">
-        <v>10794.2</v>
+        <v>10778.1</v>
       </c>
       <c r="E47" t="n">
-        <v>10822.1</v>
+        <v>10811.7</v>
       </c>
       <c r="F47" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>10739.7</v>
+        <v>10720.1</v>
       </c>
       <c r="J47" t="n">
-        <v>10786.33</v>
+        <v>10743.42</v>
       </c>
       <c r="K47" t="n">
-        <v>10805.25</v>
+        <v>10785.05</v>
       </c>
       <c r="L47" t="n">
-        <v>10824.17</v>
+        <v>10826.67</v>
       </c>
       <c r="M47" t="n">
-        <v>10856.95</v>
+        <v>10859.15</v>
       </c>
       <c r="N47" t="n">
-        <v>10889.72</v>
+        <v>10891.62</v>
       </c>
       <c r="O47" t="n">
-        <v>10894.8</v>
+        <v>10942.4</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4450,15 +4458,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4471,74 +4477,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10822.3</v>
+        <v>10811.4</v>
       </c>
       <c r="C48" t="n">
-        <v>10850.7</v>
+        <v>10811.6</v>
       </c>
       <c r="D48" t="n">
-        <v>10778.1</v>
+        <v>10651.7</v>
       </c>
       <c r="E48" t="n">
-        <v>10811.7</v>
+        <v>10670.1</v>
       </c>
       <c r="F48" t="n">
-        <v>-10.4</v>
+        <v>-141.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0131</v>
       </c>
       <c r="H48" t="n">
-        <v>72.59999999999999</v>
+        <v>159.9</v>
       </c>
       <c r="I48" t="n">
-        <v>10720.1</v>
+        <v>10705.5</v>
       </c>
       <c r="J48" t="n">
-        <v>10743.42</v>
+        <v>10737.75</v>
       </c>
       <c r="K48" t="n">
-        <v>10785.05</v>
+        <v>10775.4</v>
       </c>
       <c r="L48" t="n">
-        <v>10826.67</v>
+        <v>10813.05</v>
       </c>
       <c r="M48" t="n">
-        <v>10859.15</v>
+        <v>10848</v>
       </c>
       <c r="N48" t="n">
-        <v>10891.62</v>
+        <v>10882.95</v>
       </c>
       <c r="O48" t="n">
-        <v>10942.4</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>10923.3</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4560,67 +4566,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10811.4</v>
+        <v>10669.9</v>
       </c>
       <c r="C49" t="n">
-        <v>10811.6</v>
+        <v>10688</v>
       </c>
       <c r="D49" t="n">
-        <v>10651.7</v>
+        <v>10594.3</v>
       </c>
       <c r="E49" t="n">
-        <v>10670.1</v>
+        <v>10608.9</v>
       </c>
       <c r="F49" t="n">
-        <v>-141.6</v>
+        <v>-61.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0057</v>
       </c>
       <c r="H49" t="n">
-        <v>159.9</v>
+        <v>93.7</v>
       </c>
       <c r="I49" t="n">
-        <v>10705.5</v>
+        <v>10491.8</v>
       </c>
       <c r="J49" t="n">
-        <v>10737.75</v>
+        <v>10479.43</v>
       </c>
       <c r="K49" t="n">
-        <v>10775.4</v>
+        <v>10590.15</v>
       </c>
       <c r="L49" t="n">
-        <v>10813.05</v>
+        <v>10700.87</v>
       </c>
       <c r="M49" t="n">
-        <v>10848</v>
+        <v>10750.05</v>
       </c>
       <c r="N49" t="n">
-        <v>10882.95</v>
+        <v>10799.22</v>
       </c>
       <c r="O49" t="n">
-        <v>10923.3</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>10971.5</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4644,50 +4646,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10669.9</v>
+        <v>10609</v>
       </c>
       <c r="C50" t="n">
-        <v>10688</v>
+        <v>10714.7</v>
       </c>
       <c r="D50" t="n">
-        <v>10594.3</v>
+        <v>10602.1</v>
       </c>
       <c r="E50" t="n">
-        <v>10608.9</v>
+        <v>10650.4</v>
       </c>
       <c r="F50" t="n">
-        <v>-61.2</v>
+        <v>41.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0039</v>
       </c>
       <c r="H50" t="n">
-        <v>93.7</v>
+        <v>112.6</v>
       </c>
       <c r="I50" t="n">
-        <v>10491.8</v>
+        <v>10500.6</v>
       </c>
       <c r="J50" t="n">
-        <v>10479.43</v>
+        <v>10499.08</v>
       </c>
       <c r="K50" t="n">
-        <v>10590.15</v>
+        <v>10562.05</v>
       </c>
       <c r="L50" t="n">
-        <v>10700.87</v>
+        <v>10625.03</v>
       </c>
       <c r="M50" t="n">
-        <v>10750.05</v>
+        <v>10655.75</v>
       </c>
       <c r="N50" t="n">
-        <v>10799.22</v>
+        <v>10686.48</v>
       </c>
       <c r="O50" t="n">
-        <v>10971.5</v>
+        <v>10781.7</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,21 +4697,23 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4719,55 +4723,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10609</v>
+        <v>10650.9</v>
       </c>
       <c r="C51" t="n">
-        <v>10714.7</v>
+        <v>10734.9</v>
       </c>
       <c r="D51" t="n">
-        <v>10602.1</v>
+        <v>10650.9</v>
       </c>
       <c r="E51" t="n">
-        <v>10650.4</v>
+        <v>10697.6</v>
       </c>
       <c r="F51" t="n">
-        <v>41.5</v>
+        <v>47.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0044</v>
       </c>
       <c r="H51" t="n">
-        <v>112.6</v>
+        <v>84</v>
       </c>
       <c r="I51" t="n">
-        <v>10500.6</v>
+        <v>10489.5</v>
       </c>
       <c r="J51" t="n">
-        <v>10499.08</v>
+        <v>10533.8</v>
       </c>
       <c r="K51" t="n">
-        <v>10562.05</v>
+        <v>10594.1</v>
       </c>
       <c r="L51" t="n">
-        <v>10625.03</v>
+        <v>10654.4</v>
       </c>
       <c r="M51" t="n">
-        <v>10655.75</v>
+        <v>10706.7</v>
       </c>
       <c r="N51" t="n">
-        <v>10686.48</v>
+        <v>10759</v>
       </c>
       <c r="O51" t="n">
-        <v>10781.7</v>
+        <v>10827.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4778,7 +4786,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4788,10 +4796,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4810,69 +4816,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10650.9</v>
+        <v>10697.8</v>
       </c>
       <c r="C52" t="n">
-        <v>10734.9</v>
+        <v>10697.8</v>
       </c>
       <c r="D52" t="n">
-        <v>10650.9</v>
+        <v>10586.4</v>
       </c>
       <c r="E52" t="n">
-        <v>10697.6</v>
+        <v>10658.1</v>
       </c>
       <c r="F52" t="n">
-        <v>47.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0037</v>
       </c>
       <c r="H52" t="n">
-        <v>84</v>
+        <v>111.4</v>
       </c>
       <c r="I52" t="n">
-        <v>10489.5</v>
+        <v>10566.9</v>
       </c>
       <c r="J52" t="n">
-        <v>10533.8</v>
+        <v>10615.95</v>
       </c>
       <c r="K52" t="n">
-        <v>10594.1</v>
+        <v>10655.6</v>
       </c>
       <c r="L52" t="n">
-        <v>10654.4</v>
+        <v>10695.25</v>
       </c>
       <c r="M52" t="n">
-        <v>10706.7</v>
+        <v>10739.6</v>
       </c>
       <c r="N52" t="n">
-        <v>10759</v>
+        <v>10783.95</v>
       </c>
       <c r="O52" t="n">
-        <v>10827.3</v>
+        <v>10818.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4885,81 +4893,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10697.8</v>
+        <v>10658.2</v>
       </c>
       <c r="C53" t="n">
-        <v>10697.8</v>
+        <v>10735.3</v>
       </c>
       <c r="D53" t="n">
-        <v>10586.4</v>
+        <v>10655.8</v>
       </c>
       <c r="E53" t="n">
-        <v>10658.1</v>
+        <v>10688.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-39.5</v>
+        <v>30.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0029</v>
       </c>
       <c r="H53" t="n">
-        <v>111.4</v>
+        <v>79.5</v>
       </c>
       <c r="I53" t="n">
-        <v>10566.9</v>
+        <v>10475</v>
       </c>
       <c r="J53" t="n">
-        <v>10615.95</v>
+        <v>10554.7</v>
       </c>
       <c r="K53" t="n">
-        <v>10655.6</v>
+        <v>10602.4</v>
       </c>
       <c r="L53" t="n">
-        <v>10695.25</v>
+        <v>10650.1</v>
       </c>
       <c r="M53" t="n">
-        <v>10739.6</v>
+        <v>10713.8</v>
       </c>
       <c r="N53" t="n">
-        <v>10783.95</v>
+        <v>10777.5</v>
       </c>
       <c r="O53" t="n">
-        <v>10818.9</v>
+        <v>10809.2</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4971,55 +4973,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10658.2</v>
+        <v>10689.3</v>
       </c>
       <c r="C54" t="n">
-        <v>10735.3</v>
+        <v>10823</v>
       </c>
       <c r="D54" t="n">
-        <v>10655.8</v>
+        <v>10688.9</v>
       </c>
       <c r="E54" t="n">
-        <v>10688.5</v>
+        <v>10816.1</v>
       </c>
       <c r="F54" t="n">
-        <v>30.4</v>
+        <v>127.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0119</v>
       </c>
       <c r="H54" t="n">
-        <v>79.5</v>
+        <v>134.1</v>
       </c>
       <c r="I54" t="n">
-        <v>10475</v>
+        <v>10576.3</v>
       </c>
       <c r="J54" t="n">
-        <v>10554.7</v>
+        <v>10605.48</v>
       </c>
       <c r="K54" t="n">
-        <v>10602.4</v>
+        <v>10648.75</v>
       </c>
       <c r="L54" t="n">
-        <v>10650.1</v>
+        <v>10692.02</v>
       </c>
       <c r="M54" t="n">
-        <v>10713.8</v>
+        <v>10728.25</v>
       </c>
       <c r="N54" t="n">
-        <v>10777.5</v>
+        <v>10764.48</v>
       </c>
       <c r="O54" t="n">
-        <v>10809.2</v>
+        <v>10814.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5030,113 +5036,111 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10689.3</v>
+        <v>10815.8</v>
       </c>
       <c r="C55" t="n">
-        <v>10823</v>
+        <v>10815.9</v>
       </c>
       <c r="D55" t="n">
-        <v>10688.9</v>
+        <v>10650.2</v>
       </c>
       <c r="E55" t="n">
-        <v>10816.1</v>
+        <v>10659.1</v>
       </c>
       <c r="F55" t="n">
-        <v>127.6</v>
+        <v>-157</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0119</v>
+        <v>-0.0145</v>
       </c>
       <c r="H55" t="n">
-        <v>134.1</v>
+        <v>165.7</v>
       </c>
       <c r="I55" t="n">
-        <v>10576.3</v>
+        <v>10554.8</v>
       </c>
       <c r="J55" t="n">
-        <v>10605.48</v>
+        <v>10712.07</v>
       </c>
       <c r="K55" t="n">
-        <v>10648.75</v>
+        <v>10749.05</v>
       </c>
       <c r="L55" t="n">
-        <v>10692.02</v>
+        <v>10786.02</v>
       </c>
       <c r="M55" t="n">
-        <v>10728.25</v>
+        <v>10883.15</v>
       </c>
       <c r="N55" t="n">
-        <v>10764.48</v>
+        <v>10980.27</v>
       </c>
       <c r="O55" t="n">
-        <v>10814.8</v>
+        <v>10957.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5144,72 +5148,70 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10815.8</v>
+        <v>10659.1</v>
       </c>
       <c r="C56" t="n">
-        <v>10815.9</v>
+        <v>10774.7</v>
       </c>
       <c r="D56" t="n">
-        <v>10650.2</v>
+        <v>10656.7</v>
       </c>
       <c r="E56" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="F56" t="n">
-        <v>-157</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0075</v>
       </c>
       <c r="H56" t="n">
-        <v>165.7</v>
+        <v>118</v>
       </c>
       <c r="I56" t="n">
-        <v>10554.8</v>
+        <v>10484.5</v>
       </c>
       <c r="J56" t="n">
-        <v>10712.07</v>
+        <v>10456.42</v>
       </c>
       <c r="K56" t="n">
-        <v>10749.05</v>
+        <v>10576.25</v>
       </c>
       <c r="L56" t="n">
-        <v>10786.02</v>
+        <v>10696.07</v>
       </c>
       <c r="M56" t="n">
-        <v>10883.15</v>
+        <v>10741.95</v>
       </c>
       <c r="N56" t="n">
-        <v>10980.27</v>
+        <v>10787.82</v>
       </c>
       <c r="O56" t="n">
-        <v>10957.1</v>
+        <v>10981.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5221,55 +5223,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10659.1</v>
+        <v>10739</v>
       </c>
       <c r="C57" t="n">
-        <v>10774.7</v>
+        <v>10771.6</v>
       </c>
       <c r="D57" t="n">
-        <v>10656.7</v>
+        <v>10708.3</v>
       </c>
       <c r="E57" t="n">
-        <v>10739</v>
+        <v>10708.3</v>
       </c>
       <c r="F57" t="n">
-        <v>79.90000000000001</v>
+        <v>-30.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0029</v>
       </c>
       <c r="H57" t="n">
-        <v>118</v>
+        <v>63.3</v>
       </c>
       <c r="I57" t="n">
-        <v>10484.5</v>
+        <v>10538.7</v>
       </c>
       <c r="J57" t="n">
-        <v>10456.42</v>
+        <v>10632.65</v>
       </c>
       <c r="K57" t="n">
-        <v>10576.25</v>
+        <v>10680</v>
       </c>
       <c r="L57" t="n">
-        <v>10696.07</v>
+        <v>10727.35</v>
       </c>
       <c r="M57" t="n">
-        <v>10741.95</v>
+        <v>10798</v>
       </c>
       <c r="N57" t="n">
-        <v>10787.82</v>
+        <v>10868.65</v>
       </c>
       <c r="O57" t="n">
-        <v>10981.6</v>
+        <v>10892.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5282,13 +5288,11 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5303,57 +5307,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10739</v>
+        <v>10708.8</v>
       </c>
       <c r="C58" t="n">
-        <v>10771.6</v>
+        <v>10762.5</v>
       </c>
       <c r="D58" t="n">
-        <v>10708.3</v>
+        <v>10682.7</v>
       </c>
       <c r="E58" t="n">
-        <v>10708.3</v>
+        <v>10705.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-30.7</v>
+        <v>-3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0003</v>
       </c>
       <c r="H58" t="n">
-        <v>63.3</v>
+        <v>79.8</v>
       </c>
       <c r="I58" t="n">
-        <v>10538.7</v>
+        <v>10645</v>
       </c>
       <c r="J58" t="n">
-        <v>10632.65</v>
+        <v>10629.18</v>
       </c>
       <c r="K58" t="n">
-        <v>10680</v>
+        <v>10676.65</v>
       </c>
       <c r="L58" t="n">
-        <v>10727.35</v>
+        <v>10724.12</v>
       </c>
       <c r="M58" t="n">
-        <v>10798</v>
+        <v>10739.95</v>
       </c>
       <c r="N58" t="n">
-        <v>10868.65</v>
+        <v>10755.77</v>
       </c>
       <c r="O58" t="n">
-        <v>10892.7</v>
+        <v>10834.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5364,16 +5368,20 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5383,59 +5391,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10708.8</v>
+        <v>10705.5</v>
       </c>
       <c r="C59" t="n">
-        <v>10762.5</v>
+        <v>10741.1</v>
       </c>
       <c r="D59" t="n">
-        <v>10682.7</v>
+        <v>10666.9</v>
       </c>
       <c r="E59" t="n">
-        <v>10705.3</v>
+        <v>10680</v>
       </c>
       <c r="F59" t="n">
-        <v>-3</v>
+        <v>-25.3</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0024</v>
       </c>
       <c r="H59" t="n">
-        <v>79.8</v>
+        <v>74.2</v>
       </c>
       <c r="I59" t="n">
-        <v>10645</v>
+        <v>10602.9</v>
       </c>
       <c r="J59" t="n">
-        <v>10629.18</v>
+        <v>10616.85</v>
       </c>
       <c r="K59" t="n">
-        <v>10676.65</v>
+        <v>10665.4</v>
       </c>
       <c r="L59" t="n">
-        <v>10724.12</v>
+        <v>10713.95</v>
       </c>
       <c r="M59" t="n">
-        <v>10739.95</v>
+        <v>10745.2</v>
       </c>
       <c r="N59" t="n">
-        <v>10755.77</v>
+        <v>10776.45</v>
       </c>
       <c r="O59" t="n">
-        <v>10834.9</v>
+        <v>10842.3</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5443,23 +5447,21 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5474,50 +5476,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10705.5</v>
+        <v>10679.9</v>
       </c>
       <c r="C60" t="n">
-        <v>10741.1</v>
+        <v>10753.4</v>
       </c>
       <c r="D60" t="n">
-        <v>10666.9</v>
+        <v>10667</v>
       </c>
       <c r="E60" t="n">
-        <v>10680</v>
+        <v>10695.3</v>
       </c>
       <c r="F60" t="n">
-        <v>-25.3</v>
+        <v>15.3</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.0014</v>
       </c>
       <c r="H60" t="n">
-        <v>74.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>10602.9</v>
+        <v>10592.7</v>
       </c>
       <c r="J60" t="n">
-        <v>10616.85</v>
+        <v>10593.8</v>
       </c>
       <c r="K60" t="n">
-        <v>10665.4</v>
+        <v>10642.9</v>
       </c>
       <c r="L60" t="n">
-        <v>10713.95</v>
+        <v>10692</v>
       </c>
       <c r="M60" t="n">
-        <v>10745.2</v>
+        <v>10717.1</v>
       </c>
       <c r="N60" t="n">
-        <v>10776.45</v>
+        <v>10742.2</v>
       </c>
       <c r="O60" t="n">
-        <v>10842.3</v>
+        <v>10815.3</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5525,21 +5527,23 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5549,55 +5553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10679.9</v>
+        <v>10695.2</v>
       </c>
       <c r="C61" t="n">
-        <v>10753.4</v>
+        <v>10758.7</v>
       </c>
       <c r="D61" t="n">
-        <v>10667</v>
+        <v>10684.9</v>
       </c>
       <c r="E61" t="n">
-        <v>10695.3</v>
+        <v>10684.9</v>
       </c>
       <c r="F61" t="n">
-        <v>15.3</v>
+        <v>-10.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.001</v>
       </c>
       <c r="H61" t="n">
-        <v>86.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="I61" t="n">
-        <v>10592.7</v>
+        <v>10580.6</v>
       </c>
       <c r="J61" t="n">
-        <v>10593.8</v>
+        <v>10601.45</v>
       </c>
       <c r="K61" t="n">
-        <v>10642.9</v>
+        <v>10652.1</v>
       </c>
       <c r="L61" t="n">
-        <v>10692</v>
+        <v>10702.75</v>
       </c>
       <c r="M61" t="n">
-        <v>10717.1</v>
+        <v>10738.5</v>
       </c>
       <c r="N61" t="n">
-        <v>10742.2</v>
+        <v>10774.25</v>
       </c>
       <c r="O61" t="n">
-        <v>10815.3</v>
+        <v>10839.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5610,7 +5618,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5618,10 +5626,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5633,57 +5639,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10695.2</v>
+        <v>10685.2</v>
       </c>
       <c r="C62" t="n">
-        <v>10758.7</v>
+        <v>10756.2</v>
       </c>
       <c r="D62" t="n">
-        <v>10684.9</v>
+        <v>10622</v>
       </c>
       <c r="E62" t="n">
-        <v>10684.9</v>
+        <v>10636.7</v>
       </c>
       <c r="F62" t="n">
-        <v>-10.4</v>
+        <v>-48.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0045</v>
       </c>
       <c r="H62" t="n">
-        <v>73.8</v>
+        <v>134.2</v>
       </c>
       <c r="I62" t="n">
-        <v>10580.6</v>
+        <v>10611.1</v>
       </c>
       <c r="J62" t="n">
-        <v>10601.45</v>
+        <v>10592.65</v>
       </c>
       <c r="K62" t="n">
-        <v>10652.1</v>
+        <v>10648</v>
       </c>
       <c r="L62" t="n">
-        <v>10702.75</v>
+        <v>10703.35</v>
       </c>
       <c r="M62" t="n">
-        <v>10738.5</v>
+        <v>10721.8</v>
       </c>
       <c r="N62" t="n">
-        <v>10774.25</v>
+        <v>10740.25</v>
       </c>
       <c r="O62" t="n">
-        <v>10839.8</v>
+        <v>10832.5</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5691,12 +5697,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5704,8 +5712,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5715,59 +5725,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10685.2</v>
+        <v>10635.8</v>
       </c>
       <c r="C63" t="n">
-        <v>10756.2</v>
+        <v>10725.3</v>
       </c>
       <c r="D63" t="n">
-        <v>10622</v>
+        <v>10599.2</v>
       </c>
       <c r="E63" t="n">
-        <v>10636.7</v>
+        <v>10606</v>
       </c>
       <c r="F63" t="n">
-        <v>-48.2</v>
+        <v>-30.7</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0029</v>
       </c>
       <c r="H63" t="n">
-        <v>134.2</v>
+        <v>126.1</v>
       </c>
       <c r="I63" t="n">
-        <v>10611.1</v>
+        <v>10487.8</v>
       </c>
       <c r="J63" t="n">
-        <v>10592.65</v>
+        <v>10476.3</v>
       </c>
       <c r="K63" t="n">
-        <v>10648</v>
+        <v>10569.6</v>
       </c>
       <c r="L63" t="n">
-        <v>10703.35</v>
+        <v>10662.9</v>
       </c>
       <c r="M63" t="n">
-        <v>10721.8</v>
+        <v>10703.8</v>
       </c>
       <c r="N63" t="n">
-        <v>10740.25</v>
+        <v>10744.7</v>
       </c>
       <c r="O63" t="n">
-        <v>10832.5</v>
+        <v>10890.4</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5780,7 +5786,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5790,10 +5796,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5808,71 +5812,73 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10635.82</v>
+        <v>10606.39</v>
       </c>
       <c r="C64" t="n">
-        <v>10725.31</v>
+        <v>10606.39</v>
       </c>
       <c r="D64" t="n">
-        <v>10599.21</v>
+        <v>10390.73</v>
       </c>
       <c r="E64" t="n">
-        <v>10606</v>
+        <v>10428.27</v>
       </c>
       <c r="F64" t="n">
-        <v>-30.7</v>
+        <v>-177.73</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0168</v>
       </c>
       <c r="H64" t="n">
-        <v>126.1</v>
+        <v>215.66</v>
       </c>
       <c r="I64" t="n">
-        <v>10487.8</v>
+        <v>10473.1</v>
       </c>
       <c r="J64" t="n">
-        <v>10476.3</v>
+        <v>10451.78</v>
       </c>
       <c r="K64" t="n">
-        <v>10569.6</v>
+        <v>10542.95</v>
       </c>
       <c r="L64" t="n">
-        <v>10662.9</v>
+        <v>10634.12</v>
       </c>
       <c r="M64" t="n">
-        <v>10703.8</v>
+        <v>10669.05</v>
       </c>
       <c r="N64" t="n">
-        <v>10744.7</v>
+        <v>10703.97</v>
       </c>
       <c r="O64" t="n">
-        <v>10890.4</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
+        <v>10851.4</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>

--- a/three_gate/analysis/FTSE_daily.xlsx
+++ b/three_gate/analysis/FTSE_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10679.4</v>
+        <v>10651.3</v>
       </c>
       <c r="C2" t="n">
-        <v>10733.4</v>
+        <v>10747</v>
       </c>
       <c r="D2" t="n">
-        <v>10618.4</v>
+        <v>10651.2</v>
       </c>
       <c r="E2" t="n">
-        <v>10651.8</v>
+        <v>10665.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-27.2</v>
+        <v>14.1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="H2" t="n">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="I2" t="n">
-        <v>10507.3</v>
+        <v>10503.4</v>
       </c>
       <c r="J2" t="n">
-        <v>10595.1</v>
+        <v>10524.75</v>
       </c>
       <c r="K2" t="n">
-        <v>10630.5</v>
+        <v>10594.3</v>
       </c>
       <c r="L2" t="n">
-        <v>10665.9</v>
+        <v>10663.85</v>
       </c>
       <c r="M2" t="n">
-        <v>10727.5</v>
+        <v>10709.3</v>
       </c>
       <c r="N2" t="n">
-        <v>10789.1</v>
+        <v>10754.75</v>
       </c>
       <c r="O2" t="n">
-        <v>10798.3</v>
+        <v>10848.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,21 +685,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,78 +709,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10651.3</v>
+        <v>10666.1</v>
       </c>
       <c r="C3" t="n">
-        <v>10747</v>
+        <v>10666.1</v>
       </c>
       <c r="D3" t="n">
-        <v>10651.2</v>
+        <v>10467</v>
       </c>
       <c r="E3" t="n">
-        <v>10665.9</v>
+        <v>10489</v>
       </c>
       <c r="F3" t="n">
-        <v>14.1</v>
+        <v>-176.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0013</v>
+        <v>-0.0166</v>
       </c>
       <c r="H3" t="n">
-        <v>95.8</v>
+        <v>199.1</v>
       </c>
       <c r="I3" t="n">
-        <v>10503.4</v>
+        <v>10555.4</v>
       </c>
       <c r="J3" t="n">
-        <v>10524.75</v>
+        <v>10553.5</v>
       </c>
       <c r="K3" t="n">
-        <v>10594.3</v>
+        <v>10618</v>
       </c>
       <c r="L3" t="n">
-        <v>10663.85</v>
+        <v>10682.5</v>
       </c>
       <c r="M3" t="n">
-        <v>10709.3</v>
+        <v>10713.8</v>
       </c>
       <c r="N3" t="n">
-        <v>10754.75</v>
+        <v>10745.1</v>
       </c>
       <c r="O3" t="n">
-        <v>10848.4</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+        <v>10842.8</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -790,9 +788,9 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -800,69 +798,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10666.1</v>
+        <v>10487.9</v>
       </c>
       <c r="C4" t="n">
-        <v>10666.1</v>
+        <v>10539.5</v>
       </c>
       <c r="D4" t="n">
-        <v>10467</v>
+        <v>10397.5</v>
       </c>
       <c r="E4" t="n">
-        <v>10489</v>
+        <v>10472.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-176.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.0016</v>
       </c>
       <c r="H4" t="n">
-        <v>199.1</v>
+        <v>142</v>
       </c>
       <c r="I4" t="n">
-        <v>10555.4</v>
+        <v>10267.9</v>
       </c>
       <c r="J4" t="n">
-        <v>10553.5</v>
+        <v>10251.13</v>
       </c>
       <c r="K4" t="n">
-        <v>10618</v>
+        <v>10389.45</v>
       </c>
       <c r="L4" t="n">
-        <v>10682.5</v>
+        <v>10527.77</v>
       </c>
       <c r="M4" t="n">
-        <v>10713.8</v>
+        <v>10588.55</v>
       </c>
       <c r="N4" t="n">
-        <v>10745.1</v>
+        <v>10649.32</v>
       </c>
       <c r="O4" t="n">
-        <v>10842.8</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>10865.2</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -884,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10487.9</v>
+        <v>10471.9</v>
       </c>
       <c r="C5" t="n">
-        <v>10539.5</v>
+        <v>10513.9</v>
       </c>
       <c r="D5" t="n">
-        <v>10397.5</v>
+        <v>10462.8</v>
       </c>
       <c r="E5" t="n">
-        <v>10472.5</v>
+        <v>10497.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-16.5</v>
+        <v>24.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0024</v>
       </c>
       <c r="H5" t="n">
-        <v>142</v>
+        <v>51.1</v>
       </c>
       <c r="I5" t="n">
-        <v>10267.9</v>
+        <v>10255.5</v>
       </c>
       <c r="J5" t="n">
-        <v>10251.13</v>
+        <v>10332.5</v>
       </c>
       <c r="K5" t="n">
-        <v>10389.45</v>
+        <v>10401.5</v>
       </c>
       <c r="L5" t="n">
-        <v>10527.77</v>
+        <v>10470.5</v>
       </c>
       <c r="M5" t="n">
-        <v>10588.55</v>
+        <v>10543.5</v>
       </c>
       <c r="N5" t="n">
-        <v>10649.32</v>
+        <v>10616.5</v>
       </c>
       <c r="O5" t="n">
-        <v>10865.2</v>
+        <v>10681.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,7 +932,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -957,55 +949,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10471.9</v>
+        <v>10498.1</v>
       </c>
       <c r="C6" t="n">
-        <v>10513.9</v>
+        <v>10532.1</v>
       </c>
       <c r="D6" t="n">
-        <v>10462.8</v>
+        <v>10465</v>
       </c>
       <c r="E6" t="n">
-        <v>10497.3</v>
+        <v>10498.3</v>
       </c>
       <c r="F6" t="n">
-        <v>24.8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H6" t="n">
-        <v>51.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>10255.5</v>
+        <v>10411.7</v>
       </c>
       <c r="J6" t="n">
-        <v>10332.5</v>
+        <v>10450.67</v>
       </c>
       <c r="K6" t="n">
-        <v>10401.5</v>
+        <v>10471.75</v>
       </c>
       <c r="L6" t="n">
-        <v>10470.5</v>
+        <v>10492.82</v>
       </c>
       <c r="M6" t="n">
-        <v>10543.5</v>
+        <v>10522.85</v>
       </c>
       <c r="N6" t="n">
-        <v>10616.5</v>
+        <v>10552.88</v>
       </c>
       <c r="O6" t="n">
-        <v>10681.5</v>
+        <v>10565</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,16 +1009,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1037,77 +1037,79 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10498.1</v>
+        <v>10498.7</v>
       </c>
       <c r="C7" t="n">
-        <v>10532.1</v>
+        <v>10552.6</v>
       </c>
       <c r="D7" t="n">
-        <v>10465</v>
+        <v>10423</v>
       </c>
       <c r="E7" t="n">
-        <v>10498.3</v>
+        <v>10529.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>31.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.003</v>
       </c>
       <c r="H7" t="n">
-        <v>67.09999999999999</v>
+        <v>129.6</v>
       </c>
       <c r="I7" t="n">
-        <v>10411.7</v>
+        <v>10397.9</v>
       </c>
       <c r="J7" t="n">
-        <v>10450.67</v>
+        <v>10431.08</v>
       </c>
       <c r="K7" t="n">
-        <v>10471.75</v>
+        <v>10464.75</v>
       </c>
       <c r="L7" t="n">
-        <v>10492.82</v>
+        <v>10498.42</v>
       </c>
       <c r="M7" t="n">
-        <v>10522.85</v>
+        <v>10531.85</v>
       </c>
       <c r="N7" t="n">
-        <v>10552.88</v>
+        <v>10565.27</v>
       </c>
       <c r="O7" t="n">
-        <v>10565</v>
+        <v>10599.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1123,80 +1125,76 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10498.7</v>
+        <v>10529.1</v>
       </c>
       <c r="C8" t="n">
-        <v>10552.6</v>
+        <v>10546.2</v>
       </c>
       <c r="D8" t="n">
-        <v>10423</v>
+        <v>10443.6</v>
       </c>
       <c r="E8" t="n">
-        <v>10529.4</v>
+        <v>10515.9</v>
       </c>
       <c r="F8" t="n">
-        <v>31.1</v>
+        <v>-13.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0013</v>
       </c>
       <c r="H8" t="n">
-        <v>129.6</v>
+        <v>102.6</v>
       </c>
       <c r="I8" t="n">
-        <v>10397.9</v>
+        <v>10293.4</v>
       </c>
       <c r="J8" t="n">
-        <v>10431.08</v>
+        <v>10420.6</v>
       </c>
       <c r="K8" t="n">
-        <v>10464.75</v>
+        <v>10464.6</v>
       </c>
       <c r="L8" t="n">
-        <v>10498.42</v>
+        <v>10508.6</v>
       </c>
       <c r="M8" t="n">
-        <v>10531.85</v>
+        <v>10594.2</v>
       </c>
       <c r="N8" t="n">
-        <v>10565.27</v>
+        <v>10679.8</v>
       </c>
       <c r="O8" t="n">
-        <v>10599.2</v>
+        <v>10682.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1211,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10529.1</v>
+        <v>10515</v>
       </c>
       <c r="C9" t="n">
-        <v>10546.2</v>
+        <v>10572.2</v>
       </c>
       <c r="D9" t="n">
-        <v>10443.6</v>
+        <v>10447.6</v>
       </c>
       <c r="E9" t="n">
-        <v>10515.9</v>
+        <v>10572.2</v>
       </c>
       <c r="F9" t="n">
-        <v>-13.5</v>
+        <v>56.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0054</v>
       </c>
       <c r="H9" t="n">
-        <v>102.6</v>
+        <v>124.6</v>
       </c>
       <c r="I9" t="n">
-        <v>10293.4</v>
+        <v>10341</v>
       </c>
       <c r="J9" t="n">
-        <v>10420.6</v>
+        <v>10423.8</v>
       </c>
       <c r="K9" t="n">
         <v>10464.6</v>
       </c>
       <c r="L9" t="n">
-        <v>10508.6</v>
+        <v>10505.4</v>
       </c>
       <c r="M9" t="n">
-        <v>10594.2</v>
+        <v>10567.2</v>
       </c>
       <c r="N9" t="n">
-        <v>10679.8</v>
+        <v>10629</v>
       </c>
       <c r="O9" t="n">
-        <v>10682.2</v>
+        <v>10648.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,13 +1272,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1295,57 +1295,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10515</v>
+        <v>10572.4</v>
       </c>
       <c r="C10" t="n">
-        <v>10572.2</v>
+        <v>10623.7</v>
       </c>
       <c r="D10" t="n">
-        <v>10447.6</v>
+        <v>10527.7</v>
       </c>
       <c r="E10" t="n">
-        <v>10572.2</v>
+        <v>10600.4</v>
       </c>
       <c r="F10" t="n">
-        <v>56.3</v>
+        <v>28.2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0027</v>
       </c>
       <c r="H10" t="n">
-        <v>124.6</v>
+        <v>96</v>
       </c>
       <c r="I10" t="n">
-        <v>10341</v>
+        <v>10323</v>
       </c>
       <c r="J10" t="n">
-        <v>10423.8</v>
+        <v>10478.75</v>
       </c>
       <c r="K10" t="n">
-        <v>10464.6</v>
+        <v>10509.9</v>
       </c>
       <c r="L10" t="n">
-        <v>10505.4</v>
+        <v>10541.05</v>
       </c>
       <c r="M10" t="n">
-        <v>10567.2</v>
+        <v>10634.5</v>
       </c>
       <c r="N10" t="n">
-        <v>10629</v>
+        <v>10727.95</v>
       </c>
       <c r="O10" t="n">
-        <v>10648.8</v>
+        <v>10696.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,12 +1353,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1388,69 +1386,71 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10572.4</v>
+        <v>10600.3</v>
       </c>
       <c r="C11" t="n">
-        <v>10623.7</v>
+        <v>10600.3</v>
       </c>
       <c r="D11" t="n">
-        <v>10527.7</v>
+        <v>10512.8</v>
       </c>
       <c r="E11" t="n">
-        <v>10600.4</v>
+        <v>10524.8</v>
       </c>
       <c r="F11" t="n">
-        <v>28.2</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0071</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>87.5</v>
       </c>
       <c r="I11" t="n">
-        <v>10323</v>
+        <v>10431.7</v>
       </c>
       <c r="J11" t="n">
-        <v>10478.75</v>
+        <v>10516.75</v>
       </c>
       <c r="K11" t="n">
-        <v>10509.9</v>
+        <v>10552.4</v>
       </c>
       <c r="L11" t="n">
-        <v>10541.05</v>
+        <v>10588.05</v>
       </c>
       <c r="M11" t="n">
-        <v>10634.5</v>
+        <v>10648.4</v>
       </c>
       <c r="N11" t="n">
-        <v>10727.95</v>
+        <v>10708.75</v>
       </c>
       <c r="O11" t="n">
-        <v>10696.8</v>
+        <v>10719.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1463,84 +1463,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10600.3</v>
+        <v>10524.3</v>
       </c>
       <c r="C12" t="n">
-        <v>10600.3</v>
+        <v>10585.9</v>
       </c>
       <c r="D12" t="n">
-        <v>10512.8</v>
+        <v>10483.1</v>
       </c>
       <c r="E12" t="n">
-        <v>10524.8</v>
+        <v>10585.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-75.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0071</v>
+        <v>0.0058</v>
       </c>
       <c r="H12" t="n">
-        <v>87.5</v>
+        <v>102.8</v>
       </c>
       <c r="I12" t="n">
-        <v>10431.7</v>
+        <v>10425.3</v>
       </c>
       <c r="J12" t="n">
-        <v>10516.75</v>
+        <v>10421.42</v>
       </c>
       <c r="K12" t="n">
-        <v>10552.4</v>
+        <v>10481.05</v>
       </c>
       <c r="L12" t="n">
-        <v>10588.05</v>
+        <v>10540.67</v>
       </c>
       <c r="M12" t="n">
-        <v>10648.4</v>
+        <v>10568.55</v>
       </c>
       <c r="N12" t="n">
-        <v>10708.75</v>
+        <v>10596.42</v>
       </c>
       <c r="O12" t="n">
-        <v>10719.7</v>
+        <v>10687.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1549,55 +1545,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10524.3</v>
+        <v>10585.9</v>
       </c>
       <c r="C13" t="n">
-        <v>10585.9</v>
+        <v>10763.4</v>
       </c>
       <c r="D13" t="n">
-        <v>10483.1</v>
+        <v>10568.7</v>
       </c>
       <c r="E13" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="F13" t="n">
-        <v>61.1</v>
+        <v>131.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0124</v>
       </c>
       <c r="H13" t="n">
-        <v>102.8</v>
+        <v>194.7</v>
       </c>
       <c r="I13" t="n">
-        <v>10425.3</v>
+        <v>10380.3</v>
       </c>
       <c r="J13" t="n">
-        <v>10421.42</v>
+        <v>10508.8</v>
       </c>
       <c r="K13" t="n">
-        <v>10481.05</v>
+        <v>10534.5</v>
       </c>
       <c r="L13" t="n">
-        <v>10540.67</v>
+        <v>10560.2</v>
       </c>
       <c r="M13" t="n">
-        <v>10568.55</v>
+        <v>10637.3</v>
       </c>
       <c r="N13" t="n">
-        <v>10596.42</v>
+        <v>10714.4</v>
       </c>
       <c r="O13" t="n">
-        <v>10687.8</v>
+        <v>10688.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,7 +1608,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1623,67 +1623,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10585.9</v>
+        <v>10717</v>
       </c>
       <c r="C14" t="n">
-        <v>10763.4</v>
+        <v>10720.3</v>
       </c>
       <c r="D14" t="n">
-        <v>10568.7</v>
+        <v>10610.4</v>
       </c>
       <c r="E14" t="n">
-        <v>10717</v>
+        <v>10639.2</v>
       </c>
       <c r="F14" t="n">
-        <v>131.1</v>
+        <v>-77.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0124</v>
+        <v>-0.0073</v>
       </c>
       <c r="H14" t="n">
-        <v>194.7</v>
+        <v>109.9</v>
       </c>
       <c r="I14" t="n">
-        <v>10380.3</v>
+        <v>10374</v>
       </c>
       <c r="J14" t="n">
-        <v>10508.8</v>
+        <v>10547.77</v>
       </c>
       <c r="K14" t="n">
-        <v>10534.5</v>
+        <v>10619.65</v>
       </c>
       <c r="L14" t="n">
-        <v>10560.2</v>
+        <v>10691.53</v>
       </c>
       <c r="M14" t="n">
-        <v>10637.3</v>
+        <v>10814.35</v>
       </c>
       <c r="N14" t="n">
-        <v>10714.4</v>
+        <v>10937.18</v>
       </c>
       <c r="O14" t="n">
-        <v>10688.7</v>
+        <v>10958.1</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,83 +1689,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10717</v>
+        <v>10638.9</v>
       </c>
       <c r="C15" t="n">
-        <v>10720.3</v>
+        <v>10738.8</v>
       </c>
       <c r="D15" t="n">
-        <v>10610.4</v>
+        <v>10599.1</v>
       </c>
       <c r="E15" t="n">
-        <v>10639.2</v>
+        <v>10736.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-77.8</v>
+        <v>97</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0091</v>
       </c>
       <c r="H15" t="n">
-        <v>109.9</v>
+        <v>139.7</v>
       </c>
       <c r="I15" t="n">
-        <v>10374</v>
+        <v>10500.5</v>
       </c>
       <c r="J15" t="n">
-        <v>10547.77</v>
+        <v>10516.23</v>
       </c>
       <c r="K15" t="n">
-        <v>10619.65</v>
+        <v>10584.25</v>
       </c>
       <c r="L15" t="n">
-        <v>10691.53</v>
+        <v>10652.28</v>
       </c>
       <c r="M15" t="n">
-        <v>10814.35</v>
+        <v>10694.15</v>
       </c>
       <c r="N15" t="n">
-        <v>10937.18</v>
+        <v>10736.02</v>
       </c>
       <c r="O15" t="n">
-        <v>10958.1</v>
+        <v>10830.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1775,22 +1773,24 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1801,57 +1801,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10638.9</v>
+        <v>10736.1</v>
       </c>
       <c r="C16" t="n">
-        <v>10738.8</v>
+        <v>10820.9</v>
       </c>
       <c r="D16" t="n">
-        <v>10599.1</v>
+        <v>10736.1</v>
       </c>
       <c r="E16" t="n">
-        <v>10736.2</v>
+        <v>10781.8</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>45.6</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0042</v>
       </c>
       <c r="H16" t="n">
-        <v>139.7</v>
+        <v>84.8</v>
       </c>
       <c r="I16" t="n">
-        <v>10500.5</v>
+        <v>10459.4</v>
       </c>
       <c r="J16" t="n">
-        <v>10516.23</v>
+        <v>10630.13</v>
       </c>
       <c r="K16" t="n">
-        <v>10584.25</v>
+        <v>10666.35</v>
       </c>
       <c r="L16" t="n">
-        <v>10652.28</v>
+        <v>10702.57</v>
       </c>
       <c r="M16" t="n">
-        <v>10694.15</v>
+        <v>10806.05</v>
       </c>
       <c r="N16" t="n">
-        <v>10736.02</v>
+        <v>10909.53</v>
       </c>
       <c r="O16" t="n">
-        <v>10830.2</v>
+        <v>10878.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1862,21 +1862,19 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1885,59 +1883,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10736.1</v>
+        <v>10781.9</v>
       </c>
       <c r="C17" t="n">
-        <v>10820.9</v>
+        <v>10884.3</v>
       </c>
       <c r="D17" t="n">
-        <v>10736.1</v>
+        <v>10770.3</v>
       </c>
       <c r="E17" t="n">
-        <v>10781.8</v>
+        <v>10871</v>
       </c>
       <c r="F17" t="n">
-        <v>45.6</v>
+        <v>89.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0083</v>
       </c>
       <c r="H17" t="n">
-        <v>84.8</v>
+        <v>114</v>
       </c>
       <c r="I17" t="n">
-        <v>10459.4</v>
+        <v>10651.3</v>
       </c>
       <c r="J17" t="n">
-        <v>10630.13</v>
+        <v>10698.65</v>
       </c>
       <c r="K17" t="n">
-        <v>10666.35</v>
+        <v>10739.4</v>
       </c>
       <c r="L17" t="n">
-        <v>10702.57</v>
+        <v>10780.15</v>
       </c>
       <c r="M17" t="n">
-        <v>10806.05</v>
+        <v>10824.2</v>
       </c>
       <c r="N17" t="n">
-        <v>10909.53</v>
+        <v>10868.25</v>
       </c>
       <c r="O17" t="n">
-        <v>10878.5</v>
+        <v>10905.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1948,18 +1942,20 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1974,50 +1970,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10781.9</v>
+        <v>10871.2</v>
       </c>
       <c r="C18" t="n">
-        <v>10884.3</v>
+        <v>10951.1</v>
       </c>
       <c r="D18" t="n">
-        <v>10770.3</v>
+        <v>10864.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10871</v>
+        <v>10908.4</v>
       </c>
       <c r="F18" t="n">
-        <v>89.2</v>
+        <v>37.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0034</v>
       </c>
       <c r="H18" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="I18" t="n">
-        <v>10651.3</v>
+        <v>10656.3</v>
       </c>
       <c r="J18" t="n">
-        <v>10698.65</v>
+        <v>10778.85</v>
       </c>
       <c r="K18" t="n">
-        <v>10739.4</v>
+        <v>10814</v>
       </c>
       <c r="L18" t="n">
-        <v>10780.15</v>
+        <v>10849.15</v>
       </c>
       <c r="M18" t="n">
-        <v>10824.2</v>
+        <v>10928</v>
       </c>
       <c r="N18" t="n">
-        <v>10868.25</v>
+        <v>11006.85</v>
       </c>
       <c r="O18" t="n">
-        <v>10905.7</v>
+        <v>10998.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,20 +2024,18 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2056,50 +2050,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10871.2</v>
+        <v>10907.4</v>
       </c>
       <c r="C19" t="n">
-        <v>10951.1</v>
+        <v>10979.6</v>
       </c>
       <c r="D19" t="n">
-        <v>10864.1</v>
+        <v>10865.4</v>
       </c>
       <c r="E19" t="n">
-        <v>10908.4</v>
+        <v>10897.3</v>
       </c>
       <c r="F19" t="n">
-        <v>37.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>87</v>
+        <v>114.2</v>
       </c>
       <c r="I19" t="n">
-        <v>10656.3</v>
+        <v>10777.1</v>
       </c>
       <c r="J19" t="n">
-        <v>10778.85</v>
+        <v>10821.8</v>
       </c>
       <c r="K19" t="n">
-        <v>10814</v>
+        <v>10864.9</v>
       </c>
       <c r="L19" t="n">
-        <v>10849.15</v>
+        <v>10908</v>
       </c>
       <c r="M19" t="n">
-        <v>10928</v>
+        <v>10951.9</v>
       </c>
       <c r="N19" t="n">
-        <v>11006.85</v>
+        <v>10995.8</v>
       </c>
       <c r="O19" t="n">
-        <v>10998.3</v>
+        <v>11038.1</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,12 +2106,12 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2131,55 +2125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10907.4</v>
+        <v>10897.1</v>
       </c>
       <c r="C20" t="n">
-        <v>10979.6</v>
+        <v>10989.5</v>
       </c>
       <c r="D20" t="n">
-        <v>10865.4</v>
+        <v>10829.3</v>
       </c>
       <c r="E20" t="n">
-        <v>10897.3</v>
+        <v>10868.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.1</v>
+        <v>-29.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0027</v>
       </c>
       <c r="H20" t="n">
-        <v>114.2</v>
+        <v>160.2</v>
       </c>
       <c r="I20" t="n">
-        <v>10777.1</v>
+        <v>10751.2</v>
       </c>
       <c r="J20" t="n">
-        <v>10821.8</v>
+        <v>10770.5</v>
       </c>
       <c r="K20" t="n">
-        <v>10864.9</v>
+        <v>10840.2</v>
       </c>
       <c r="L20" t="n">
-        <v>10908</v>
+        <v>10909.9</v>
       </c>
       <c r="M20" t="n">
-        <v>10951.9</v>
+        <v>10954.4</v>
       </c>
       <c r="N20" t="n">
-        <v>10995.8</v>
+        <v>10998.9</v>
       </c>
       <c r="O20" t="n">
-        <v>11038.1</v>
+        <v>11093.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2187,12 +2185,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2213,57 +2213,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10897.1</v>
+        <v>10868.1</v>
       </c>
       <c r="C21" t="n">
-        <v>10989.5</v>
+        <v>10917.4</v>
       </c>
       <c r="D21" t="n">
-        <v>10829.3</v>
+        <v>10832.5</v>
       </c>
       <c r="E21" t="n">
-        <v>10868.1</v>
+        <v>10857.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-29.2</v>
+        <v>-10.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>160.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>10751.2</v>
+        <v>10669.1</v>
       </c>
       <c r="J21" t="n">
-        <v>10770.5</v>
+        <v>10687.25</v>
       </c>
       <c r="K21" t="n">
-        <v>10840.2</v>
+        <v>10788</v>
       </c>
       <c r="L21" t="n">
-        <v>10909.9</v>
+        <v>10888.75</v>
       </c>
       <c r="M21" t="n">
-        <v>10954.4</v>
+        <v>10948.2</v>
       </c>
       <c r="N21" t="n">
-        <v>10998.9</v>
+        <v>11007.65</v>
       </c>
       <c r="O21" t="n">
-        <v>11093.8</v>
+        <v>11149.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,20 +2271,16 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2306,50 +2302,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10868.1</v>
+        <v>10857.6</v>
       </c>
       <c r="C22" t="n">
-        <v>10917.4</v>
+        <v>10932.5</v>
       </c>
       <c r="D22" t="n">
-        <v>10832.5</v>
+        <v>10855.2</v>
       </c>
       <c r="E22" t="n">
-        <v>10857.7</v>
+        <v>10879.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.4</v>
+        <v>21.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H22" t="n">
-        <v>84.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I22" t="n">
-        <v>10669.1</v>
+        <v>10747.6</v>
       </c>
       <c r="J22" t="n">
-        <v>10687.25</v>
+        <v>10764.17</v>
       </c>
       <c r="K22" t="n">
-        <v>10788</v>
+        <v>10815.25</v>
       </c>
       <c r="L22" t="n">
-        <v>10888.75</v>
+        <v>10866.33</v>
       </c>
       <c r="M22" t="n">
-        <v>10948.2</v>
+        <v>10900.15</v>
       </c>
       <c r="N22" t="n">
-        <v>11007.65</v>
+        <v>10933.98</v>
       </c>
       <c r="O22" t="n">
-        <v>11149.7</v>
+        <v>11002.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,11 +2358,13 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2379,59 +2377,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10857.6</v>
+        <v>10879</v>
       </c>
       <c r="C23" t="n">
-        <v>10932.5</v>
+        <v>10952.3</v>
       </c>
       <c r="D23" t="n">
-        <v>10855.2</v>
+        <v>10836.9</v>
       </c>
       <c r="E23" t="n">
-        <v>10879.4</v>
+        <v>10888.3</v>
       </c>
       <c r="F23" t="n">
-        <v>21.7</v>
+        <v>8.9</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="H23" t="n">
-        <v>77.3</v>
+        <v>115.4</v>
       </c>
       <c r="I23" t="n">
-        <v>10747.6</v>
+        <v>10777.9</v>
       </c>
       <c r="J23" t="n">
-        <v>10764.17</v>
+        <v>10794.88</v>
       </c>
       <c r="K23" t="n">
-        <v>10815.25</v>
+        <v>10840.75</v>
       </c>
       <c r="L23" t="n">
-        <v>10866.33</v>
+        <v>10886.63</v>
       </c>
       <c r="M23" t="n">
-        <v>10900.15</v>
+        <v>10918.05</v>
       </c>
       <c r="N23" t="n">
-        <v>10933.98</v>
+        <v>10949.48</v>
       </c>
       <c r="O23" t="n">
-        <v>11002.3</v>
+        <v>11009.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,10 +2433,12 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2452,8 +2448,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2463,55 +2461,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10879</v>
+        <v>10888.5</v>
       </c>
       <c r="C24" t="n">
-        <v>10952.3</v>
+        <v>10944.8</v>
       </c>
       <c r="D24" t="n">
-        <v>10836.9</v>
+        <v>10865.3</v>
       </c>
       <c r="E24" t="n">
-        <v>10888.3</v>
+        <v>10867.9</v>
       </c>
       <c r="F24" t="n">
-        <v>8.9</v>
+        <v>-20.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0019</v>
       </c>
       <c r="H24" t="n">
-        <v>115.4</v>
+        <v>79.5</v>
       </c>
       <c r="I24" t="n">
-        <v>10777.9</v>
+        <v>10721.5</v>
       </c>
       <c r="J24" t="n">
-        <v>10794.88</v>
+        <v>10769.75</v>
       </c>
       <c r="K24" t="n">
-        <v>10840.75</v>
+        <v>10830.6</v>
       </c>
       <c r="L24" t="n">
-        <v>10886.63</v>
+        <v>10891.45</v>
       </c>
       <c r="M24" t="n">
-        <v>10918.05</v>
+        <v>10946</v>
       </c>
       <c r="N24" t="n">
-        <v>10949.48</v>
+        <v>11000.55</v>
       </c>
       <c r="O24" t="n">
-        <v>11009.8</v>
+        <v>11067.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,25 +2521,19 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2549,57 +2545,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10888.5</v>
+        <v>10867.9</v>
       </c>
       <c r="C25" t="n">
-        <v>10944.8</v>
+        <v>10959.9</v>
       </c>
       <c r="D25" t="n">
-        <v>10865.3</v>
+        <v>10855.2</v>
       </c>
       <c r="E25" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.4</v>
+        <v>33.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.0031</v>
       </c>
       <c r="H25" t="n">
-        <v>79.5</v>
+        <v>104.7</v>
       </c>
       <c r="I25" t="n">
-        <v>10721.5</v>
+        <v>10785.8</v>
       </c>
       <c r="J25" t="n">
-        <v>10769.75</v>
+        <v>10769.83</v>
       </c>
       <c r="K25" t="n">
-        <v>10830.6</v>
+        <v>10828.15</v>
       </c>
       <c r="L25" t="n">
-        <v>10891.45</v>
+        <v>10886.48</v>
       </c>
       <c r="M25" t="n">
-        <v>10946</v>
+        <v>10907.65</v>
       </c>
       <c r="N25" t="n">
-        <v>11000.55</v>
+        <v>10928.83</v>
       </c>
       <c r="O25" t="n">
-        <v>11067.7</v>
+        <v>11024.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2612,14 +2608,18 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2631,57 +2631,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10867.9</v>
+        <v>10901.1</v>
       </c>
       <c r="C26" t="n">
-        <v>10959.9</v>
+        <v>10910.9</v>
       </c>
       <c r="D26" t="n">
-        <v>10855.2</v>
+        <v>10829</v>
       </c>
       <c r="E26" t="n">
-        <v>10901.1</v>
+        <v>10862.5</v>
       </c>
       <c r="F26" t="n">
-        <v>33.2</v>
+        <v>-38.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="H26" t="n">
-        <v>104.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>10785.8</v>
+        <v>10750.5</v>
       </c>
       <c r="J26" t="n">
-        <v>10769.83</v>
+        <v>10793.17</v>
       </c>
       <c r="K26" t="n">
-        <v>10828.15</v>
+        <v>10848.75</v>
       </c>
       <c r="L26" t="n">
-        <v>10886.48</v>
+        <v>10904.32</v>
       </c>
       <c r="M26" t="n">
-        <v>10907.65</v>
+        <v>10953.45</v>
       </c>
       <c r="N26" t="n">
-        <v>10928.83</v>
+        <v>11002.57</v>
       </c>
       <c r="O26" t="n">
-        <v>11024.3</v>
+        <v>11064.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,23 +2689,21 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2717,57 +2715,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10901.1</v>
+        <v>10862.9</v>
       </c>
       <c r="C27" t="n">
-        <v>10910.9</v>
+        <v>10893.2</v>
       </c>
       <c r="D27" t="n">
-        <v>10829</v>
+        <v>10825.4</v>
       </c>
       <c r="E27" t="n">
-        <v>10862.5</v>
+        <v>10844.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-38.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0017</v>
       </c>
       <c r="H27" t="n">
-        <v>81.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I27" t="n">
-        <v>10750.5</v>
+        <v>10747.1</v>
       </c>
       <c r="J27" t="n">
-        <v>10793.17</v>
+        <v>10776.87</v>
       </c>
       <c r="K27" t="n">
-        <v>10848.75</v>
+        <v>10821.55</v>
       </c>
       <c r="L27" t="n">
-        <v>10904.32</v>
+        <v>10866.23</v>
       </c>
       <c r="M27" t="n">
-        <v>10953.45</v>
+        <v>10903.45</v>
       </c>
       <c r="N27" t="n">
-        <v>11002.57</v>
+        <v>10940.68</v>
       </c>
       <c r="O27" t="n">
-        <v>11064.6</v>
+        <v>10992.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2775,14 +2773,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2808,50 +2804,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10862.9</v>
+        <v>10844.2</v>
       </c>
       <c r="C28" t="n">
-        <v>10893.2</v>
+        <v>10863.8</v>
       </c>
       <c r="D28" t="n">
-        <v>10825.4</v>
+        <v>10809.6</v>
       </c>
       <c r="E28" t="n">
-        <v>10844.2</v>
+        <v>10833.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-18.3</v>
+        <v>-11</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>67.8</v>
+        <v>54.2</v>
       </c>
       <c r="I28" t="n">
-        <v>10747.1</v>
+        <v>10757.6</v>
       </c>
       <c r="J28" t="n">
-        <v>10776.87</v>
+        <v>10768.85</v>
       </c>
       <c r="K28" t="n">
-        <v>10821.55</v>
+        <v>10810.3</v>
       </c>
       <c r="L28" t="n">
-        <v>10866.23</v>
+        <v>10851.75</v>
       </c>
       <c r="M28" t="n">
-        <v>10903.45</v>
+        <v>10878.1</v>
       </c>
       <c r="N28" t="n">
-        <v>10940.68</v>
+        <v>10904.45</v>
       </c>
       <c r="O28" t="n">
-        <v>10992.8</v>
+        <v>10961</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,10 +2855,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2890,65 +2888,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10844.2</v>
+        <v>10833.6</v>
       </c>
       <c r="C29" t="n">
-        <v>10863.8</v>
+        <v>10837</v>
       </c>
       <c r="D29" t="n">
-        <v>10809.6</v>
+        <v>10756.4</v>
       </c>
       <c r="E29" t="n">
-        <v>10833.2</v>
+        <v>10772.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-11</v>
+        <v>-60.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0056</v>
       </c>
       <c r="H29" t="n">
-        <v>54.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>10757.6</v>
+        <v>10755.4</v>
       </c>
       <c r="J29" t="n">
-        <v>10768.85</v>
+        <v>10777.25</v>
       </c>
       <c r="K29" t="n">
-        <v>10810.3</v>
+        <v>10806.1</v>
       </c>
       <c r="L29" t="n">
-        <v>10851.75</v>
+        <v>10834.95</v>
       </c>
       <c r="M29" t="n">
-        <v>10878.1</v>
+        <v>10860.3</v>
       </c>
       <c r="N29" t="n">
-        <v>10904.45</v>
+        <v>10885.65</v>
       </c>
       <c r="O29" t="n">
-        <v>10961</v>
+        <v>10918</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2960,79 +2960,73 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10833.6</v>
+        <v>10772.5</v>
       </c>
       <c r="C30" t="n">
-        <v>10837</v>
+        <v>10789.7</v>
       </c>
       <c r="D30" t="n">
-        <v>10756.4</v>
+        <v>10723.7</v>
       </c>
       <c r="E30" t="n">
-        <v>10772.7</v>
+        <v>10750.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-60.5</v>
+        <v>-22.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0021</v>
       </c>
       <c r="H30" t="n">
-        <v>80.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I30" t="n">
-        <v>10755.4</v>
+        <v>10675.8</v>
       </c>
       <c r="J30" t="n">
-        <v>10777.25</v>
+        <v>10680.1</v>
       </c>
       <c r="K30" t="n">
-        <v>10806.1</v>
+        <v>10732.4</v>
       </c>
       <c r="L30" t="n">
-        <v>10834.95</v>
+        <v>10784.7</v>
       </c>
       <c r="M30" t="n">
-        <v>10860.3</v>
+        <v>10813</v>
       </c>
       <c r="N30" t="n">
-        <v>10885.65</v>
+        <v>10841.3</v>
       </c>
       <c r="O30" t="n">
-        <v>10918</v>
+        <v>10917.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3056,50 +3050,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10772.5</v>
+        <v>10750</v>
       </c>
       <c r="C31" t="n">
-        <v>10789.7</v>
+        <v>10793.6</v>
       </c>
       <c r="D31" t="n">
-        <v>10723.7</v>
+        <v>10717.6</v>
       </c>
       <c r="E31" t="n">
-        <v>10750.1</v>
+        <v>10720.3</v>
       </c>
       <c r="F31" t="n">
-        <v>-22.6</v>
+        <v>-29.8</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0028</v>
       </c>
       <c r="H31" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I31" t="n">
-        <v>10675.8</v>
+        <v>10657.7</v>
       </c>
       <c r="J31" t="n">
-        <v>10680.1</v>
+        <v>10680.8</v>
       </c>
       <c r="K31" t="n">
-        <v>10732.4</v>
+        <v>10717.1</v>
       </c>
       <c r="L31" t="n">
-        <v>10784.7</v>
+        <v>10753.4</v>
       </c>
       <c r="M31" t="n">
-        <v>10813</v>
+        <v>10783.1</v>
       </c>
       <c r="N31" t="n">
-        <v>10841.3</v>
+        <v>10812.8</v>
       </c>
       <c r="O31" t="n">
-        <v>10917.6</v>
+        <v>10855.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,13 +3106,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3131,55 +3127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10750</v>
+        <v>10720.9</v>
       </c>
       <c r="C32" t="n">
-        <v>10793.6</v>
+        <v>10779.9</v>
       </c>
       <c r="D32" t="n">
-        <v>10717.6</v>
+        <v>10701.7</v>
       </c>
       <c r="E32" t="n">
-        <v>10720.3</v>
+        <v>10728</v>
       </c>
       <c r="F32" t="n">
-        <v>-29.8</v>
+        <v>7.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0007</v>
       </c>
       <c r="H32" t="n">
-        <v>76</v>
+        <v>78.2</v>
       </c>
       <c r="I32" t="n">
-        <v>10657.7</v>
+        <v>10641.6</v>
       </c>
       <c r="J32" t="n">
-        <v>10680.8</v>
+        <v>10626.65</v>
       </c>
       <c r="K32" t="n">
-        <v>10717.1</v>
+        <v>10682.3</v>
       </c>
       <c r="L32" t="n">
-        <v>10753.4</v>
+        <v>10737.95</v>
       </c>
       <c r="M32" t="n">
-        <v>10783.1</v>
+        <v>10758.3</v>
       </c>
       <c r="N32" t="n">
-        <v>10812.8</v>
+        <v>10778.65</v>
       </c>
       <c r="O32" t="n">
-        <v>10855.7</v>
+        <v>10869.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,14 +3187,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3202,8 +3200,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3222,50 +3222,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10720.9</v>
+        <v>10727.8</v>
       </c>
       <c r="C33" t="n">
-        <v>10779.9</v>
+        <v>10766</v>
       </c>
       <c r="D33" t="n">
-        <v>10701.7</v>
+        <v>10701.1</v>
       </c>
       <c r="E33" t="n">
-        <v>10728</v>
+        <v>10743.4</v>
       </c>
       <c r="F33" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0014</v>
       </c>
       <c r="H33" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>10641.6</v>
+        <v>10623.5</v>
       </c>
       <c r="J33" t="n">
-        <v>10626.65</v>
+        <v>10643.4</v>
       </c>
       <c r="K33" t="n">
-        <v>10682.3</v>
+        <v>10688.9</v>
       </c>
       <c r="L33" t="n">
-        <v>10737.95</v>
+        <v>10734.4</v>
       </c>
       <c r="M33" t="n">
-        <v>10758.3</v>
+        <v>10767.1</v>
       </c>
       <c r="N33" t="n">
-        <v>10778.65</v>
+        <v>10799.8</v>
       </c>
       <c r="O33" t="n">
-        <v>10869.6</v>
+        <v>10858.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3278,18 +3278,14 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3308,50 +3304,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10727.8</v>
+        <v>10743.2</v>
       </c>
       <c r="C34" t="n">
-        <v>10766</v>
+        <v>10766.9</v>
       </c>
       <c r="D34" t="n">
-        <v>10701.1</v>
+        <v>10684.4</v>
       </c>
       <c r="E34" t="n">
-        <v>10743.4</v>
+        <v>10748.2</v>
       </c>
       <c r="F34" t="n">
-        <v>15.4</v>
+        <v>4.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H34" t="n">
-        <v>64.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I34" t="n">
-        <v>10623.5</v>
+        <v>10636.2</v>
       </c>
       <c r="J34" t="n">
-        <v>10643.4</v>
+        <v>10683.43</v>
       </c>
       <c r="K34" t="n">
-        <v>10688.9</v>
+        <v>10710.95</v>
       </c>
       <c r="L34" t="n">
-        <v>10734.4</v>
+        <v>10738.48</v>
       </c>
       <c r="M34" t="n">
-        <v>10767.1</v>
+        <v>10775.85</v>
       </c>
       <c r="N34" t="n">
-        <v>10799.8</v>
+        <v>10813.23</v>
       </c>
       <c r="O34" t="n">
-        <v>10858.1</v>
+        <v>10830.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3359,10 +3355,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3383,57 +3381,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>10743.2</v>
+        <v>10748.1</v>
       </c>
       <c r="C35" t="n">
-        <v>10766.9</v>
+        <v>10831.6</v>
       </c>
       <c r="D35" t="n">
-        <v>10684.4</v>
+        <v>10734.9</v>
       </c>
       <c r="E35" t="n">
-        <v>10748.2</v>
+        <v>10816.6</v>
       </c>
       <c r="F35" t="n">
-        <v>4.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0064</v>
       </c>
       <c r="H35" t="n">
-        <v>82.5</v>
+        <v>96.7</v>
       </c>
       <c r="I35" t="n">
-        <v>10636.2</v>
+        <v>10601.9</v>
       </c>
       <c r="J35" t="n">
-        <v>10683.43</v>
+        <v>10676.98</v>
       </c>
       <c r="K35" t="n">
-        <v>10710.95</v>
+        <v>10706.95</v>
       </c>
       <c r="L35" t="n">
-        <v>10738.48</v>
+        <v>10736.93</v>
       </c>
       <c r="M35" t="n">
-        <v>10775.85</v>
+        <v>10789.45</v>
       </c>
       <c r="N35" t="n">
-        <v>10813.23</v>
+        <v>10841.98</v>
       </c>
       <c r="O35" t="n">
-        <v>10830.9</v>
+        <v>10849.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3441,21 +3439,23 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3467,57 +3467,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10748.1</v>
+        <v>10816.3</v>
       </c>
       <c r="C36" t="n">
-        <v>10831.6</v>
+        <v>10864.8</v>
       </c>
       <c r="D36" t="n">
-        <v>10734.9</v>
+        <v>10799</v>
       </c>
       <c r="E36" t="n">
-        <v>10816.6</v>
+        <v>10854.3</v>
       </c>
       <c r="F36" t="n">
-        <v>68.40000000000001</v>
+        <v>37.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0035</v>
       </c>
       <c r="H36" t="n">
-        <v>96.7</v>
+        <v>65.8</v>
       </c>
       <c r="I36" t="n">
-        <v>10601.9</v>
+        <v>10638.2</v>
       </c>
       <c r="J36" t="n">
-        <v>10676.98</v>
+        <v>10736.58</v>
       </c>
       <c r="K36" t="n">
-        <v>10706.95</v>
+        <v>10768.25</v>
       </c>
       <c r="L36" t="n">
-        <v>10736.93</v>
+        <v>10799.92</v>
       </c>
       <c r="M36" t="n">
-        <v>10789.45</v>
+        <v>10864.95</v>
       </c>
       <c r="N36" t="n">
-        <v>10841.98</v>
+        <v>10929.97</v>
       </c>
       <c r="O36" t="n">
-        <v>10849.4</v>
+        <v>10928.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3528,20 +3528,18 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3560,50 +3558,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10816.3</v>
+        <v>10854.6</v>
       </c>
       <c r="C37" t="n">
-        <v>10864.8</v>
+        <v>10887</v>
       </c>
       <c r="D37" t="n">
-        <v>10799</v>
+        <v>10825.8</v>
       </c>
       <c r="E37" t="n">
-        <v>10854.3</v>
+        <v>10886.2</v>
       </c>
       <c r="F37" t="n">
-        <v>37.7</v>
+        <v>31.9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0029</v>
       </c>
       <c r="H37" t="n">
-        <v>65.8</v>
+        <v>61.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10638.2</v>
+        <v>10733.2</v>
       </c>
       <c r="J37" t="n">
-        <v>10736.58</v>
+        <v>10799.7</v>
       </c>
       <c r="K37" t="n">
-        <v>10768.25</v>
+        <v>10821.4</v>
       </c>
       <c r="L37" t="n">
-        <v>10799.92</v>
+        <v>10843.1</v>
       </c>
       <c r="M37" t="n">
-        <v>10864.95</v>
+        <v>10887.2</v>
       </c>
       <c r="N37" t="n">
-        <v>10929.97</v>
+        <v>10931.3</v>
       </c>
       <c r="O37" t="n">
-        <v>10928.3</v>
+        <v>10930.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3614,7 +3612,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3644,50 +3642,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10854.6</v>
+        <v>10886.2</v>
       </c>
       <c r="C38" t="n">
-        <v>10887</v>
+        <v>10920.5</v>
       </c>
       <c r="D38" t="n">
-        <v>10825.8</v>
+        <v>10855.6</v>
       </c>
       <c r="E38" t="n">
-        <v>10886.2</v>
+        <v>10878.1</v>
       </c>
       <c r="F38" t="n">
-        <v>31.9</v>
+        <v>-8.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>61.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>10733.2</v>
+        <v>10764.6</v>
       </c>
       <c r="J38" t="n">
-        <v>10799.7</v>
+        <v>10839.9</v>
       </c>
       <c r="K38" t="n">
-        <v>10821.4</v>
+        <v>10855.6</v>
       </c>
       <c r="L38" t="n">
-        <v>10843.1</v>
+        <v>10871.3</v>
       </c>
       <c r="M38" t="n">
-        <v>10887.2</v>
+        <v>10916.8</v>
       </c>
       <c r="N38" t="n">
-        <v>10931.3</v>
+        <v>10962.3</v>
       </c>
       <c r="O38" t="n">
-        <v>10930.6</v>
+        <v>10948.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,17 +3693,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3721,63 +3721,67 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>